--- a/Excels/Items.xlsx
+++ b/Excels/Items.xlsx
@@ -331,7 +331,7 @@
         </is>
       </c>
       <c r="AA2" s="0">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="AV2" s="0" t="inlineStr">
         <is>
@@ -376,7 +376,7 @@
         </is>
       </c>
       <c r="AA3" s="0">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AV3" s="0" t="inlineStr">
         <is>
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="AA5" s="0">
-        <v>206</v>
+        <v>162</v>
       </c>
       <c r="AV5" s="0" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="AA12" s="0">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AV12" s="0" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="AA13" s="0">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="AV13" s="0" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="AA17" s="0">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AV17" s="0" t="inlineStr">
         <is>
@@ -1022,12 +1022,12 @@
     <row r="18" spans="1:48">
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>Beautiful Fashion Wax</t>
+          <t>Baby Blueberry Material</t>
         </is>
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="O18" s="0" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="R18" s="0" t="inlineStr">
         <is>
-          <t>11501.0829302672</t>
+          <t>13000.00</t>
         </is>
       </c>
       <c r="S18" s="0" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="T18" s="0" t="inlineStr">
         <is>
-          <t>13000.00</t>
+          <t>14000.00</t>
         </is>
       </c>
       <c r="Z18" s="0" t="inlineStr">
@@ -1056,18 +1056,18 @@
         </is>
       </c>
       <c r="AA18" s="0">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="AV18" s="0" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>215</t>
         </is>
       </c>
     </row>
     <row r="19" spans="1:48">
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>BELLDAM</t>
+          <t>Beautiful Fashion Wax</t>
         </is>
       </c>
       <c r="G19" s="0" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="R19" s="0" t="inlineStr">
         <is>
-          <t>4600.00</t>
+          <t>11501.0829302672</t>
         </is>
       </c>
       <c r="S19" s="0" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="T19" s="0" t="inlineStr">
         <is>
-          <t>5000.00</t>
+          <t>13000.00</t>
         </is>
       </c>
       <c r="Z19" s="0" t="inlineStr">
@@ -1101,23 +1101,23 @@
         </is>
       </c>
       <c r="AA19" s="0">
-        <v>622</v>
+        <v>24</v>
       </c>
       <c r="AV19" s="0" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>203</t>
         </is>
       </c>
     </row>
     <row r="20" spans="1:48">
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>Blueberry NG DIGITAL </t>
+          <t>BELLDAM</t>
         </is>
       </c>
       <c r="G20" s="0" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O20" s="0" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="R20" s="0" t="inlineStr">
         <is>
-          <t>10600.00</t>
+          <t>4600.00</t>
         </is>
       </c>
       <c r="S20" s="0" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="T20" s="0" t="inlineStr">
         <is>
-          <t>12000.00</t>
+          <t>5000.00</t>
         </is>
       </c>
       <c r="Z20" s="0" t="inlineStr">
@@ -1146,23 +1146,23 @@
         </is>
       </c>
       <c r="AA20" s="0">
-        <v>68</v>
+        <v>580</v>
       </c>
       <c r="AV20" s="0" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>141</t>
         </is>
       </c>
     </row>
     <row r="21" spans="1:48">
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>BRITISH GLITTER GOLD </t>
+          <t>Blueberry NG DIGITAL </t>
         </is>
       </c>
       <c r="G21" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="O21" s="0" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="R21" s="0" t="inlineStr">
         <is>
-          <t>30000.00</t>
+          <t>10600.00</t>
         </is>
       </c>
       <c r="S21" s="0" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="T21" s="0" t="inlineStr">
         <is>
-          <t>35000.00</t>
+          <t>12000.00</t>
         </is>
       </c>
       <c r="Z21" s="0" t="inlineStr">
@@ -1191,18 +1191,18 @@
         </is>
       </c>
       <c r="AA21" s="0">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="AV21" s="0" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="22" spans="1:48">
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>BRITISH HOLLAND PLAIN</t>
+          <t>BRITISH GLITTER GOLD </t>
         </is>
       </c>
       <c r="G22" s="0" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="R22" s="0" t="inlineStr">
         <is>
-          <t>25051.2820512821</t>
+          <t>30000.00</t>
         </is>
       </c>
       <c r="S22" s="0" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="T22" s="0" t="inlineStr">
         <is>
-          <t>30000.00</t>
+          <t>35000.00</t>
         </is>
       </c>
       <c r="Z22" s="0" t="inlineStr">
@@ -1236,23 +1236,23 @@
         </is>
       </c>
       <c r="AA22" s="0">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AV22" s="0" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
     </row>
     <row r="23" spans="1:48">
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>CHECY POLISH MEN LACE A</t>
+          <t>BRITISH HOLLAND PLAIN</t>
         </is>
       </c>
       <c r="G23" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O23" s="0" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="R23" s="0" t="inlineStr">
         <is>
-          <t>150000.00</t>
+          <t>25051.2820512821</t>
         </is>
       </c>
       <c r="S23" s="0" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="T23" s="0" t="inlineStr">
         <is>
-          <t>230000.00</t>
+          <t>30000.00</t>
         </is>
       </c>
       <c r="Z23" s="0" t="inlineStr">
@@ -1280,21 +1280,19 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA23" s="0" t="inlineStr">
-        <is>
-          <t>12.5</t>
-        </is>
+      <c r="AA23" s="0">
+        <v>8</v>
       </c>
       <c r="AV23" s="0" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>93</t>
         </is>
       </c>
     </row>
     <row r="24" spans="1:48">
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>CHECY POLISH MEN LACE B</t>
+          <t>CHECY POLISH MEN LACE A</t>
         </is>
       </c>
       <c r="G24" s="0" t="inlineStr">
@@ -1309,7 +1307,7 @@
       </c>
       <c r="R24" s="0" t="inlineStr">
         <is>
-          <t>135000.00</t>
+          <t>150000.00</t>
         </is>
       </c>
       <c r="S24" s="0" t="inlineStr">
@@ -1319,7 +1317,7 @@
       </c>
       <c r="T24" s="0" t="inlineStr">
         <is>
-          <t>200000.00</t>
+          <t>230000.00</t>
         </is>
       </c>
       <c r="Z24" s="0" t="inlineStr">
@@ -1327,24 +1325,26 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA24" s="0">
-        <v>2</v>
+      <c r="AA24" s="0" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
       </c>
       <c r="AV24" s="0" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>168</t>
         </is>
       </c>
     </row>
     <row r="25" spans="1:48">
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>CHIGANVY COTONOU PLAIN</t>
+          <t>CHECY POLISH MEN LACE B</t>
         </is>
       </c>
       <c r="G25" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O25" s="0" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="R25" s="0" t="inlineStr">
         <is>
-          <t>18000.00</t>
+          <t>135000.00</t>
         </is>
       </c>
       <c r="S25" s="0" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="T25" s="0" t="inlineStr">
         <is>
-          <t>20000.00</t>
+          <t>200000.00</t>
         </is>
       </c>
       <c r="Z25" s="0" t="inlineStr">
@@ -1373,18 +1373,18 @@
         </is>
       </c>
       <c r="AA25" s="0">
-        <v>180</v>
+        <v>2</v>
       </c>
       <c r="AV25" s="0" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>169</t>
         </is>
       </c>
     </row>
     <row r="26" spans="1:48">
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>CHIGANVY COTTON POPLIN</t>
+          <t>CHIGANVY COTONOU PLAIN</t>
         </is>
       </c>
       <c r="G26" s="0" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="R26" s="0" t="inlineStr">
         <is>
-          <t>24981.1335407589</t>
+          <t>18000.00</t>
         </is>
       </c>
       <c r="S26" s="0" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="T26" s="0" t="inlineStr">
         <is>
-          <t>27000.00</t>
+          <t>20000.00</t>
         </is>
       </c>
       <c r="Z26" s="0" t="inlineStr">
@@ -1418,18 +1418,18 @@
         </is>
       </c>
       <c r="AA26" s="0">
-        <v>359</v>
+        <v>178</v>
       </c>
       <c r="AV26" s="0" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>106</t>
         </is>
       </c>
     </row>
     <row r="27" spans="1:48">
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>CHIGANVY GOLD</t>
+          <t>CHIGANVY COTTON POPLIN</t>
         </is>
       </c>
       <c r="G27" s="0" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="R27" s="0" t="inlineStr">
         <is>
-          <t>22500.00</t>
+          <t>24986.350073268</t>
         </is>
       </c>
       <c r="S27" s="0" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T27" s="0" t="inlineStr">
         <is>
-          <t>25000.00</t>
+          <t>27000.00</t>
         </is>
       </c>
       <c r="Z27" s="0" t="inlineStr">
@@ -1463,18 +1463,18 @@
         </is>
       </c>
       <c r="AA27" s="0">
-        <v>22</v>
+        <v>410</v>
       </c>
       <c r="AV27" s="0" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>104</t>
         </is>
       </c>
     </row>
     <row r="28" spans="1:48">
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>CHIGANVY INDIA</t>
+          <t>CHIGANVY GOLD</t>
         </is>
       </c>
       <c r="G28" s="0" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="R28" s="0" t="inlineStr">
         <is>
-          <t>7105.0495076194</t>
+          <t>22500.00</t>
         </is>
       </c>
       <c r="S28" s="0" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="T28" s="0" t="inlineStr">
         <is>
-          <t>8000.00</t>
+          <t>25000.00</t>
         </is>
       </c>
       <c r="Z28" s="0" t="inlineStr">
@@ -1508,18 +1508,18 @@
         </is>
       </c>
       <c r="AA28" s="0">
-        <v>125</v>
+        <v>16</v>
       </c>
       <c r="AV28" s="0" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>105</t>
         </is>
       </c>
     </row>
     <row r="29" spans="1:48">
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>Chiganvy Satin Royal</t>
+          <t>CHIGANVY INDIA</t>
         </is>
       </c>
       <c r="G29" s="0" t="inlineStr">
@@ -1527,11 +1527,6 @@
           <t>ATAMPA</t>
         </is>
       </c>
-      <c r="H29" s="0" t="inlineStr">
-        <is>
-          <t>FAHAD TAHIR</t>
-        </is>
-      </c>
       <c r="O29" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -1539,7 +1534,7 @@
       </c>
       <c r="R29" s="0" t="inlineStr">
         <is>
-          <t>35000.00</t>
+          <t>7105.0495076194</t>
         </is>
       </c>
       <c r="S29" s="0" t="inlineStr">
@@ -1549,7 +1544,7 @@
       </c>
       <c r="T29" s="0" t="inlineStr">
         <is>
-          <t>40000.00</t>
+          <t>8000.00</t>
         </is>
       </c>
       <c r="Z29" s="0" t="inlineStr">
@@ -1558,18 +1553,18 @@
         </is>
       </c>
       <c r="AA29" s="0">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="AV29" s="0" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>139</t>
         </is>
       </c>
     </row>
     <row r="30" spans="1:48">
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>Chiganvy Sky Poplin</t>
+          <t>Chiganvy Satin Royal</t>
         </is>
       </c>
       <c r="G30" s="0" t="inlineStr">
@@ -1589,7 +1584,7 @@
       </c>
       <c r="R30" s="0" t="inlineStr">
         <is>
-          <t>28000.00</t>
+          <t>35000.00</t>
         </is>
       </c>
       <c r="S30" s="0" t="inlineStr">
@@ -1599,7 +1594,7 @@
       </c>
       <c r="T30" s="0" t="inlineStr">
         <is>
-          <t>30000.00</t>
+          <t>40000.00</t>
         </is>
       </c>
       <c r="Z30" s="0" t="inlineStr">
@@ -1608,18 +1603,18 @@
         </is>
       </c>
       <c r="AA30" s="0">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="AV30" s="0" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>204</t>
         </is>
       </c>
     </row>
     <row r="31" spans="1:48">
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>COTED'VIORE MEDIUM</t>
+          <t>Chiganvy Sky Poplin</t>
         </is>
       </c>
       <c r="G31" s="0" t="inlineStr">
@@ -1627,6 +1622,11 @@
           <t>ATAMPA</t>
         </is>
       </c>
+      <c r="H31" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
+        </is>
+      </c>
       <c r="O31" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="R31" s="0" t="inlineStr">
         <is>
-          <t>13500.00</t>
+          <t>28000.00</t>
         </is>
       </c>
       <c r="S31" s="0" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="T31" s="0" t="inlineStr">
         <is>
-          <t>15000.00</t>
+          <t>30000.00</t>
         </is>
       </c>
       <c r="Z31" s="0" t="inlineStr">
@@ -1653,23 +1653,23 @@
         </is>
       </c>
       <c r="AA31" s="0">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AV31" s="0" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>202</t>
         </is>
       </c>
     </row>
     <row r="32" spans="1:48">
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>COUS COUS LACE</t>
+          <t>COTED'VIORE MEDIUM</t>
         </is>
       </c>
       <c r="G32" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O32" s="0" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="R32" s="0" t="inlineStr">
         <is>
-          <t>45234.375</t>
+          <t>13500.00</t>
         </is>
       </c>
       <c r="S32" s="0" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="T32" s="0" t="inlineStr">
         <is>
-          <t>55000.00</t>
+          <t>15000.00</t>
         </is>
       </c>
       <c r="Z32" s="0" t="inlineStr">
@@ -1698,23 +1698,23 @@
         </is>
       </c>
       <c r="AA32" s="0">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="AV32" s="0" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>120</t>
         </is>
       </c>
     </row>
     <row r="33" spans="1:48">
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>DIAMOND AND CLASSIC </t>
+          <t>COUS COUS LACE</t>
         </is>
       </c>
       <c r="G33" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O33" s="0" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="R33" s="0" t="inlineStr">
         <is>
-          <t>10000.00</t>
+          <t>45234.375</t>
         </is>
       </c>
       <c r="S33" s="0" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="T33" s="0" t="inlineStr">
         <is>
-          <t>12000.00</t>
+          <t>55000.00</t>
         </is>
       </c>
       <c r="Z33" s="0" t="inlineStr">
@@ -1743,23 +1743,23 @@
         </is>
       </c>
       <c r="AA33" s="0">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="AV33" s="0" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="34" spans="1:48">
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t>DIAMOND PLUS</t>
+          <t>DIAMOND AND CLASSIC </t>
         </is>
       </c>
       <c r="G34" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O34" s="0" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="R34" s="0" t="inlineStr">
         <is>
-          <t>7000.00</t>
+          <t>10000.00</t>
         </is>
       </c>
       <c r="S34" s="0" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="T34" s="0" t="inlineStr">
         <is>
-          <t>9500.00</t>
+          <t>12000.00</t>
         </is>
       </c>
       <c r="Z34" s="0" t="inlineStr">
@@ -1788,23 +1788,23 @@
         </is>
       </c>
       <c r="AA34" s="0">
-        <v>134</v>
+        <v>23</v>
       </c>
       <c r="AV34" s="0" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>130</t>
         </is>
       </c>
     </row>
     <row r="35" spans="1:48">
       <c r="C35" s="0" t="inlineStr">
         <is>
-          <t>DISCO WAX</t>
+          <t>DIAMOND PLUS</t>
         </is>
       </c>
       <c r="G35" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O35" s="0" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="R35" s="0" t="inlineStr">
         <is>
-          <t>10017.9069767442</t>
+          <t>7000.00</t>
         </is>
       </c>
       <c r="S35" s="0" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="T35" s="0" t="inlineStr">
         <is>
-          <t>11000.00</t>
+          <t>9500.00</t>
         </is>
       </c>
       <c r="Z35" s="0" t="inlineStr">
@@ -1833,18 +1833,18 @@
         </is>
       </c>
       <c r="AA35" s="0">
-        <v>51</v>
+        <v>134</v>
       </c>
       <c r="AV35" s="0" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>174</t>
         </is>
       </c>
     </row>
     <row r="36" spans="1:48">
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>ELIZABETH EMBELLISHED</t>
+          <t>DISCO WAX</t>
         </is>
       </c>
       <c r="G36" s="0" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="R36" s="0" t="inlineStr">
         <is>
-          <t>35000.00</t>
+          <t>10017.9069767442</t>
         </is>
       </c>
       <c r="S36" s="0" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="T36" s="0" t="inlineStr">
         <is>
-          <t>40000.00</t>
+          <t>11000.00</t>
         </is>
       </c>
       <c r="Z36" s="0" t="inlineStr">
@@ -1878,18 +1878,18 @@
         </is>
       </c>
       <c r="AA36" s="0">
-        <v>141</v>
+        <v>36</v>
       </c>
       <c r="AV36" s="0" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>131</t>
         </is>
       </c>
     </row>
     <row r="37" spans="1:48">
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>EMBELLISHED MDT</t>
+          <t>ELIZABETH EMBELLISHED</t>
         </is>
       </c>
       <c r="G37" s="0" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="R37" s="0" t="inlineStr">
         <is>
-          <t>14904.913275101</t>
+          <t>35000.00</t>
         </is>
       </c>
       <c r="S37" s="0" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T37" s="0" t="inlineStr">
         <is>
-          <t>18000.00</t>
+          <t>40000.00</t>
         </is>
       </c>
       <c r="Z37" s="0" t="inlineStr">
@@ -1923,23 +1923,23 @@
         </is>
       </c>
       <c r="AA37" s="0">
-        <v>1349</v>
+        <v>129</v>
       </c>
       <c r="AV37" s="0" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="38" spans="1:48">
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>EMIRATEY YARD</t>
+          <t>EMBELLISHED MDT</t>
         </is>
       </c>
       <c r="G38" s="0" t="inlineStr">
         <is>
-          <t>YARD</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O38" s="0" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="R38" s="0" t="inlineStr">
         <is>
-          <t>4500.00</t>
+          <t>14904.913275101</t>
         </is>
       </c>
       <c r="S38" s="0" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="T38" s="0" t="inlineStr">
         <is>
-          <t>6500.00</t>
+          <t>18000.00</t>
         </is>
       </c>
       <c r="Z38" s="0" t="inlineStr">
@@ -1967,26 +1967,24 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA38" s="0" t="inlineStr">
-        <is>
-          <t>177.5</t>
-        </is>
+      <c r="AA38" s="0">
+        <v>1181</v>
       </c>
       <c r="AV38" s="0" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>117</t>
         </is>
       </c>
     </row>
     <row r="39" spans="1:48">
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>EXCLUSIVE SWISS LACE A</t>
+          <t>EMIRATEY YARD</t>
         </is>
       </c>
       <c r="G39" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>YARD</t>
         </is>
       </c>
       <c r="O39" s="0" t="inlineStr">
@@ -1996,7 +1994,7 @@
       </c>
       <c r="R39" s="0" t="inlineStr">
         <is>
-          <t>400000.00</t>
+          <t>4500.00</t>
         </is>
       </c>
       <c r="S39" s="0" t="inlineStr">
@@ -2006,7 +2004,7 @@
       </c>
       <c r="T39" s="0" t="inlineStr">
         <is>
-          <t>480000.00</t>
+          <t>6500.00</t>
         </is>
       </c>
       <c r="Z39" s="0" t="inlineStr">
@@ -2014,19 +2012,21 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA39" s="0">
-        <v>6</v>
+      <c r="AA39" s="0" t="inlineStr">
+        <is>
+          <t>177.5</t>
+        </is>
       </c>
       <c r="AV39" s="0" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>192</t>
         </is>
       </c>
     </row>
     <row r="40" spans="1:48">
       <c r="C40" s="0" t="inlineStr">
         <is>
-          <t>EXCLUSIVE SWISS LACE B</t>
+          <t>EXCLUSIVE SWISS LACE A</t>
         </is>
       </c>
       <c r="G40" s="0" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="R40" s="0" t="inlineStr">
         <is>
-          <t>380000.00</t>
+          <t>400000.00</t>
         </is>
       </c>
       <c r="S40" s="0" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="T40" s="0" t="inlineStr">
         <is>
-          <t>450000.00</t>
+          <t>480000.00</t>
         </is>
       </c>
       <c r="Z40" s="0" t="inlineStr">
@@ -2060,18 +2060,18 @@
         </is>
       </c>
       <c r="AA40" s="0">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="AV40" s="0" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="41" spans="1:48">
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t>EXCLUSIVE SWISS LACE C</t>
+          <t>EXCLUSIVE SWISS LACE B</t>
         </is>
       </c>
       <c r="G41" s="0" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="R41" s="0" t="inlineStr">
         <is>
-          <t>350000.00</t>
+          <t>380000.00</t>
         </is>
       </c>
       <c r="S41" s="0" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="T41" s="0" t="inlineStr">
         <is>
-          <t>420000.00</t>
+          <t>450000.00</t>
         </is>
       </c>
       <c r="Z41" s="0" t="inlineStr">
@@ -2105,18 +2105,18 @@
         </is>
       </c>
       <c r="AA41" s="0">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AV41" s="0" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="42" spans="1:48">
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t>EXCLUSIVE SWISS LACE D</t>
+          <t>EXCLUSIVE SWISS LACE C</t>
         </is>
       </c>
       <c r="G42" s="0" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="R42" s="0" t="inlineStr">
         <is>
-          <t>320000.00</t>
+          <t>350000.00</t>
         </is>
       </c>
       <c r="S42" s="0" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="T42" s="0" t="inlineStr">
         <is>
-          <t>400000.00</t>
+          <t>420000.00</t>
         </is>
       </c>
       <c r="Z42" s="0" t="inlineStr">
@@ -2150,23 +2150,23 @@
         </is>
       </c>
       <c r="AA42" s="0">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="AV42" s="0" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="43" spans="1:48">
       <c r="C43" s="0" t="inlineStr">
         <is>
-          <t>EXCLUSIVE SWISS LAFAYA B</t>
+          <t>EXCLUSIVE SWISS LACE D</t>
         </is>
       </c>
       <c r="G43" s="0" t="inlineStr">
         <is>
-          <t>LAFAYYA</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O43" s="0" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="R43" s="0" t="inlineStr">
         <is>
-          <t>180000.00</t>
+          <t>320000.00</t>
         </is>
       </c>
       <c r="S43" s="0" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="T43" s="0" t="inlineStr">
         <is>
-          <t>250000.00</t>
+          <t>400000.00</t>
         </is>
       </c>
       <c r="Z43" s="0" t="inlineStr">
@@ -2199,14 +2199,14 @@
       </c>
       <c r="AV43" s="0" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="44" spans="1:48">
       <c r="C44" s="0" t="inlineStr">
         <is>
-          <t>EXCLUSIVE SWISS LAFAYA C</t>
+          <t>EXCLUSIVE SWISS LAFAYA B</t>
         </is>
       </c>
       <c r="G44" s="0" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="R44" s="0" t="inlineStr">
         <is>
-          <t>120000.00</t>
+          <t>180000.00</t>
         </is>
       </c>
       <c r="S44" s="0" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="T44" s="0" t="inlineStr">
         <is>
-          <t>200000.00</t>
+          <t>250000.00</t>
         </is>
       </c>
       <c r="Z44" s="0" t="inlineStr">
@@ -2240,18 +2240,18 @@
         </is>
       </c>
       <c r="AA44" s="0">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AV44" s="0" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="45" spans="1:48">
       <c r="C45" s="0" t="inlineStr">
         <is>
-          <t>EXCLUSIVE SWISS LAFFAYA A</t>
+          <t>EXCLUSIVE SWISS LAFAYA C</t>
         </is>
       </c>
       <c r="G45" s="0" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="R45" s="0" t="inlineStr">
         <is>
-          <t>220000.00</t>
+          <t>120000.00</t>
         </is>
       </c>
       <c r="S45" s="0" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="T45" s="0" t="inlineStr">
         <is>
-          <t>280000.00</t>
+          <t>200000.00</t>
         </is>
       </c>
       <c r="Z45" s="0" t="inlineStr">
@@ -2285,23 +2285,23 @@
         </is>
       </c>
       <c r="AA45" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AV45" s="0" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="46" spans="1:48">
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t>EXCLUSIVE ULTRA SWISS LACE A</t>
+          <t>EXCLUSIVE SWISS LAFFAYA A</t>
         </is>
       </c>
       <c r="G46" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>LAFAYYA</t>
         </is>
       </c>
       <c r="O46" s="0" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="R46" s="0" t="inlineStr">
         <is>
-          <t>550000.00</t>
+          <t>220000.00</t>
         </is>
       </c>
       <c r="S46" s="0" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="T46" s="0" t="inlineStr">
         <is>
-          <t>700000.00</t>
+          <t>280000.00</t>
         </is>
       </c>
       <c r="Z46" s="0" t="inlineStr">
@@ -2330,38 +2330,18 @@
         </is>
       </c>
       <c r="AA46" s="0">
-        <v>2</v>
-      </c>
-      <c r="AD46" s="0" t="inlineStr">
-        <is>
-          <t>Repair Item</t>
-        </is>
-      </c>
-      <c r="AL46" s="0" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="AM46" s="0" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="AN46" s="0" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="AV46" s="0" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="47" spans="1:48">
       <c r="C47" s="0" t="inlineStr">
         <is>
-          <t>EXCLUSIVE ULTRA SWISS LACE B</t>
+          <t>EXCLUSIVE ULTRA SWISS LACE A</t>
         </is>
       </c>
       <c r="G47" s="0" t="inlineStr">
@@ -2376,7 +2356,7 @@
       </c>
       <c r="R47" s="0" t="inlineStr">
         <is>
-          <t>450000.00</t>
+          <t>550000.00</t>
         </is>
       </c>
       <c r="S47" s="0" t="inlineStr">
@@ -2386,7 +2366,7 @@
       </c>
       <c r="T47" s="0" t="inlineStr">
         <is>
-          <t>550000.00</t>
+          <t>700000.00</t>
         </is>
       </c>
       <c r="Z47" s="0" t="inlineStr">
@@ -2395,18 +2375,38 @@
         </is>
       </c>
       <c r="AA47" s="0">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AD47" s="0" t="inlineStr">
+        <is>
+          <t>Repair Item</t>
+        </is>
+      </c>
+      <c r="AL47" s="0" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AM47" s="0" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AN47" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
       </c>
       <c r="AV47" s="0" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="48" spans="1:48">
       <c r="C48" s="0" t="inlineStr">
         <is>
-          <t>EXCLUSIVE ULTRA SWISS LACE C</t>
+          <t>EXCLUSIVE ULTRA SWISS LACE B</t>
         </is>
       </c>
       <c r="G48" s="0" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="R48" s="0" t="inlineStr">
         <is>
-          <t>430000.00</t>
+          <t>450000.00</t>
         </is>
       </c>
       <c r="S48" s="0" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="T48" s="0" t="inlineStr">
         <is>
-          <t>520000.00</t>
+          <t>550000.00</t>
         </is>
       </c>
       <c r="Z48" s="0" t="inlineStr">
@@ -2440,23 +2440,23 @@
         </is>
       </c>
       <c r="AA48" s="0">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AV48" s="0" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="49" spans="1:48">
       <c r="C49" s="0" t="inlineStr">
         <is>
-          <t>EXECUTIVE YARD</t>
+          <t>EXCLUSIVE ULTRA SWISS LACE C</t>
         </is>
       </c>
       <c r="G49" s="0" t="inlineStr">
         <is>
-          <t>YARD</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O49" s="0" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="R49" s="0" t="inlineStr">
         <is>
-          <t>6000.00</t>
+          <t>430000.00</t>
         </is>
       </c>
       <c r="S49" s="0" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="T49" s="0" t="inlineStr">
         <is>
-          <t>7500.00</t>
+          <t>520000.00</t>
         </is>
       </c>
       <c r="Z49" s="0" t="inlineStr">
@@ -2485,28 +2485,23 @@
         </is>
       </c>
       <c r="AA49" s="0">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AV49" s="0" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="50" spans="1:48">
       <c r="C50" s="0" t="inlineStr">
         <is>
-          <t>Fantastic Holland</t>
+          <t>EXECUTIVE YARD</t>
         </is>
       </c>
       <c r="G50" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
-        </is>
-      </c>
-      <c r="H50" s="0" t="inlineStr">
-        <is>
-          <t>YAYA SANI</t>
+          <t>YARD</t>
         </is>
       </c>
       <c r="O50" s="0" t="inlineStr">
@@ -2516,7 +2511,7 @@
       </c>
       <c r="R50" s="0" t="inlineStr">
         <is>
-          <t>8015.3894490222</t>
+          <t>6000.00</t>
         </is>
       </c>
       <c r="S50" s="0" t="inlineStr">
@@ -2526,7 +2521,7 @@
       </c>
       <c r="T50" s="0" t="inlineStr">
         <is>
-          <t>8500.00</t>
+          <t>7500.00</t>
         </is>
       </c>
       <c r="Z50" s="0" t="inlineStr">
@@ -2535,23 +2530,28 @@
         </is>
       </c>
       <c r="AA50" s="0">
-        <v>324</v>
+        <v>3</v>
       </c>
       <c r="AV50" s="0" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>182</t>
         </is>
       </c>
     </row>
     <row r="51" spans="1:48">
       <c r="C51" s="0" t="inlineStr">
         <is>
-          <t>FILTEX ALINA</t>
+          <t>Fantastic Holland</t>
         </is>
       </c>
       <c r="G51" s="0" t="inlineStr">
         <is>
-          <t>YARD</t>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="H51" s="0" t="inlineStr">
+        <is>
+          <t>YAYA SANI</t>
         </is>
       </c>
       <c r="O51" s="0" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="R51" s="0" t="inlineStr">
         <is>
-          <t>160000.00</t>
+          <t>8004.9441216316</t>
         </is>
       </c>
       <c r="S51" s="0" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="T51" s="0" t="inlineStr">
         <is>
-          <t>200000.00</t>
+          <t>8500.00</t>
         </is>
       </c>
       <c r="Z51" s="0" t="inlineStr">
@@ -2579,26 +2579,24 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA51" s="0" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
+      <c r="AA51" s="0">
+        <v>403</v>
       </c>
       <c r="AV51" s="0" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>196</t>
         </is>
       </c>
     </row>
     <row r="52" spans="1:48">
       <c r="C52" s="0" t="inlineStr">
         <is>
-          <t>FILTEX VOILE STONE</t>
+          <t>FILTEX ALINA</t>
         </is>
       </c>
       <c r="G52" s="0" t="inlineStr">
         <is>
-          <t>VOILE</t>
+          <t>YARD</t>
         </is>
       </c>
       <c r="O52" s="0" t="inlineStr">
@@ -2608,7 +2606,7 @@
       </c>
       <c r="R52" s="0" t="inlineStr">
         <is>
-          <t>165000.00</t>
+          <t>160000.00</t>
         </is>
       </c>
       <c r="S52" s="0" t="inlineStr">
@@ -2618,7 +2616,7 @@
       </c>
       <c r="T52" s="0" t="inlineStr">
         <is>
-          <t>185000.00</t>
+          <t>200000.00</t>
         </is>
       </c>
       <c r="Z52" s="0" t="inlineStr">
@@ -2626,24 +2624,26 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA52" s="0">
-        <v>2</v>
+      <c r="AA52" s="0" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
       </c>
       <c r="AV52" s="0" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>167</t>
         </is>
       </c>
     </row>
     <row r="53" spans="1:48">
       <c r="C53" s="0" t="inlineStr">
         <is>
-          <t>FLITEX NIDO</t>
+          <t>FILTEX VOILE STONE</t>
         </is>
       </c>
       <c r="G53" s="0" t="inlineStr">
         <is>
-          <t>YARD</t>
+          <t>VOILE</t>
         </is>
       </c>
       <c r="O53" s="0" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="R53" s="0" t="inlineStr">
         <is>
-          <t>160000.00</t>
+          <t>165000.00</t>
         </is>
       </c>
       <c r="S53" s="0" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="T53" s="0" t="inlineStr">
         <is>
-          <t>220000.00</t>
+          <t>185000.00</t>
         </is>
       </c>
       <c r="Z53" s="0" t="inlineStr">
@@ -2671,26 +2671,24 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA53" s="0" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
+      <c r="AA53" s="0">
+        <v>2</v>
       </c>
       <c r="AV53" s="0" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>36</t>
         </is>
       </c>
     </row>
     <row r="54" spans="1:48">
       <c r="C54" s="0" t="inlineStr">
         <is>
-          <t>FLORA MATERIAL </t>
+          <t>FLITEX NIDO</t>
         </is>
       </c>
       <c r="G54" s="0" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>YARD</t>
         </is>
       </c>
       <c r="O54" s="0" t="inlineStr">
@@ -2700,7 +2698,7 @@
       </c>
       <c r="R54" s="0" t="inlineStr">
         <is>
-          <t>13500.00</t>
+          <t>160000.00</t>
         </is>
       </c>
       <c r="S54" s="0" t="inlineStr">
@@ -2710,7 +2708,7 @@
       </c>
       <c r="T54" s="0" t="inlineStr">
         <is>
-          <t>16000.00</t>
+          <t>220000.00</t>
         </is>
       </c>
       <c r="Z54" s="0" t="inlineStr">
@@ -2718,24 +2716,26 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA54" s="0">
-        <v>7</v>
+      <c r="AA54" s="0" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
       </c>
       <c r="AV54" s="0" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>166</t>
         </is>
       </c>
     </row>
     <row r="55" spans="1:48">
       <c r="C55" s="0" t="inlineStr">
         <is>
-          <t>FORMULAR AND LAVIK</t>
+          <t>FLORA MATERIAL </t>
         </is>
       </c>
       <c r="G55" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="O55" s="0" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="R55" s="0" t="inlineStr">
         <is>
-          <t>3500.00</t>
+          <t>13500.00</t>
         </is>
       </c>
       <c r="S55" s="0" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="T55" s="0" t="inlineStr">
         <is>
-          <t>4500.00</t>
+          <t>16000.00</t>
         </is>
       </c>
       <c r="Z55" s="0" t="inlineStr">
@@ -2764,23 +2764,23 @@
         </is>
       </c>
       <c r="AA55" s="0">
-        <v>177</v>
+        <v>5</v>
       </c>
       <c r="AV55" s="0" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>48</t>
         </is>
       </c>
     </row>
     <row r="56" spans="1:48">
       <c r="C56" s="0" t="inlineStr">
         <is>
-          <t>FULL STONE EMBELLISHED </t>
+          <t>FORMULAR AND LAVIK</t>
         </is>
       </c>
       <c r="G56" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O56" s="0" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="R56" s="0" t="inlineStr">
         <is>
-          <t>16000.00</t>
+          <t>3500.00</t>
         </is>
       </c>
       <c r="S56" s="0" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="T56" s="0" t="inlineStr">
         <is>
-          <t>20000.00</t>
+          <t>4500.00</t>
         </is>
       </c>
       <c r="Z56" s="0" t="inlineStr">
@@ -2809,23 +2809,23 @@
         </is>
       </c>
       <c r="AA56" s="0">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="AV56" s="0" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>180</t>
         </is>
       </c>
     </row>
     <row r="57" spans="1:48">
       <c r="C57" s="0" t="inlineStr">
         <is>
-          <t>G PARK AND LUXURY dot</t>
+          <t>FULL STONE EMBELLISHED </t>
         </is>
       </c>
       <c r="G57" s="0" t="inlineStr">
         <is>
-          <t>YARD</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O57" s="0" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="R57" s="0" t="inlineStr">
         <is>
-          <t>4000.00</t>
+          <t>16000.00</t>
         </is>
       </c>
       <c r="S57" s="0" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="T57" s="0" t="inlineStr">
         <is>
-          <t>5000.00</t>
+          <t>20000.00</t>
         </is>
       </c>
       <c r="Z57" s="0" t="inlineStr">
@@ -2854,23 +2854,23 @@
         </is>
       </c>
       <c r="AA57" s="0">
-        <v>49</v>
+        <v>149</v>
       </c>
       <c r="AV57" s="0" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>111</t>
         </is>
       </c>
     </row>
     <row r="58" spans="1:48">
       <c r="C58" s="0" t="inlineStr">
         <is>
-          <t>GETZNER EXCELLENCE</t>
+          <t>G PARK AND LUXURY dot</t>
         </is>
       </c>
       <c r="G58" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>YARD</t>
         </is>
       </c>
       <c r="O58" s="0" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="R58" s="0" t="inlineStr">
         <is>
-          <t>22000.00</t>
+          <t>4000.00</t>
         </is>
       </c>
       <c r="S58" s="0" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="T58" s="0" t="inlineStr">
         <is>
-          <t>25000.00</t>
+          <t>5000.00</t>
         </is>
       </c>
       <c r="Z58" s="0" t="inlineStr">
@@ -2899,18 +2899,18 @@
         </is>
       </c>
       <c r="AA58" s="0">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="AV58" s="0" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>184</t>
         </is>
       </c>
     </row>
     <row r="59" spans="1:48">
       <c r="C59" s="0" t="inlineStr">
         <is>
-          <t>GETZNER MAGNUM</t>
+          <t>GETZNER EXCELLENCE</t>
         </is>
       </c>
       <c r="G59" s="0" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="R59" s="0" t="inlineStr">
         <is>
-          <t>19444.4444444444</t>
+          <t>22000.00</t>
         </is>
       </c>
       <c r="S59" s="0" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="T59" s="0" t="inlineStr">
         <is>
-          <t>22000.00</t>
+          <t>25000.00</t>
         </is>
       </c>
       <c r="Z59" s="0" t="inlineStr">
@@ -2944,18 +2944,18 @@
         </is>
       </c>
       <c r="AA59" s="0">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="AV59" s="0" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>171</t>
         </is>
       </c>
     </row>
     <row r="60" spans="1:48">
       <c r="C60" s="0" t="inlineStr">
         <is>
-          <t>GETZNER PHANTOM</t>
+          <t>GETZNER MAGNUM</t>
         </is>
       </c>
       <c r="G60" s="0" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="R60" s="0" t="inlineStr">
         <is>
-          <t>25000.00</t>
+          <t>19444.4444444444</t>
         </is>
       </c>
       <c r="S60" s="0" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="T60" s="0" t="inlineStr">
         <is>
-          <t>29500.00</t>
+          <t>22000.00</t>
         </is>
       </c>
       <c r="Z60" s="0" t="inlineStr">
@@ -2989,23 +2989,23 @@
         </is>
       </c>
       <c r="AA60" s="0">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="AV60" s="0" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>172</t>
         </is>
       </c>
     </row>
     <row r="61" spans="1:48">
       <c r="C61" s="0" t="inlineStr">
         <is>
-          <t>GLITTER GLAM HOLLAND </t>
+          <t>GETZNER PHANTOM</t>
         </is>
       </c>
       <c r="G61" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O61" s="0" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="R61" s="0" t="inlineStr">
         <is>
-          <t>218159.3406593406</t>
+          <t>25000.00</t>
         </is>
       </c>
       <c r="S61" s="0" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="T61" s="0" t="inlineStr">
         <is>
-          <t>250000.00</t>
+          <t>29500.00</t>
         </is>
       </c>
       <c r="Z61" s="0" t="inlineStr">
@@ -3034,18 +3034,18 @@
         </is>
       </c>
       <c r="AA61" s="0">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AV61" s="0" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>170</t>
         </is>
       </c>
     </row>
     <row r="62" spans="1:48">
       <c r="C62" s="0" t="inlineStr">
         <is>
-          <t>GLITTER ROBA </t>
+          <t>GLITTER GLAM HOLLAND </t>
         </is>
       </c>
       <c r="G62" s="0" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="R62" s="0" t="inlineStr">
         <is>
-          <t>5009.948276053</t>
+          <t>218159.3406593406</t>
         </is>
       </c>
       <c r="S62" s="0" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="T62" s="0" t="inlineStr">
         <is>
-          <t>5800.00</t>
+          <t>250000.00</t>
         </is>
       </c>
       <c r="Z62" s="0" t="inlineStr">
@@ -3079,18 +3079,18 @@
         </is>
       </c>
       <c r="AA62" s="0">
-        <v>799</v>
+        <v>13</v>
       </c>
       <c r="AV62" s="0" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>66</t>
         </is>
       </c>
     </row>
     <row r="63" spans="1:48">
       <c r="C63" s="0" t="inlineStr">
         <is>
-          <t>GLORY WAX</t>
+          <t>GLITTER ROBA </t>
         </is>
       </c>
       <c r="G63" s="0" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="R63" s="0" t="inlineStr">
         <is>
-          <t>9000.00</t>
+          <t>5009.948276053</t>
         </is>
       </c>
       <c r="S63" s="0" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="T63" s="0" t="inlineStr">
         <is>
-          <t>10000.00</t>
+          <t>5800.00</t>
         </is>
       </c>
       <c r="Z63" s="0" t="inlineStr">
@@ -3124,18 +3124,18 @@
         </is>
       </c>
       <c r="AA63" s="0">
-        <v>62</v>
+        <v>786</v>
       </c>
       <c r="AV63" s="0" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>140</t>
         </is>
       </c>
     </row>
     <row r="64" spans="1:48">
       <c r="C64" s="0" t="inlineStr">
         <is>
-          <t>GRAND SUPER GLITTER </t>
+          <t>GLORY WAX</t>
         </is>
       </c>
       <c r="G64" s="0" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="R64" s="0" t="inlineStr">
         <is>
-          <t>302712.962962963</t>
+          <t>9000.00</t>
         </is>
       </c>
       <c r="S64" s="0" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="T64" s="0" t="inlineStr">
         <is>
-          <t>330000.00</t>
+          <t>10000.00</t>
         </is>
       </c>
       <c r="Z64" s="0" t="inlineStr">
@@ -3169,18 +3169,18 @@
         </is>
       </c>
       <c r="AA64" s="0">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AV64" s="0" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>136</t>
         </is>
       </c>
     </row>
     <row r="65" spans="1:48">
       <c r="C65" s="0" t="inlineStr">
         <is>
-          <t>GRANDEUR EMBELLISHED</t>
+          <t>GRAND SUPER GLITTER </t>
         </is>
       </c>
       <c r="G65" s="0" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="R65" s="0" t="inlineStr">
         <is>
-          <t>25000.00</t>
+          <t>302712.962962963</t>
         </is>
       </c>
       <c r="S65" s="0" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="T65" s="0" t="inlineStr">
         <is>
-          <t>30000.00</t>
+          <t>330000.00</t>
         </is>
       </c>
       <c r="Z65" s="0" t="inlineStr">
@@ -3214,18 +3214,18 @@
         </is>
       </c>
       <c r="AA65" s="0">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AV65" s="0" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>65</t>
         </is>
       </c>
     </row>
     <row r="66" spans="1:48">
       <c r="C66" s="0" t="inlineStr">
         <is>
-          <t>GRANDEUR PLAIN</t>
+          <t>GRANDEUR EMBELLISHED</t>
         </is>
       </c>
       <c r="G66" s="0" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="R66" s="0" t="inlineStr">
         <is>
-          <t>20000.00</t>
+          <t>25000.00</t>
         </is>
       </c>
       <c r="S66" s="0" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="T66" s="0" t="inlineStr">
         <is>
-          <t>25000.00</t>
+          <t>30000.00</t>
         </is>
       </c>
       <c r="Z66" s="0" t="inlineStr">
@@ -3259,18 +3259,18 @@
         </is>
       </c>
       <c r="AA66" s="0">
-        <v>268</v>
+        <v>20</v>
       </c>
       <c r="AV66" s="0" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>159</t>
         </is>
       </c>
     </row>
     <row r="67" spans="1:48">
       <c r="C67" s="0" t="inlineStr">
         <is>
-          <t>GRANDUER EMBELLISHED</t>
+          <t>GRANDEUR PLAIN</t>
         </is>
       </c>
       <c r="G67" s="0" t="inlineStr">
@@ -3285,42 +3285,42 @@
       </c>
       <c r="R67" s="0" t="inlineStr">
         <is>
+          <t>20000.00</t>
+        </is>
+      </c>
+      <c r="S67" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="T67" s="0" t="inlineStr">
+        <is>
           <t>25000.00</t>
         </is>
       </c>
-      <c r="S67" s="0" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="T67" s="0" t="inlineStr">
-        <is>
-          <t>30000.00</t>
-        </is>
-      </c>
       <c r="Z67" s="0" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
       <c r="AA67" s="0">
-        <v>220</v>
+        <v>267</v>
       </c>
       <c r="AV67" s="0" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>98</t>
         </is>
       </c>
     </row>
     <row r="68" spans="1:48">
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>HACKER AND GOLDEN WOOL</t>
+          <t>GRANDUER EMBELLISHED</t>
         </is>
       </c>
       <c r="G68" s="0" t="inlineStr">
         <is>
-          <t>YARD</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O68" s="0" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="R68" s="0" t="inlineStr">
         <is>
-          <t>6000.00</t>
+          <t>25000.00</t>
         </is>
       </c>
       <c r="S68" s="0" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="T68" s="0" t="inlineStr">
         <is>
-          <t>8000.00</t>
+          <t>30000.00</t>
         </is>
       </c>
       <c r="Z68" s="0" t="inlineStr">
@@ -3348,26 +3348,24 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA68" s="0" t="inlineStr">
-        <is>
-          <t>132.5</t>
-        </is>
+      <c r="AA68" s="0">
+        <v>140</v>
       </c>
       <c r="AV68" s="0" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>97</t>
         </is>
       </c>
     </row>
     <row r="69" spans="1:48">
       <c r="C69" s="0" t="inlineStr">
         <is>
-          <t>HIGHOLLAND</t>
+          <t>HACKER AND GOLDEN WOOL</t>
         </is>
       </c>
       <c r="G69" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>YARD</t>
         </is>
       </c>
       <c r="O69" s="0" t="inlineStr">
@@ -3377,7 +3375,7 @@
       </c>
       <c r="R69" s="0" t="inlineStr">
         <is>
-          <t>4200.00</t>
+          <t>6000.00</t>
         </is>
       </c>
       <c r="S69" s="0" t="inlineStr">
@@ -3387,7 +3385,7 @@
       </c>
       <c r="T69" s="0" t="inlineStr">
         <is>
-          <t>4500.00</t>
+          <t>8000.00</t>
         </is>
       </c>
       <c r="Z69" s="0" t="inlineStr">
@@ -3395,19 +3393,21 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA69" s="0">
-        <v>214</v>
+      <c r="AA69" s="0" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
       </c>
       <c r="AV69" s="0" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>186</t>
         </is>
       </c>
     </row>
     <row r="70" spans="1:48">
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t>HIGHTEST</t>
+          <t>HIGHOLLAND</t>
         </is>
       </c>
       <c r="G70" s="0" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="R70" s="0" t="inlineStr">
         <is>
-          <t>10000.00</t>
+          <t>4200.00</t>
         </is>
       </c>
       <c r="S70" s="0" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="T70" s="0" t="inlineStr">
         <is>
-          <t>11000.00</t>
+          <t>4500.00</t>
         </is>
       </c>
       <c r="Z70" s="0" t="inlineStr">
@@ -3441,23 +3441,23 @@
         </is>
       </c>
       <c r="AA70" s="0">
-        <v>754</v>
+        <v>214</v>
       </c>
       <c r="AV70" s="0" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>142</t>
         </is>
       </c>
     </row>
     <row r="71" spans="1:48">
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t>HILTON JACQUARD VOILE </t>
+          <t>HIGHTEST</t>
         </is>
       </c>
       <c r="G71" s="0" t="inlineStr">
         <is>
-          <t>VOILE</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O71" s="0" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="R71" s="0" t="inlineStr">
         <is>
-          <t>130000.00</t>
+          <t>10000.00</t>
         </is>
       </c>
       <c r="S71" s="0" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="T71" s="0" t="inlineStr">
         <is>
-          <t>180000.00</t>
+          <t>11000.00</t>
         </is>
       </c>
       <c r="Z71" s="0" t="inlineStr">
@@ -3486,23 +3486,23 @@
         </is>
       </c>
       <c r="AA71" s="0">
-        <v>16</v>
+        <v>759</v>
       </c>
       <c r="AV71" s="0" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>134</t>
         </is>
       </c>
     </row>
     <row r="72" spans="1:48">
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t>HILTON POLISH MENLACE</t>
+          <t>HILTON JACQUARD VOILE </t>
         </is>
       </c>
       <c r="G72" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>VOILE</t>
         </is>
       </c>
       <c r="O72" s="0" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="R72" s="0" t="inlineStr">
         <is>
-          <t>360000.00</t>
+          <t>130000.00</t>
         </is>
       </c>
       <c r="S72" s="0" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="T72" s="0" t="inlineStr">
         <is>
-          <t>480000.00</t>
+          <t>180000.00</t>
         </is>
       </c>
       <c r="Z72" s="0" t="inlineStr">
@@ -3531,23 +3531,23 @@
         </is>
       </c>
       <c r="AA72" s="0">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AV72" s="0" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>35</t>
         </is>
       </c>
     </row>
     <row r="73" spans="1:48">
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t>HILTON VOILE EMBELLISHED</t>
+          <t>HILTON POLISH MENLACE</t>
         </is>
       </c>
       <c r="G73" s="0" t="inlineStr">
         <is>
-          <t>VOILE</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O73" s="0" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="R73" s="0" t="inlineStr">
         <is>
-          <t>200000.00</t>
+          <t>360000.00</t>
         </is>
       </c>
       <c r="S73" s="0" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="T73" s="0" t="inlineStr">
         <is>
-          <t>250000.00</t>
+          <t>480000.00</t>
         </is>
       </c>
       <c r="Z73" s="0" t="inlineStr">
@@ -3576,23 +3576,23 @@
         </is>
       </c>
       <c r="AA73" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV73" s="0" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>163</t>
         </is>
       </c>
     </row>
     <row r="74" spans="1:48">
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t>HKG EXCLUSIVE YARD</t>
+          <t>HILTON VOILE EMBELLISHED</t>
         </is>
       </c>
       <c r="G74" s="0" t="inlineStr">
         <is>
-          <t>YARD</t>
+          <t>VOILE</t>
         </is>
       </c>
       <c r="O74" s="0" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="R74" s="0" t="inlineStr">
         <is>
-          <t>260000.00</t>
+          <t>200000.00</t>
         </is>
       </c>
       <c r="S74" s="0" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="T74" s="0" t="inlineStr">
         <is>
-          <t>370000.00</t>
+          <t>250000.00</t>
         </is>
       </c>
       <c r="Z74" s="0" t="inlineStr">
@@ -3621,28 +3621,23 @@
         </is>
       </c>
       <c r="AA74" s="0">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AV74" s="0" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>34</t>
         </is>
       </c>
     </row>
     <row r="75" spans="1:48">
       <c r="C75" s="0" t="inlineStr">
         <is>
-          <t>Holland Exclusive Embellished</t>
+          <t>HKG EXCLUSIVE YARD</t>
         </is>
       </c>
       <c r="G75" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
-        </is>
-      </c>
-      <c r="H75" s="0" t="inlineStr">
-        <is>
-          <t>FAHAD TAHIR</t>
+          <t>YARD</t>
         </is>
       </c>
       <c r="O75" s="0" t="inlineStr">
@@ -3652,7 +3647,7 @@
       </c>
       <c r="R75" s="0" t="inlineStr">
         <is>
-          <t>208000.00</t>
+          <t>260000.00</t>
         </is>
       </c>
       <c r="S75" s="0" t="inlineStr">
@@ -3662,7 +3657,7 @@
       </c>
       <c r="T75" s="0" t="inlineStr">
         <is>
-          <t>240000.00</t>
+          <t>370000.00</t>
         </is>
       </c>
       <c r="Z75" s="0" t="inlineStr">
@@ -3671,18 +3666,18 @@
         </is>
       </c>
       <c r="AA75" s="0">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AV75" s="0" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>165</t>
         </is>
       </c>
     </row>
     <row r="76" spans="1:48">
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t>HOLLAND MEDIUM</t>
+          <t>Holland Exclusive Embellished</t>
         </is>
       </c>
       <c r="G76" s="0" t="inlineStr">
@@ -3690,6 +3685,11 @@
           <t>ATAMPA</t>
         </is>
       </c>
+      <c r="H76" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
+        </is>
+      </c>
       <c r="O76" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="R76" s="0" t="inlineStr">
         <is>
-          <t>11000.00</t>
+          <t>208000.00</t>
         </is>
       </c>
       <c r="S76" s="0" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="T76" s="0" t="inlineStr">
         <is>
-          <t>12000.00</t>
+          <t>240000.00</t>
         </is>
       </c>
       <c r="Z76" s="0" t="inlineStr">
@@ -3716,18 +3716,18 @@
         </is>
       </c>
       <c r="AA76" s="0">
-        <v>259</v>
+        <v>8</v>
       </c>
       <c r="AV76" s="0" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>213</t>
         </is>
       </c>
     </row>
     <row r="77" spans="1:48">
       <c r="C77" s="0" t="inlineStr">
         <is>
-          <t>HOLLAND WAX COLLECTION</t>
+          <t>HOLLAND MEDIUM</t>
         </is>
       </c>
       <c r="G77" s="0" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="R77" s="0" t="inlineStr">
         <is>
-          <t>120000.00</t>
+          <t>11001.1933174224</t>
         </is>
       </c>
       <c r="S77" s="0" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="T77" s="0" t="inlineStr">
         <is>
-          <t>150000.00</t>
+          <t>12000.00</t>
         </is>
       </c>
       <c r="Z77" s="0" t="inlineStr">
@@ -3761,18 +3761,18 @@
         </is>
       </c>
       <c r="AA77" s="0">
-        <v>9</v>
+        <v>332</v>
       </c>
       <c r="AV77" s="0" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>126</t>
         </is>
       </c>
     </row>
     <row r="78" spans="1:48">
       <c r="C78" s="0" t="inlineStr">
         <is>
-          <t>Holland Wax Embellished </t>
+          <t>HOLLAND WAX COLLECTION</t>
         </is>
       </c>
       <c r="G78" s="0" t="inlineStr">
@@ -3780,11 +3780,6 @@
           <t>ATAMPA</t>
         </is>
       </c>
-      <c r="H78" s="0" t="inlineStr">
-        <is>
-          <t>FAHAD TAHIR</t>
-        </is>
-      </c>
       <c r="O78" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -3792,7 +3787,7 @@
       </c>
       <c r="R78" s="0" t="inlineStr">
         <is>
-          <t>130000.00</t>
+          <t>120000.00</t>
         </is>
       </c>
       <c r="S78" s="0" t="inlineStr">
@@ -3802,7 +3797,7 @@
       </c>
       <c r="T78" s="0" t="inlineStr">
         <is>
-          <t>180000.00</t>
+          <t>150000.00</t>
         </is>
       </c>
       <c r="Z78" s="0" t="inlineStr">
@@ -3811,18 +3806,18 @@
         </is>
       </c>
       <c r="AA78" s="0">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV78" s="0" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="79" spans="1:48">
       <c r="C79" s="0" t="inlineStr">
         <is>
-          <t>HOLLANDAD</t>
+          <t>Holland Wax Embellished </t>
         </is>
       </c>
       <c r="G79" s="0" t="inlineStr">
@@ -3830,6 +3825,11 @@
           <t>ATAMPA</t>
         </is>
       </c>
+      <c r="H79" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
+        </is>
+      </c>
       <c r="O79" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -3837,7 +3837,7 @@
       </c>
       <c r="R79" s="0" t="inlineStr">
         <is>
-          <t>7917.8890470591</t>
+          <t>130000.00</t>
         </is>
       </c>
       <c r="S79" s="0" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="T79" s="0" t="inlineStr">
         <is>
-          <t>8500.00</t>
+          <t>180000.00</t>
         </is>
       </c>
       <c r="Z79" s="0" t="inlineStr">
@@ -3856,18 +3856,18 @@
         </is>
       </c>
       <c r="AA79" s="0">
-        <v>376</v>
+        <v>0</v>
       </c>
       <c r="AV79" s="0" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>208</t>
         </is>
       </c>
     </row>
     <row r="80" spans="1:48">
       <c r="C80" s="0" t="inlineStr">
         <is>
-          <t>HOLLANTEX </t>
+          <t>HOLLANDAD</t>
         </is>
       </c>
       <c r="G80" s="0" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="R80" s="0" t="inlineStr">
         <is>
-          <t>11002.1645021645</t>
+          <t>7917.8890470591</t>
         </is>
       </c>
       <c r="S80" s="0" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="T80" s="0" t="inlineStr">
         <is>
-          <t>12000.00</t>
+          <t>8500.00</t>
         </is>
       </c>
       <c r="Z80" s="0" t="inlineStr">
@@ -3901,18 +3901,18 @@
         </is>
       </c>
       <c r="AA80" s="0">
-        <v>36</v>
+        <v>299</v>
       </c>
       <c r="AV80" s="0" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>138</t>
         </is>
       </c>
     </row>
     <row r="81" spans="1:48">
       <c r="C81" s="0" t="inlineStr">
         <is>
-          <t>HOLLANTEX COTED'VIORE</t>
+          <t>HOLLANTEX </t>
         </is>
       </c>
       <c r="G81" s="0" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="R81" s="0" t="inlineStr">
         <is>
-          <t>11000.00</t>
+          <t>11000.537056928</t>
         </is>
       </c>
       <c r="S81" s="0" t="inlineStr">
@@ -3946,18 +3946,18 @@
         </is>
       </c>
       <c r="AA81" s="0">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AV81" s="0" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>125</t>
         </is>
       </c>
     </row>
     <row r="82" spans="1:48">
       <c r="C82" s="0" t="inlineStr">
         <is>
-          <t>HOLLANTEX EMBELLISHED</t>
+          <t>HOLLANTEX COTED'VIORE</t>
         </is>
       </c>
       <c r="G82" s="0" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="R82" s="0" t="inlineStr">
         <is>
-          <t>16028.898306636</t>
+          <t>11000.00</t>
         </is>
       </c>
       <c r="S82" s="0" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="T82" s="0" t="inlineStr">
         <is>
-          <t>18000.00</t>
+          <t>12000.00</t>
         </is>
       </c>
       <c r="Z82" s="0" t="inlineStr">
@@ -3991,18 +3991,18 @@
         </is>
       </c>
       <c r="AA82" s="0">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="AV82" s="0" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>124</t>
         </is>
       </c>
     </row>
     <row r="83" spans="1:48">
       <c r="C83" s="0" t="inlineStr">
         <is>
-          <t>HOLLANTEX GOLD STONE</t>
+          <t>HOLLANTEX EMBELLISHED</t>
         </is>
       </c>
       <c r="G83" s="0" t="inlineStr">
@@ -4017,37 +4017,37 @@
       </c>
       <c r="R83" s="0" t="inlineStr">
         <is>
+          <t>16028.898306636</t>
+        </is>
+      </c>
+      <c r="S83" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="T83" s="0" t="inlineStr">
+        <is>
           <t>18000.00</t>
         </is>
       </c>
-      <c r="S83" s="0" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="T83" s="0" t="inlineStr">
-        <is>
-          <t>20000.00</t>
-        </is>
-      </c>
       <c r="Z83" s="0" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
       <c r="AA83" s="0">
-        <v>89</v>
+        <v>167</v>
       </c>
       <c r="AV83" s="0" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>114</t>
         </is>
       </c>
     </row>
     <row r="84" spans="1:48">
       <c r="C84" s="0" t="inlineStr">
         <is>
-          <t>Hollantex Mix pattern</t>
+          <t>HOLLANTEX GOLD STONE</t>
         </is>
       </c>
       <c r="G84" s="0" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="R84" s="0" t="inlineStr">
         <is>
-          <t>11268.5314685315</t>
+          <t>18000.00</t>
         </is>
       </c>
       <c r="S84" s="0" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="T84" s="0" t="inlineStr">
         <is>
-          <t>12000.00</t>
+          <t>20000.00</t>
         </is>
       </c>
       <c r="Z84" s="0" t="inlineStr">
@@ -4081,18 +4081,18 @@
         </is>
       </c>
       <c r="AA84" s="0">
-        <v>12</v>
+        <v>79</v>
       </c>
       <c r="AV84" s="0" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>107</t>
         </is>
       </c>
     </row>
     <row r="85" spans="1:48">
       <c r="C85" s="0" t="inlineStr">
         <is>
-          <t>HOLLANTREE</t>
+          <t>Hollantex Mix pattern</t>
         </is>
       </c>
       <c r="G85" s="0" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="R85" s="0" t="inlineStr">
         <is>
-          <t>10000.00</t>
+          <t>11770.2702702703</t>
         </is>
       </c>
       <c r="S85" s="0" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="T85" s="0" t="inlineStr">
         <is>
-          <t>11000.00</t>
+          <t>12500.00</t>
         </is>
       </c>
       <c r="Z85" s="0" t="inlineStr">
@@ -4126,23 +4126,23 @@
         </is>
       </c>
       <c r="AA85" s="0">
-        <v>262</v>
+        <v>48</v>
       </c>
       <c r="AV85" s="0" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>201</t>
         </is>
       </c>
     </row>
     <row r="86" spans="1:48">
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t>HYPER FILTEX</t>
+          <t>HOLLANTREE</t>
         </is>
       </c>
       <c r="G86" s="0" t="inlineStr">
         <is>
-          <t>YARD</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O86" s="0" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="R86" s="0" t="inlineStr">
         <is>
-          <t>5000.00</t>
+          <t>10000.00</t>
         </is>
       </c>
       <c r="S86" s="0" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="T86" s="0" t="inlineStr">
         <is>
-          <t>7500.00</t>
+          <t>11000.00</t>
         </is>
       </c>
       <c r="Z86" s="0" t="inlineStr">
@@ -4171,23 +4171,23 @@
         </is>
       </c>
       <c r="AA86" s="0">
-        <v>80</v>
+        <v>260</v>
       </c>
       <c r="AV86" s="0" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>132</t>
         </is>
       </c>
     </row>
     <row r="87" spans="1:48">
       <c r="C87" s="0" t="inlineStr">
         <is>
-          <t>IMPERIAL GRAND SATIN</t>
+          <t>HYPER FILTEX</t>
         </is>
       </c>
       <c r="G87" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>YARD</t>
         </is>
       </c>
       <c r="O87" s="0" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="R87" s="0" t="inlineStr">
         <is>
-          <t>25000.00</t>
+          <t>5000.00</t>
         </is>
       </c>
       <c r="S87" s="0" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="T87" s="0" t="inlineStr">
         <is>
-          <t>30000.00</t>
+          <t>7500.00</t>
         </is>
       </c>
       <c r="Z87" s="0" t="inlineStr">
@@ -4216,28 +4216,23 @@
         </is>
       </c>
       <c r="AA87" s="0">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AV87" s="0" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>183</t>
         </is>
       </c>
     </row>
     <row r="88" spans="1:48">
       <c r="C88" s="0" t="inlineStr">
         <is>
-          <t>Indonesian Creepe</t>
+          <t>IMPERIAL GRAND SATIN</t>
         </is>
       </c>
       <c r="G88" s="0" t="inlineStr">
         <is>
-          <t>LAFAYYA</t>
-        </is>
-      </c>
-      <c r="H88" s="0" t="inlineStr">
-        <is>
-          <t>FAHAD TAHIR</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O88" s="0" t="inlineStr">
@@ -4247,7 +4242,7 @@
       </c>
       <c r="R88" s="0" t="inlineStr">
         <is>
-          <t>11500.00</t>
+          <t>25000.00</t>
         </is>
       </c>
       <c r="S88" s="0" t="inlineStr">
@@ -4257,7 +4252,7 @@
       </c>
       <c r="T88" s="0" t="inlineStr">
         <is>
-          <t>14000.00</t>
+          <t>30000.00</t>
         </is>
       </c>
       <c r="Z88" s="0" t="inlineStr">
@@ -4266,23 +4261,28 @@
         </is>
       </c>
       <c r="AA88" s="0">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="AV88" s="0" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="89" spans="1:48">
       <c r="C89" s="0" t="inlineStr">
         <is>
-          <t>JAVA HOLLAND GOLD</t>
+          <t>Indonesian Creepe</t>
         </is>
       </c>
       <c r="G89" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>LAFAYYA</t>
+        </is>
+      </c>
+      <c r="H89" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
         </is>
       </c>
       <c r="O89" s="0" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="R89" s="0" t="inlineStr">
         <is>
-          <t>17000.00</t>
+          <t>11500.00</t>
         </is>
       </c>
       <c r="S89" s="0" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="T89" s="0" t="inlineStr">
         <is>
-          <t>20000.00</t>
+          <t>14000.00</t>
         </is>
       </c>
       <c r="Z89" s="0" t="inlineStr">
@@ -4311,18 +4311,18 @@
         </is>
       </c>
       <c r="AA89" s="0">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AV89" s="0" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>210</t>
         </is>
       </c>
     </row>
     <row r="90" spans="1:48">
       <c r="C90" s="0" t="inlineStr">
         <is>
-          <t>JIDDAM METTALIC</t>
+          <t>JAVA HOLLAND GOLD</t>
         </is>
       </c>
       <c r="G90" s="0" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="R90" s="0" t="inlineStr">
         <is>
-          <t>25000.00</t>
+          <t>17000.00</t>
         </is>
       </c>
       <c r="S90" s="0" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="T90" s="0" t="inlineStr">
         <is>
-          <t>26000.00</t>
+          <t>20000.00</t>
         </is>
       </c>
       <c r="Z90" s="0" t="inlineStr">
@@ -4356,23 +4356,23 @@
         </is>
       </c>
       <c r="AA90" s="0">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AV90" s="0" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>109</t>
         </is>
       </c>
     </row>
     <row r="91" spans="1:48">
       <c r="C91" s="0" t="inlineStr">
         <is>
-          <t>JOSEF OTTEN BARCODE</t>
+          <t>JIDDAM METTALIC</t>
         </is>
       </c>
       <c r="G91" s="0" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O91" s="0" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="R91" s="0" t="inlineStr">
         <is>
-          <t>165000.00</t>
+          <t>25000.00</t>
         </is>
       </c>
       <c r="S91" s="0" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="T91" s="0" t="inlineStr">
         <is>
-          <t>200000.00</t>
+          <t>26000.00</t>
         </is>
       </c>
       <c r="Z91" s="0" t="inlineStr">
@@ -4401,23 +4401,23 @@
         </is>
       </c>
       <c r="AA91" s="0">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="AV91" s="0" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>101</t>
         </is>
       </c>
     </row>
     <row r="92" spans="1:48">
       <c r="C92" s="0" t="inlineStr">
         <is>
-          <t>JOSEF OTTEN PLAIN 4YRDS</t>
+          <t>JOSEF OTTEN BARCODE</t>
         </is>
       </c>
       <c r="G92" s="0" t="inlineStr">
         <is>
-          <t>VOILE</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="O92" s="0" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="R92" s="0" t="inlineStr">
         <is>
-          <t>80000.00</t>
+          <t>165000.00</t>
         </is>
       </c>
       <c r="S92" s="0" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="T92" s="0" t="inlineStr">
         <is>
-          <t>100000.00</t>
+          <t>200000.00</t>
         </is>
       </c>
       <c r="Z92" s="0" t="inlineStr">
@@ -4446,18 +4446,18 @@
         </is>
       </c>
       <c r="AA92" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV92" s="0" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>51</t>
         </is>
       </c>
     </row>
     <row r="93" spans="1:48">
       <c r="C93" s="0" t="inlineStr">
         <is>
-          <t>JOSEF OTTEN PLAIN 5YRDS</t>
+          <t>JOSEF OTTEN PLAIN 4YRDS</t>
         </is>
       </c>
       <c r="G93" s="0" t="inlineStr">
@@ -4472,37 +4472,37 @@
       </c>
       <c r="R93" s="0" t="inlineStr">
         <is>
+          <t>80000.00</t>
+        </is>
+      </c>
+      <c r="S93" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="T93" s="0" t="inlineStr">
+        <is>
           <t>100000.00</t>
         </is>
       </c>
-      <c r="S93" s="0" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="T93" s="0" t="inlineStr">
-        <is>
-          <t>125000.00</t>
-        </is>
-      </c>
       <c r="Z93" s="0" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
       <c r="AA93" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV93" s="0" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
     </row>
     <row r="94" spans="1:48">
       <c r="C94" s="0" t="inlineStr">
         <is>
-          <t>JOSEF OTTEN VOILE</t>
+          <t>JOSEF OTTEN PLAIN 5YRDS</t>
         </is>
       </c>
       <c r="G94" s="0" t="inlineStr">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="R94" s="0" t="inlineStr">
         <is>
-          <t>175000.00</t>
+          <t>100000.00</t>
         </is>
       </c>
       <c r="S94" s="0" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="T94" s="0" t="inlineStr">
         <is>
-          <t>200000.00</t>
+          <t>125000.00</t>
         </is>
       </c>
       <c r="Z94" s="0" t="inlineStr">
@@ -4536,18 +4536,18 @@
         </is>
       </c>
       <c r="AA94" s="0">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="AV94" s="0" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="95" spans="1:48">
       <c r="C95" s="0" t="inlineStr">
         <is>
-          <t>JOSEF OTTEN VOILE 2.5YRDS</t>
+          <t>JOSEF OTTEN VOILE</t>
         </is>
       </c>
       <c r="G95" s="0" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="R95" s="0" t="inlineStr">
         <is>
-          <t>75000.00</t>
+          <t>175000.00</t>
         </is>
       </c>
       <c r="S95" s="0" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="T95" s="0" t="inlineStr">
         <is>
-          <t>100000.00</t>
+          <t>200000.00</t>
         </is>
       </c>
       <c r="Z95" s="0" t="inlineStr">
@@ -4581,18 +4581,18 @@
         </is>
       </c>
       <c r="AA95" s="0">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="AV95" s="0" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>37</t>
         </is>
       </c>
     </row>
     <row r="96" spans="1:48">
       <c r="C96" s="0" t="inlineStr">
         <is>
-          <t>JOSEF OTTEN VOILE 2YRDS</t>
+          <t>JOSEF OTTEN VOILE 2.5YRDS</t>
         </is>
       </c>
       <c r="G96" s="0" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="R96" s="0" t="inlineStr">
         <is>
-          <t>60000.00</t>
+          <t>75000.00</t>
         </is>
       </c>
       <c r="S96" s="0" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="T96" s="0" t="inlineStr">
         <is>
-          <t>80000.00</t>
+          <t>100000.00</t>
         </is>
       </c>
       <c r="Z96" s="0" t="inlineStr">
@@ -4626,18 +4626,18 @@
         </is>
       </c>
       <c r="AA96" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV96" s="0" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
     </row>
     <row r="97" spans="1:48">
       <c r="C97" s="0" t="inlineStr">
         <is>
-          <t>JOSEF OTTEN VOILE 3YRDS</t>
+          <t>JOSEF OTTEN VOILE 2YRDS</t>
         </is>
       </c>
       <c r="G97" s="0" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="R97" s="0" t="inlineStr">
         <is>
-          <t>90000.00</t>
+          <t>60000.00</t>
         </is>
       </c>
       <c r="S97" s="0" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="T97" s="0" t="inlineStr">
         <is>
-          <t>120000.00</t>
+          <t>80000.00</t>
         </is>
       </c>
       <c r="Z97" s="0" t="inlineStr">
@@ -4675,14 +4675,14 @@
       </c>
       <c r="AV97" s="0" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
     </row>
     <row r="98" spans="1:48">
       <c r="C98" s="0" t="inlineStr">
         <is>
-          <t>JOSEF OTTEN VOILE 4YRDS</t>
+          <t>JOSEF OTTEN VOILE 3YRDS</t>
         </is>
       </c>
       <c r="G98" s="0" t="inlineStr">
@@ -4697,42 +4697,42 @@
       </c>
       <c r="R98" s="0" t="inlineStr">
         <is>
+          <t>90000.00</t>
+        </is>
+      </c>
+      <c r="S98" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="T98" s="0" t="inlineStr">
+        <is>
           <t>120000.00</t>
         </is>
       </c>
-      <c r="S98" s="0" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="T98" s="0" t="inlineStr">
-        <is>
-          <t>160000.00</t>
-        </is>
-      </c>
       <c r="Z98" s="0" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
       <c r="AA98" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV98" s="0" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
     </row>
     <row r="99" spans="1:48">
       <c r="C99" s="0" t="inlineStr">
         <is>
-          <t>JULIUS COMFORT EMBELLISHED </t>
+          <t>JOSEF OTTEN VOILE 4YRDS</t>
         </is>
       </c>
       <c r="G99" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>VOILE</t>
         </is>
       </c>
       <c r="O99" s="0" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="R99" s="0" t="inlineStr">
         <is>
-          <t>85000.00</t>
+          <t>120000.00</t>
         </is>
       </c>
       <c r="S99" s="0" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="T99" s="0" t="inlineStr">
         <is>
-          <t>95000.00</t>
+          <t>160000.00</t>
         </is>
       </c>
       <c r="Z99" s="0" t="inlineStr">
@@ -4761,18 +4761,18 @@
         </is>
       </c>
       <c r="AA99" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV99" s="0" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="100" spans="1:48">
       <c r="C100" s="0" t="inlineStr">
         <is>
-          <t>JULIUS COMFORT PLAIN WAX</t>
+          <t>JULIUS COMFORT EMBELLISHED </t>
         </is>
       </c>
       <c r="G100" s="0" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="R100" s="0" t="inlineStr">
         <is>
-          <t>75000.00</t>
+          <t>85000.00</t>
         </is>
       </c>
       <c r="S100" s="0" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="T100" s="0" t="inlineStr">
         <is>
-          <t>82000.00</t>
+          <t>95000.00</t>
         </is>
       </c>
       <c r="Z100" s="0" t="inlineStr">
@@ -4806,18 +4806,18 @@
         </is>
       </c>
       <c r="AA100" s="0">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AV100" s="0" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>79</t>
         </is>
       </c>
     </row>
     <row r="101" spans="1:48">
       <c r="C101" s="0" t="inlineStr">
         <is>
-          <t>JULIUS CRYSTAL SHINE</t>
+          <t>JULIUS COMFORT PLAIN WAX</t>
         </is>
       </c>
       <c r="G101" s="0" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="R101" s="0" t="inlineStr">
         <is>
-          <t>86000.00</t>
+          <t>75000.00</t>
         </is>
       </c>
       <c r="S101" s="0" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="T101" s="0" t="inlineStr">
         <is>
-          <t>100000.00</t>
+          <t>82000.00</t>
         </is>
       </c>
       <c r="Z101" s="0" t="inlineStr">
@@ -4851,18 +4851,18 @@
         </is>
       </c>
       <c r="AA101" s="0">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="AV101" s="0" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="102" spans="1:48">
       <c r="C102" s="0" t="inlineStr">
         <is>
-          <t>JULIUS EMBELLISHED </t>
+          <t>JULIUS CRYSTAL SHINE</t>
         </is>
       </c>
       <c r="G102" s="0" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="R102" s="0" t="inlineStr">
         <is>
-          <t>75041.4291449217</t>
+          <t>86000.00</t>
         </is>
       </c>
       <c r="S102" s="0" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="T102" s="0" t="inlineStr">
         <is>
-          <t>85000.00</t>
+          <t>100000.00</t>
         </is>
       </c>
       <c r="Z102" s="0" t="inlineStr">
@@ -4896,18 +4896,18 @@
         </is>
       </c>
       <c r="AA102" s="0">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AV102" s="0" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>78</t>
         </is>
       </c>
     </row>
     <row r="103" spans="1:48">
       <c r="C103" s="0" t="inlineStr">
         <is>
-          <t>JULIUS EMBROIDERY </t>
+          <t>JULIUS EMBELLISHED </t>
         </is>
       </c>
       <c r="G103" s="0" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="R103" s="0" t="inlineStr">
         <is>
-          <t>330000.00</t>
+          <t>75041.4291449217</t>
         </is>
       </c>
       <c r="S103" s="0" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="T103" s="0" t="inlineStr">
         <is>
-          <t>400000.00</t>
+          <t>85000.00</t>
         </is>
       </c>
       <c r="Z103" s="0" t="inlineStr">
@@ -4945,14 +4945,14 @@
       </c>
       <c r="AV103" s="0" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>81</t>
         </is>
       </c>
     </row>
     <row r="104" spans="1:48">
       <c r="C104" s="0" t="inlineStr">
         <is>
-          <t>JULIUS EMBROIDERY MIX AND MATCH</t>
+          <t>JULIUS EMBROIDERY </t>
         </is>
       </c>
       <c r="G104" s="0" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="R104" s="0" t="inlineStr">
         <is>
-          <t>210000.00</t>
+          <t>330000.00</t>
         </is>
       </c>
       <c r="S104" s="0" t="inlineStr">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="T104" s="0" t="inlineStr">
         <is>
-          <t>250000.00</t>
+          <t>400000.00</t>
         </is>
       </c>
       <c r="Z104" s="0" t="inlineStr">
@@ -4986,18 +4986,18 @@
         </is>
       </c>
       <c r="AA104" s="0">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="AV104" s="0" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
     </row>
     <row r="105" spans="1:48">
       <c r="C105" s="0" t="inlineStr">
         <is>
-          <t>JULIUS HOLLAND PLAIN</t>
+          <t>JULIUS EMBROIDERY MIX AND MATCH</t>
         </is>
       </c>
       <c r="G105" s="0" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="R105" s="0" t="inlineStr">
         <is>
-          <t>58000.00</t>
+          <t>210000.00</t>
         </is>
       </c>
       <c r="S105" s="0" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="T105" s="0" t="inlineStr">
         <is>
-          <t>62000.00</t>
+          <t>250000.00</t>
         </is>
       </c>
       <c r="Z105" s="0" t="inlineStr">
@@ -5031,28 +5031,23 @@
         </is>
       </c>
       <c r="AA105" s="0">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV105" s="0" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>64</t>
         </is>
       </c>
     </row>
     <row r="106" spans="1:48">
       <c r="C106" s="0" t="inlineStr">
         <is>
-          <t>Kohinnoor VOILE EMBROIDERY </t>
+          <t>JULIUS HOLLAND PLAIN</t>
         </is>
       </c>
       <c r="G106" s="0" t="inlineStr">
         <is>
-          <t>VOILE</t>
-        </is>
-      </c>
-      <c r="H106" s="0" t="inlineStr">
-        <is>
-          <t>FAHAD TAHIR</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O106" s="0" t="inlineStr">
@@ -5062,7 +5057,7 @@
       </c>
       <c r="R106" s="0" t="inlineStr">
         <is>
-          <t>23000.00</t>
+          <t>58000.00</t>
         </is>
       </c>
       <c r="S106" s="0" t="inlineStr">
@@ -5072,7 +5067,7 @@
       </c>
       <c r="T106" s="0" t="inlineStr">
         <is>
-          <t>30000.00</t>
+          <t>62000.00</t>
         </is>
       </c>
       <c r="Z106" s="0" t="inlineStr">
@@ -5081,23 +5076,28 @@
         </is>
       </c>
       <c r="AA106" s="0">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AV106" s="0" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>160</t>
         </is>
       </c>
     </row>
     <row r="107" spans="1:48">
       <c r="C107" s="0" t="inlineStr">
         <is>
-          <t>LAGOS LACE A</t>
+          <t>Kohinnoor VOILE EMBROIDERY </t>
         </is>
       </c>
       <c r="G107" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>VOILE</t>
+        </is>
+      </c>
+      <c r="H107" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
         </is>
       </c>
       <c r="O107" s="0" t="inlineStr">
@@ -5107,37 +5107,37 @@
       </c>
       <c r="R107" s="0" t="inlineStr">
         <is>
+          <t>23000.00</t>
+        </is>
+      </c>
+      <c r="S107" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="T107" s="0" t="inlineStr">
+        <is>
           <t>30000.00</t>
         </is>
       </c>
-      <c r="S107" s="0" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="T107" s="0" t="inlineStr">
-        <is>
-          <t>35000.00</t>
-        </is>
-      </c>
       <c r="Z107" s="0" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
       <c r="AA107" s="0">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV107" s="0" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>209</t>
         </is>
       </c>
     </row>
     <row r="108" spans="1:48">
       <c r="C108" s="0" t="inlineStr">
         <is>
-          <t>LAGOS LACE B</t>
+          <t>LAGOS LACE A</t>
         </is>
       </c>
       <c r="G108" s="0" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="R108" s="0" t="inlineStr">
         <is>
-          <t>26000.00</t>
+          <t>30000.00</t>
         </is>
       </c>
       <c r="S108" s="0" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="T108" s="0" t="inlineStr">
         <is>
-          <t>30000.00</t>
+          <t>35000.00</t>
         </is>
       </c>
       <c r="Z108" s="0" t="inlineStr">
@@ -5171,18 +5171,18 @@
         </is>
       </c>
       <c r="AA108" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV108" s="0" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>147</t>
         </is>
       </c>
     </row>
     <row r="109" spans="1:48">
       <c r="C109" s="0" t="inlineStr">
         <is>
-          <t>LAGOS LACE C</t>
+          <t>LAGOS LACE B</t>
         </is>
       </c>
       <c r="G109" s="0" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="R109" s="0" t="inlineStr">
         <is>
-          <t>22037.6659856997</t>
+          <t>26000.00</t>
         </is>
       </c>
       <c r="S109" s="0" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="T109" s="0" t="inlineStr">
         <is>
-          <t>25000.00</t>
+          <t>30000.00</t>
         </is>
       </c>
       <c r="Z109" s="0" t="inlineStr">
@@ -5216,18 +5216,18 @@
         </is>
       </c>
       <c r="AA109" s="0">
-        <v>84</v>
+        <v>4</v>
       </c>
       <c r="AV109" s="0" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>148</t>
         </is>
       </c>
     </row>
     <row r="110" spans="1:48">
       <c r="C110" s="0" t="inlineStr">
         <is>
-          <t>LAGOS LACE D</t>
+          <t>LAGOS LACE C</t>
         </is>
       </c>
       <c r="G110" s="0" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="R110" s="0" t="inlineStr">
         <is>
-          <t>19573.0487804878</t>
+          <t>22027.3934441452</t>
         </is>
       </c>
       <c r="S110" s="0" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="T110" s="0" t="inlineStr">
         <is>
-          <t>23000.00</t>
+          <t>25000.00</t>
         </is>
       </c>
       <c r="Z110" s="0" t="inlineStr">
@@ -5261,18 +5261,18 @@
         </is>
       </c>
       <c r="AA110" s="0">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="AV110" s="0" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>150</t>
         </is>
       </c>
     </row>
     <row r="111" spans="1:48">
       <c r="C111" s="0" t="inlineStr">
         <is>
-          <t>LAGOS LACE E</t>
+          <t>LAGOS LACE D</t>
         </is>
       </c>
       <c r="G111" s="0" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="R111" s="0" t="inlineStr">
         <is>
-          <t>16064.5441917243</t>
+          <t>19665.8642629905</t>
         </is>
       </c>
       <c r="S111" s="0" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="T111" s="0" t="inlineStr">
         <is>
-          <t>20000.00</t>
+          <t>23000.00</t>
         </is>
       </c>
       <c r="Z111" s="0" t="inlineStr">
@@ -5306,18 +5306,18 @@
         </is>
       </c>
       <c r="AA111" s="0">
-        <v>81</v>
+        <v>138</v>
       </c>
       <c r="AV111" s="0" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>151</t>
         </is>
       </c>
     </row>
     <row r="112" spans="1:48">
       <c r="C112" s="0" t="inlineStr">
         <is>
-          <t>LAGOS LACE F</t>
+          <t>LAGOS LACE E</t>
         </is>
       </c>
       <c r="G112" s="0" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="R112" s="0" t="inlineStr">
         <is>
-          <t>15000.00</t>
+          <t>16064.5441917243</t>
         </is>
       </c>
       <c r="S112" s="0" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="T112" s="0" t="inlineStr">
         <is>
-          <t>18000.00</t>
+          <t>20000.00</t>
         </is>
       </c>
       <c r="Z112" s="0" t="inlineStr">
@@ -5351,18 +5351,18 @@
         </is>
       </c>
       <c r="AA112" s="0">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="AV112" s="0" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>152</t>
         </is>
       </c>
     </row>
     <row r="113" spans="1:48">
       <c r="C113" s="0" t="inlineStr">
         <is>
-          <t>LAGOS LAFFAYA LACE A</t>
+          <t>LAGOS LACE F</t>
         </is>
       </c>
       <c r="G113" s="0" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="R113" s="0" t="inlineStr">
         <is>
-          <t>23000.00</t>
+          <t>15000.00</t>
         </is>
       </c>
       <c r="S113" s="0" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="T113" s="0" t="inlineStr">
         <is>
-          <t>28000.00</t>
+          <t>18000.00</t>
         </is>
       </c>
       <c r="Z113" s="0" t="inlineStr">
@@ -5396,28 +5396,23 @@
         </is>
       </c>
       <c r="AA113" s="0">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="AV113" s="0" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>153</t>
         </is>
       </c>
     </row>
     <row r="114" spans="1:48">
       <c r="C114" s="0" t="inlineStr">
         <is>
-          <t>Lagos laffaya lace B</t>
+          <t>LAGOS LAFFAYA LACE A</t>
         </is>
       </c>
       <c r="G114" s="0" t="inlineStr">
         <is>
-          <t>LAFAYYA</t>
-        </is>
-      </c>
-      <c r="H114" s="0" t="inlineStr">
-        <is>
-          <t>FAHAD TAHIR</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O114" s="0" t="inlineStr">
@@ -5427,7 +5422,7 @@
       </c>
       <c r="R114" s="0" t="inlineStr">
         <is>
-          <t>16000.00</t>
+          <t>23000.00</t>
         </is>
       </c>
       <c r="S114" s="0" t="inlineStr">
@@ -5437,7 +5432,7 @@
       </c>
       <c r="T114" s="0" t="inlineStr">
         <is>
-          <t>21000.00</t>
+          <t>28000.00</t>
         </is>
       </c>
       <c r="Z114" s="0" t="inlineStr">
@@ -5446,23 +5441,28 @@
         </is>
       </c>
       <c r="AA114" s="0">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AV114" s="0" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>149</t>
         </is>
       </c>
     </row>
     <row r="115" spans="1:48">
       <c r="C115" s="0" t="inlineStr">
         <is>
-          <t>LATEST ATAMPA APPLIQUE</t>
+          <t>Lagos laffaya lace B</t>
         </is>
       </c>
       <c r="G115" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>LAFAYYA</t>
+        </is>
+      </c>
+      <c r="H115" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
         </is>
       </c>
       <c r="O115" s="0" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="R115" s="0" t="inlineStr">
         <is>
-          <t>280000.00</t>
+          <t>16000.00</t>
         </is>
       </c>
       <c r="S115" s="0" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="T115" s="0" t="inlineStr">
         <is>
-          <t>350000.00</t>
+          <t>21000.00</t>
         </is>
       </c>
       <c r="Z115" s="0" t="inlineStr">
@@ -5491,18 +5491,18 @@
         </is>
       </c>
       <c r="AA115" s="0">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AV115" s="0" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>197</t>
         </is>
       </c>
     </row>
     <row r="116" spans="1:48">
       <c r="C116" s="0" t="inlineStr">
         <is>
-          <t>LATEST SHERATON SATIN WAX</t>
+          <t>LATEST ATAMPA APPLIQUE</t>
         </is>
       </c>
       <c r="G116" s="0" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="R116" s="0" t="inlineStr">
         <is>
-          <t>265000.00</t>
+          <t>280000.00</t>
         </is>
       </c>
       <c r="S116" s="0" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="T116" s="0" t="inlineStr">
         <is>
-          <t>300000.00</t>
+          <t>350000.00</t>
         </is>
       </c>
       <c r="Z116" s="0" t="inlineStr">
@@ -5536,18 +5536,18 @@
         </is>
       </c>
       <c r="AA116" s="0">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AV116" s="0" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>57</t>
         </is>
       </c>
     </row>
     <row r="117" spans="1:48">
       <c r="C117" s="0" t="inlineStr">
         <is>
-          <t>LATEST ULTRA EMBELLISHED </t>
+          <t>LATEST SHERATON SATIN WAX</t>
         </is>
       </c>
       <c r="G117" s="0" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="R117" s="0" t="inlineStr">
         <is>
-          <t>35000.00</t>
+          <t>265000.00</t>
         </is>
       </c>
       <c r="S117" s="0" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="T117" s="0" t="inlineStr">
         <is>
-          <t>40000.00</t>
+          <t>300000.00</t>
         </is>
       </c>
       <c r="Z117" s="0" t="inlineStr">
@@ -5581,23 +5581,23 @@
         </is>
       </c>
       <c r="AA117" s="0">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="AV117" s="0" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="118" spans="1:48">
       <c r="C118" s="0" t="inlineStr">
         <is>
-          <t>LEXIS AIR</t>
+          <t>LATEST ULTRA EMBELLISHED </t>
         </is>
       </c>
       <c r="G118" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O118" s="0" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="R118" s="0" t="inlineStr">
         <is>
-          <t>6642.8571428571</t>
+          <t>35124.0694789082</t>
         </is>
       </c>
       <c r="S118" s="0" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="T118" s="0" t="inlineStr">
         <is>
-          <t>9500.00</t>
+          <t>40000.00</t>
         </is>
       </c>
       <c r="Z118" s="0" t="inlineStr">
@@ -5626,23 +5626,23 @@
         </is>
       </c>
       <c r="AA118" s="0">
-        <v>562</v>
+        <v>255</v>
       </c>
       <c r="AV118" s="0" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>86</t>
         </is>
       </c>
     </row>
     <row r="119" spans="1:48">
       <c r="C119" s="0" t="inlineStr">
         <is>
-          <t>LONGHUA YARD COLLECTION</t>
+          <t>LEXIS AIR</t>
         </is>
       </c>
       <c r="G119" s="0" t="inlineStr">
         <is>
-          <t>YARD</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O119" s="0" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="R119" s="0" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>6642.8571428571</t>
         </is>
       </c>
       <c r="S119" s="0" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="T119" s="0" t="inlineStr">
         <is>
-          <t>4000.00</t>
+          <t>9500.00</t>
         </is>
       </c>
       <c r="Z119" s="0" t="inlineStr">
@@ -5670,26 +5670,24 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA119" s="0" t="inlineStr">
-        <is>
-          <t>234.5</t>
-        </is>
+      <c r="AA119" s="0">
+        <v>558</v>
       </c>
       <c r="AV119" s="0" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>173</t>
         </is>
       </c>
     </row>
     <row r="120" spans="1:48">
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t>LUXURY AND VEBA PLUS</t>
+          <t>LONGHUA YARD COLLECTION</t>
         </is>
       </c>
       <c r="G120" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>YARD</t>
         </is>
       </c>
       <c r="O120" s="0" t="inlineStr">
@@ -5699,7 +5697,7 @@
       </c>
       <c r="R120" s="0" t="inlineStr">
         <is>
-          <t>7000.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="S120" s="0" t="inlineStr">
@@ -5709,7 +5707,7 @@
       </c>
       <c r="T120" s="0" t="inlineStr">
         <is>
-          <t>8500.00</t>
+          <t>4000.00</t>
         </is>
       </c>
       <c r="Z120" s="0" t="inlineStr">
@@ -5717,19 +5715,21 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA120" s="0">
-        <v>188</v>
+      <c r="AA120" s="0" t="inlineStr">
+        <is>
+          <t>234.5</t>
+        </is>
       </c>
       <c r="AV120" s="0" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>189</t>
         </is>
       </c>
     </row>
     <row r="121" spans="1:48">
       <c r="C121" s="0" t="inlineStr">
         <is>
-          <t>Madam Getzner Gold edition</t>
+          <t>LUXURY AND VEBA PLUS</t>
         </is>
       </c>
       <c r="G121" s="0" t="inlineStr">
@@ -5737,11 +5737,6 @@
           <t>SHADDA</t>
         </is>
       </c>
-      <c r="H121" s="0" t="inlineStr">
-        <is>
-          <t>FAHAD TAHIR</t>
-        </is>
-      </c>
       <c r="O121" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -5749,7 +5744,7 @@
       </c>
       <c r="R121" s="0" t="inlineStr">
         <is>
-          <t>30000.00</t>
+          <t>7000.00</t>
         </is>
       </c>
       <c r="S121" s="0" t="inlineStr">
@@ -5759,7 +5754,7 @@
       </c>
       <c r="T121" s="0" t="inlineStr">
         <is>
-          <t>45000.00</t>
+          <t>8500.00</t>
         </is>
       </c>
       <c r="Z121" s="0" t="inlineStr">
@@ -5768,18 +5763,18 @@
         </is>
       </c>
       <c r="AA121" s="0">
-        <v>99</v>
+        <v>188</v>
       </c>
       <c r="AV121" s="0" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>175</t>
         </is>
       </c>
     </row>
     <row r="122" spans="1:48">
       <c r="C122" s="0" t="inlineStr">
         <is>
-          <t>MADAM GRTZNER MEDIUM</t>
+          <t>Madam Getzner Gold edition</t>
         </is>
       </c>
       <c r="G122" s="0" t="inlineStr">
@@ -5787,6 +5782,11 @@
           <t>SHADDA</t>
         </is>
       </c>
+      <c r="H122" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
+        </is>
+      </c>
       <c r="O122" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="R122" s="0" t="inlineStr">
         <is>
-          <t>5500.00</t>
+          <t>30000.00</t>
         </is>
       </c>
       <c r="S122" s="0" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="T122" s="0" t="inlineStr">
         <is>
-          <t>7500.00</t>
+          <t>45000.00</t>
         </is>
       </c>
       <c r="Z122" s="0" t="inlineStr">
@@ -5813,28 +5813,23 @@
         </is>
       </c>
       <c r="AA122" s="0">
-        <v>328</v>
+        <v>97</v>
       </c>
       <c r="AV122" s="0" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>207</t>
         </is>
       </c>
     </row>
     <row r="123" spans="1:48">
       <c r="C123" s="0" t="inlineStr">
         <is>
-          <t>Magic holland</t>
+          <t>MADAM GRTZNER MEDIUM</t>
         </is>
       </c>
       <c r="G123" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
-        </is>
-      </c>
-      <c r="H123" s="0" t="inlineStr">
-        <is>
-          <t>YAYA SANI</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O123" s="0" t="inlineStr">
@@ -5844,7 +5839,7 @@
       </c>
       <c r="R123" s="0" t="inlineStr">
         <is>
-          <t>9500.00</t>
+          <t>5500.00</t>
         </is>
       </c>
       <c r="S123" s="0" t="inlineStr">
@@ -5854,7 +5849,7 @@
       </c>
       <c r="T123" s="0" t="inlineStr">
         <is>
-          <t>10500.00</t>
+          <t>7500.00</t>
         </is>
       </c>
       <c r="Z123" s="0" t="inlineStr">
@@ -5863,18 +5858,18 @@
         </is>
       </c>
       <c r="AA123" s="0">
-        <v>95</v>
+        <v>935</v>
       </c>
       <c r="AV123" s="0" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="124" spans="1:48">
       <c r="C124" s="0" t="inlineStr">
         <is>
-          <t>MEDIUM EMBELLISHED </t>
+          <t>Magic holland</t>
         </is>
       </c>
       <c r="G124" s="0" t="inlineStr">
@@ -5882,6 +5877,11 @@
           <t>ATAMPA</t>
         </is>
       </c>
+      <c r="H124" s="0" t="inlineStr">
+        <is>
+          <t>YAYA SANI</t>
+        </is>
+      </c>
       <c r="O124" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="R124" s="0" t="inlineStr">
         <is>
-          <t>18000.00</t>
+          <t>9500.00</t>
         </is>
       </c>
       <c r="S124" s="0" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="T124" s="0" t="inlineStr">
         <is>
-          <t>20000.00</t>
+          <t>10500.00</t>
         </is>
       </c>
       <c r="Z124" s="0" t="inlineStr">
@@ -5908,18 +5908,18 @@
         </is>
       </c>
       <c r="AA124" s="0">
-        <v>9</v>
+        <v>164</v>
       </c>
       <c r="AV124" s="0" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>206</t>
         </is>
       </c>
     </row>
     <row r="125" spans="1:48">
       <c r="C125" s="0" t="inlineStr">
         <is>
-          <t>MEDIUM GLITTER</t>
+          <t>MEDIUM EMBELLISHED </t>
         </is>
       </c>
       <c r="G125" s="0" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="R125" s="0" t="inlineStr">
         <is>
-          <t>14500.00</t>
+          <t>18000.00</t>
         </is>
       </c>
       <c r="S125" s="0" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="T125" s="0" t="inlineStr">
         <is>
-          <t>18000.00</t>
+          <t>20000.00</t>
         </is>
       </c>
       <c r="Z125" s="0" t="inlineStr">
@@ -5953,18 +5953,18 @@
         </is>
       </c>
       <c r="AA125" s="0">
-        <v>350</v>
+        <v>9</v>
       </c>
       <c r="AV125" s="0" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>113</t>
         </is>
       </c>
     </row>
     <row r="126" spans="1:48">
       <c r="C126" s="0" t="inlineStr">
         <is>
-          <t>MEDIUM SUPER </t>
+          <t>MEDIUM GLITTER</t>
         </is>
       </c>
       <c r="G126" s="0" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="R126" s="0" t="inlineStr">
         <is>
-          <t>12541.1181181036</t>
+          <t>14500.00</t>
         </is>
       </c>
       <c r="S126" s="0" t="inlineStr">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="T126" s="0" t="inlineStr">
         <is>
-          <t>14000.00</t>
+          <t>18000.00</t>
         </is>
       </c>
       <c r="Z126" s="0" t="inlineStr">
@@ -5998,18 +5998,18 @@
         </is>
       </c>
       <c r="AA126" s="0">
-        <v>87</v>
+        <v>312</v>
       </c>
       <c r="AV126" s="0" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>116</t>
         </is>
       </c>
     </row>
     <row r="127" spans="1:48">
       <c r="C127" s="0" t="inlineStr">
         <is>
-          <t>MITEX HOLLAND </t>
+          <t>MEDIUM SUPER </t>
         </is>
       </c>
       <c r="G127" s="0" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="R127" s="0" t="inlineStr">
         <is>
-          <t>47000.00</t>
+          <t>12541.1181181036</t>
         </is>
       </c>
       <c r="S127" s="0" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="T127" s="0" t="inlineStr">
         <is>
-          <t>55000.00</t>
+          <t>14000.00</t>
         </is>
       </c>
       <c r="Z127" s="0" t="inlineStr">
@@ -6043,23 +6043,23 @@
         </is>
       </c>
       <c r="AA127" s="0">
-        <v>2</v>
+        <v>86</v>
       </c>
       <c r="AV127" s="0" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>123</t>
         </is>
       </c>
     </row>
     <row r="128" spans="1:48">
       <c r="C128" s="0" t="inlineStr">
         <is>
-          <t>MOONLIGHT AND SUPREME FOLDER</t>
+          <t>MITEX HOLLAND </t>
         </is>
       </c>
       <c r="G128" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O128" s="0" t="inlineStr">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="R128" s="0" t="inlineStr">
         <is>
-          <t>5000.00</t>
+          <t>47000.00</t>
         </is>
       </c>
       <c r="S128" s="0" t="inlineStr">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="T128" s="0" t="inlineStr">
         <is>
-          <t>6500.00</t>
+          <t>55000.00</t>
         </is>
       </c>
       <c r="Z128" s="0" t="inlineStr">
@@ -6088,23 +6088,23 @@
         </is>
       </c>
       <c r="AA128" s="0">
-        <v>187</v>
+        <v>2</v>
       </c>
       <c r="AV128" s="0" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="129" spans="1:48">
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t>MUHANTEX EMBELLISHED</t>
+          <t>MOONLIGHT AND SUPREME FOLDER</t>
         </is>
       </c>
       <c r="G129" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O129" s="0" t="inlineStr">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="R129" s="0" t="inlineStr">
         <is>
-          <t>15500.00</t>
+          <t>5000.00</t>
         </is>
       </c>
       <c r="S129" s="0" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="T129" s="0" t="inlineStr">
         <is>
-          <t>18000.00</t>
+          <t>6500.00</t>
         </is>
       </c>
       <c r="Z129" s="0" t="inlineStr">
@@ -6133,23 +6133,23 @@
         </is>
       </c>
       <c r="AA129" s="0">
-        <v>86</v>
+        <v>187</v>
       </c>
       <c r="AV129" s="0" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>177</t>
         </is>
       </c>
     </row>
     <row r="130" spans="1:48">
       <c r="C130" s="0" t="inlineStr">
         <is>
-          <t>NBTX 400</t>
+          <t>MUHANTEX EMBELLISHED</t>
         </is>
       </c>
       <c r="G130" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O130" s="0" t="inlineStr">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="R130" s="0" t="inlineStr">
         <is>
-          <t>22000.00</t>
+          <t>15500.00</t>
         </is>
       </c>
       <c r="S130" s="0" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="T130" s="0" t="inlineStr">
         <is>
-          <t>25000.00</t>
+          <t>18000.00</t>
         </is>
       </c>
       <c r="Z130" s="0" t="inlineStr">
@@ -6177,26 +6177,24 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA130" s="0" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
+      <c r="AA130" s="0">
+        <v>86</v>
       </c>
       <c r="AV130" s="0" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>155</t>
         </is>
       </c>
     </row>
     <row r="131" spans="1:48">
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t>NEW JULIUS HOLLAND</t>
+          <t>NBTX 400</t>
         </is>
       </c>
       <c r="G131" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O131" s="0" t="inlineStr">
@@ -6206,7 +6204,7 @@
       </c>
       <c r="R131" s="0" t="inlineStr">
         <is>
-          <t>62000.00</t>
+          <t>22000.00</t>
         </is>
       </c>
       <c r="S131" s="0" t="inlineStr">
@@ -6216,7 +6214,7 @@
       </c>
       <c r="T131" s="0" t="inlineStr">
         <is>
-          <t>70000.00</t>
+          <t>25000.00</t>
         </is>
       </c>
       <c r="Z131" s="0" t="inlineStr">
@@ -6224,24 +6222,26 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA131" s="0">
-        <v>36</v>
+      <c r="AA131" s="0" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
       </c>
       <c r="AV131" s="0" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>185</t>
         </is>
       </c>
     </row>
     <row r="132" spans="1:48">
       <c r="C132" s="0" t="inlineStr">
         <is>
-          <t>NEW MADAM MEDIUM GETZNER</t>
+          <t>NEW JULIUS HOLLAND</t>
         </is>
       </c>
       <c r="G132" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O132" s="0" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="R132" s="0" t="inlineStr">
         <is>
-          <t>7000.00</t>
+          <t>62000.00</t>
         </is>
       </c>
       <c r="S132" s="0" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="T132" s="0" t="inlineStr">
         <is>
-          <t>10000.00</t>
+          <t>70000.00</t>
         </is>
       </c>
       <c r="Z132" s="0" t="inlineStr">
@@ -6270,23 +6270,23 @@
         </is>
       </c>
       <c r="AA132" s="0">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="AV132" s="0" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>82</t>
         </is>
       </c>
     </row>
     <row r="133" spans="1:48">
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t>NEW MEDIUM GLITTER </t>
+          <t>NEW MADAM MEDIUM GETZNER</t>
         </is>
       </c>
       <c r="G133" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O133" s="0" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="R133" s="0" t="inlineStr">
         <is>
-          <t>19000.00</t>
+          <t>7000.00</t>
         </is>
       </c>
       <c r="S133" s="0" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="T133" s="0" t="inlineStr">
         <is>
-          <t>22000.00</t>
+          <t>10000.00</t>
         </is>
       </c>
       <c r="Z133" s="0" t="inlineStr">
@@ -6315,18 +6315,18 @@
         </is>
       </c>
       <c r="AA133" s="0">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="AV133" s="0" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>54</t>
         </is>
       </c>
     </row>
     <row r="134" spans="1:48">
       <c r="C134" s="0" t="inlineStr">
         <is>
-          <t>NEW POPULAR</t>
+          <t>NEW MEDIUM GLITTER </t>
         </is>
       </c>
       <c r="G134" s="0" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="R134" s="0" t="inlineStr">
         <is>
-          <t>9000.00</t>
+          <t>19000.00</t>
         </is>
       </c>
       <c r="S134" s="0" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="T134" s="0" t="inlineStr">
         <is>
-          <t>10000.00</t>
+          <t>22000.00</t>
         </is>
       </c>
       <c r="Z134" s="0" t="inlineStr">
@@ -6360,18 +6360,18 @@
         </is>
       </c>
       <c r="AA134" s="0">
-        <v>286</v>
+        <v>31</v>
       </c>
       <c r="AV134" s="0" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>110</t>
         </is>
       </c>
     </row>
     <row r="135" spans="1:48">
       <c r="C135" s="0" t="inlineStr">
         <is>
-          <t>NEW SHERATON SATIN WAX</t>
+          <t>NEW POPULAR</t>
         </is>
       </c>
       <c r="G135" s="0" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="R135" s="0" t="inlineStr">
         <is>
-          <t>230000.00</t>
+          <t>9000.00</t>
         </is>
       </c>
       <c r="S135" s="0" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="T135" s="0" t="inlineStr">
         <is>
-          <t>250000.00</t>
+          <t>10000.00</t>
         </is>
       </c>
       <c r="Z135" s="0" t="inlineStr">
@@ -6405,18 +6405,18 @@
         </is>
       </c>
       <c r="AA135" s="0">
-        <v>2</v>
+        <v>269</v>
       </c>
       <c r="AV135" s="0" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>133</t>
         </is>
       </c>
     </row>
     <row r="136" spans="1:48">
       <c r="C136" s="0" t="inlineStr">
         <is>
-          <t>NEW SUPER HOLLAND EMBELLISHED</t>
+          <t>NEW SHERATON SATIN WAX</t>
         </is>
       </c>
       <c r="G136" s="0" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="T136" s="0" t="inlineStr">
         <is>
-          <t>260000.00</t>
+          <t>250000.00</t>
         </is>
       </c>
       <c r="Z136" s="0" t="inlineStr">
@@ -6454,19 +6454,19 @@
       </c>
       <c r="AV136" s="0" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="137" spans="1:48">
       <c r="C137" s="0" t="inlineStr">
         <is>
-          <t>NEW TRAVELLING AND SUPER POLISH</t>
+          <t>NEW SUPER HOLLAND EMBELLISHED</t>
         </is>
       </c>
       <c r="G137" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O137" s="0" t="inlineStr">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="R137" s="0" t="inlineStr">
         <is>
-          <t>4000.00</t>
+          <t>230000.00</t>
         </is>
       </c>
       <c r="S137" s="0" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="T137" s="0" t="inlineStr">
         <is>
-          <t>5000.00</t>
+          <t>260000.00</t>
         </is>
       </c>
       <c r="Z137" s="0" t="inlineStr">
@@ -6495,23 +6495,23 @@
         </is>
       </c>
       <c r="AA137" s="0">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="AV137" s="0" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>72</t>
         </is>
       </c>
     </row>
     <row r="138" spans="1:48">
       <c r="C138" s="0" t="inlineStr">
         <is>
-          <t>NEW ULTRA EMBELLISHED</t>
+          <t>NEW TRAVELLING AND SUPER POLISH</t>
         </is>
       </c>
       <c r="G138" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O138" s="0" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="R138" s="0" t="inlineStr">
         <is>
-          <t>30532.1100917431</t>
+          <t>4000.00</t>
         </is>
       </c>
       <c r="S138" s="0" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="T138" s="0" t="inlineStr">
         <is>
-          <t>35000.00</t>
+          <t>5000.00</t>
         </is>
       </c>
       <c r="Z138" s="0" t="inlineStr">
@@ -6540,18 +6540,18 @@
         </is>
       </c>
       <c r="AA138" s="0">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="AV138" s="0" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>179</t>
         </is>
       </c>
     </row>
     <row r="139" spans="1:48">
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t>PATCHWORK ATAMPA </t>
+          <t>NEW ULTRA EMBELLISHED</t>
         </is>
       </c>
       <c r="G139" s="0" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="R139" s="0" t="inlineStr">
         <is>
-          <t>70000.00</t>
+          <t>30532.1100917431</t>
         </is>
       </c>
       <c r="S139" s="0" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="T139" s="0" t="inlineStr">
         <is>
-          <t>85000.00</t>
+          <t>35000.00</t>
         </is>
       </c>
       <c r="Z139" s="0" t="inlineStr">
@@ -6585,18 +6585,18 @@
         </is>
       </c>
       <c r="AA139" s="0">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AV139" s="0" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>156</t>
         </is>
       </c>
     </row>
     <row r="140" spans="1:48">
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t>PATCHWORK ATAMPA MIX AND MATCH</t>
+          <t>PATCHWORK ATAMPA </t>
         </is>
       </c>
       <c r="G140" s="0" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="R140" s="0" t="inlineStr">
         <is>
-          <t>54000.00</t>
+          <t>70000.00</t>
         </is>
       </c>
       <c r="S140" s="0" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="T140" s="0" t="inlineStr">
         <is>
-          <t>60000.00</t>
+          <t>85000.00</t>
         </is>
       </c>
       <c r="Z140" s="0" t="inlineStr">
@@ -6630,18 +6630,18 @@
         </is>
       </c>
       <c r="AA140" s="0">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AV140" s="0" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>60</t>
         </is>
       </c>
     </row>
     <row r="141" spans="1:48">
       <c r="C141" s="0" t="inlineStr">
         <is>
-          <t>PERFECT ROYAL JAVA</t>
+          <t>PATCHWORK ATAMPA MIX AND MATCH</t>
         </is>
       </c>
       <c r="G141" s="0" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="R141" s="0" t="inlineStr">
         <is>
-          <t>30000.00</t>
+          <t>54000.00</t>
         </is>
       </c>
       <c r="S141" s="0" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="T141" s="0" t="inlineStr">
         <is>
-          <t>35000.00</t>
+          <t>60000.00</t>
         </is>
       </c>
       <c r="Z141" s="0" t="inlineStr">
@@ -6675,18 +6675,18 @@
         </is>
       </c>
       <c r="AA141" s="0">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV141" s="0" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>145</t>
         </is>
       </c>
     </row>
     <row r="142" spans="1:48">
       <c r="C142" s="0" t="inlineStr">
         <is>
-          <t>PRESTIGE EMBELLISHED</t>
+          <t>PERFECT ROYAL JAVA</t>
         </is>
       </c>
       <c r="G142" s="0" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="R142" s="0" t="inlineStr">
         <is>
-          <t>15500.00</t>
+          <t>30000.00</t>
         </is>
       </c>
       <c r="S142" s="0" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="T142" s="0" t="inlineStr">
         <is>
-          <t>17500.00</t>
+          <t>35000.00</t>
         </is>
       </c>
       <c r="Z142" s="0" t="inlineStr">
@@ -6720,23 +6720,23 @@
         </is>
       </c>
       <c r="AA142" s="0">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="AV142" s="0" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="143" spans="1:48">
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t>RIEDMAN MENLACE</t>
+          <t>PRESTIGE EMBELLISHED</t>
         </is>
       </c>
       <c r="G143" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O143" s="0" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="R143" s="0" t="inlineStr">
         <is>
-          <t>410000.00</t>
+          <t>15502.427184466</t>
         </is>
       </c>
       <c r="S143" s="0" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="T143" s="0" t="inlineStr">
         <is>
-          <t>500000.00</t>
+          <t>17500.00</t>
         </is>
       </c>
       <c r="Z143" s="0" t="inlineStr">
@@ -6765,18 +6765,18 @@
         </is>
       </c>
       <c r="AA143" s="0">
-        <v>6</v>
+        <v>190</v>
       </c>
       <c r="AV143" s="0" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>118</t>
         </is>
       </c>
     </row>
     <row r="144" spans="1:48">
       <c r="C144" s="0" t="inlineStr">
         <is>
-          <t>RIEDMAN TAIWO ATIKU</t>
+          <t>RIEDMAN MENLACE</t>
         </is>
       </c>
       <c r="G144" s="0" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="R144" s="0" t="inlineStr">
         <is>
-          <t>260000.00</t>
+          <t>410000.00</t>
         </is>
       </c>
       <c r="S144" s="0" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="T144" s="0" t="inlineStr">
         <is>
-          <t>380000.00</t>
+          <t>500000.00</t>
         </is>
       </c>
       <c r="Z144" s="0" t="inlineStr">
@@ -6809,26 +6809,24 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA144" s="0" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
+      <c r="AA144" s="0">
+        <v>6</v>
       </c>
       <c r="AV144" s="0" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>162</t>
         </is>
       </c>
     </row>
     <row r="145" spans="1:48">
       <c r="C145" s="0" t="inlineStr">
         <is>
-          <t>RIGHTMAN AND WISEMAN</t>
+          <t>RIEDMAN TAIWO ATIKU</t>
         </is>
       </c>
       <c r="G145" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O145" s="0" t="inlineStr">
@@ -6838,7 +6836,7 @@
       </c>
       <c r="R145" s="0" t="inlineStr">
         <is>
-          <t>4000.00</t>
+          <t>260000.00</t>
         </is>
       </c>
       <c r="S145" s="0" t="inlineStr">
@@ -6848,7 +6846,7 @@
       </c>
       <c r="T145" s="0" t="inlineStr">
         <is>
-          <t>5500.00</t>
+          <t>380000.00</t>
         </is>
       </c>
       <c r="Z145" s="0" t="inlineStr">
@@ -6856,24 +6854,26 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA145" s="0">
-        <v>548</v>
+      <c r="AA145" s="0" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
       </c>
       <c r="AV145" s="0" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>164</t>
         </is>
       </c>
     </row>
     <row r="146" spans="1:48">
       <c r="C146" s="0" t="inlineStr">
         <is>
-          <t>ROBA ATAMPA</t>
+          <t>RIGHTMAN AND WISEMAN</t>
         </is>
       </c>
       <c r="G146" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O146" s="0" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="R146" s="0" t="inlineStr">
         <is>
-          <t>2700.00</t>
+          <t>4000.00</t>
         </is>
       </c>
       <c r="S146" s="0" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="T146" s="0" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>5500.00</t>
         </is>
       </c>
       <c r="Z146" s="0" t="inlineStr">
@@ -6902,18 +6902,18 @@
         </is>
       </c>
       <c r="AA146" s="0">
-        <v>357</v>
+        <v>526</v>
       </c>
       <c r="AV146" s="0" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>178</t>
         </is>
       </c>
     </row>
     <row r="147" spans="1:48">
       <c r="C147" s="0" t="inlineStr">
         <is>
-          <t>Rotana holland</t>
+          <t>ROBA ATAMPA</t>
         </is>
       </c>
       <c r="G147" s="0" t="inlineStr">
@@ -6921,11 +6921,6 @@
           <t>ATAMPA</t>
         </is>
       </c>
-      <c r="H147" s="0" t="inlineStr">
-        <is>
-          <t>YAYA SANI</t>
-        </is>
-      </c>
       <c r="O147" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -6933,7 +6928,7 @@
       </c>
       <c r="R147" s="0" t="inlineStr">
         <is>
-          <t>8000.00</t>
+          <t>2700.00</t>
         </is>
       </c>
       <c r="S147" s="0" t="inlineStr">
@@ -6943,7 +6938,7 @@
       </c>
       <c r="T147" s="0" t="inlineStr">
         <is>
-          <t>8500.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="Z147" s="0" t="inlineStr">
@@ -6952,23 +6947,28 @@
         </is>
       </c>
       <c r="AA147" s="0">
-        <v>216</v>
+        <v>328</v>
       </c>
       <c r="AV147" s="0" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>143</t>
         </is>
       </c>
     </row>
     <row r="148" spans="1:48">
       <c r="C148" s="0" t="inlineStr">
         <is>
-          <t>Shadda lace</t>
+          <t>Rotana holland</t>
         </is>
       </c>
       <c r="G148" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="H148" s="0" t="inlineStr">
+        <is>
+          <t>YAYA SANI</t>
         </is>
       </c>
       <c r="O148" s="0" t="inlineStr">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="R148" s="0" t="inlineStr">
         <is>
-          <t>25000.00</t>
+          <t>8021.5189873418</t>
         </is>
       </c>
       <c r="S148" s="0" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="T148" s="0" t="inlineStr">
         <is>
-          <t>32000.00</t>
+          <t>8500.00</t>
         </is>
       </c>
       <c r="Z148" s="0" t="inlineStr">
@@ -6997,23 +6997,23 @@
         </is>
       </c>
       <c r="AA148" s="0">
-        <v>11</v>
+        <v>134</v>
       </c>
       <c r="AV148" s="0" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>214</t>
         </is>
       </c>
     </row>
     <row r="149" spans="1:48">
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t>SHERATON BROCADE</t>
+          <t>Shadda lace</t>
         </is>
       </c>
       <c r="G149" s="0" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O149" s="0" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="R149" s="0" t="inlineStr">
         <is>
-          <t>80000.00</t>
+          <t>25000.00</t>
         </is>
       </c>
       <c r="S149" s="0" t="inlineStr">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="T149" s="0" t="inlineStr">
         <is>
-          <t>100000.00</t>
+          <t>32000.00</t>
         </is>
       </c>
       <c r="Z149" s="0" t="inlineStr">
@@ -7042,23 +7042,23 @@
         </is>
       </c>
       <c r="AA149" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AV149" s="0" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>205</t>
         </is>
       </c>
     </row>
     <row r="150" spans="1:48">
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t>SHERATON EXCLUSIVE EMBELLISHED</t>
+          <t>SHERATON BROCADE</t>
         </is>
       </c>
       <c r="G150" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="O150" s="0" t="inlineStr">
@@ -7068,7 +7068,7 @@
       </c>
       <c r="R150" s="0" t="inlineStr">
         <is>
-          <t>244006.0851926978</t>
+          <t>80000.00</t>
         </is>
       </c>
       <c r="S150" s="0" t="inlineStr">
@@ -7078,7 +7078,7 @@
       </c>
       <c r="T150" s="0" t="inlineStr">
         <is>
-          <t>280000.00</t>
+          <t>100000.00</t>
         </is>
       </c>
       <c r="Z150" s="0" t="inlineStr">
@@ -7087,18 +7087,18 @@
         </is>
       </c>
       <c r="AA150" s="0">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="AV150" s="0" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="151" spans="1:48">
       <c r="C151" s="0" t="inlineStr">
         <is>
-          <t>SHERATON EXCLUSIVE PLAIN </t>
+          <t>SHERATON EXCLUSIVE EMBELLISHED</t>
         </is>
       </c>
       <c r="G151" s="0" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="R151" s="0" t="inlineStr">
         <is>
-          <t>200000.00</t>
+          <t>244006.0851926978</t>
         </is>
       </c>
       <c r="S151" s="0" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="T151" s="0" t="inlineStr">
         <is>
-          <t>220000.00</t>
+          <t>280000.00</t>
         </is>
       </c>
       <c r="Z151" s="0" t="inlineStr">
@@ -7132,18 +7132,18 @@
         </is>
       </c>
       <c r="AA151" s="0">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="AV151" s="0" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="152" spans="1:48">
       <c r="C152" s="0" t="inlineStr">
         <is>
-          <t>SHERATON HOLLAND EMBELLISHED</t>
+          <t>SHERATON EXCLUSIVE PLAIN </t>
         </is>
       </c>
       <c r="G152" s="0" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="R152" s="0" t="inlineStr">
         <is>
-          <t>210000.00</t>
+          <t>200000.00</t>
         </is>
       </c>
       <c r="S152" s="0" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="T152" s="0" t="inlineStr">
         <is>
-          <t>240000.00</t>
+          <t>220000.00</t>
         </is>
       </c>
       <c r="Z152" s="0" t="inlineStr">
@@ -7177,18 +7177,18 @@
         </is>
       </c>
       <c r="AA152" s="0">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="AV152" s="0" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>71</t>
         </is>
       </c>
     </row>
     <row r="153" spans="1:48">
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t>SHERATON HOLLAND PLAIN</t>
+          <t>SHERATON HOLLAND EMBELLISHED</t>
         </is>
       </c>
       <c r="G153" s="0" t="inlineStr">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="R153" s="0" t="inlineStr">
         <is>
-          <t>150000.00</t>
+          <t>210000.00</t>
         </is>
       </c>
       <c r="S153" s="0" t="inlineStr">
@@ -7213,7 +7213,7 @@
       </c>
       <c r="T153" s="0" t="inlineStr">
         <is>
-          <t>180000.00</t>
+          <t>240000.00</t>
         </is>
       </c>
       <c r="Z153" s="0" t="inlineStr">
@@ -7222,18 +7222,18 @@
         </is>
       </c>
       <c r="AA153" s="0">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AV153" s="0" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>74</t>
         </is>
       </c>
     </row>
     <row r="154" spans="1:48">
       <c r="C154" s="0" t="inlineStr">
         <is>
-          <t>SHERATON SATIN WAX</t>
+          <t>SHERATON HOLLAND PLAIN</t>
         </is>
       </c>
       <c r="G154" s="0" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="R154" s="0" t="inlineStr">
         <is>
-          <t>160000.00</t>
+          <t>150000.00</t>
         </is>
       </c>
       <c r="S154" s="0" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="T154" s="0" t="inlineStr">
         <is>
-          <t>200000.00</t>
+          <t>180000.00</t>
         </is>
       </c>
       <c r="Z154" s="0" t="inlineStr">
@@ -7267,23 +7267,23 @@
         </is>
       </c>
       <c r="AA154" s="0">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV154" s="0" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>75</t>
         </is>
       </c>
     </row>
     <row r="155" spans="1:48">
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t>SMALL KAMPALA</t>
+          <t>SHERATON SATIN WAX</t>
         </is>
       </c>
       <c r="G155" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O155" s="0" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="R155" s="0" t="inlineStr">
         <is>
-          <t>3500.00</t>
+          <t>160000.00</t>
         </is>
       </c>
       <c r="S155" s="0" t="inlineStr">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="T155" s="0" t="inlineStr">
         <is>
-          <t>4500.00</t>
+          <t>200000.00</t>
         </is>
       </c>
       <c r="Z155" s="0" t="inlineStr">
@@ -7312,23 +7312,23 @@
         </is>
       </c>
       <c r="AA155" s="0">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="AV155" s="0" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>69</t>
         </is>
       </c>
     </row>
     <row r="156" spans="1:48">
       <c r="C156" s="0" t="inlineStr">
         <is>
-          <t>Sober And Queen VOILE EMBROIDERY </t>
+          <t>SMALL KAMPALA</t>
         </is>
       </c>
       <c r="G156" s="0" t="inlineStr">
         <is>
-          <t>VOILE</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O156" s="0" t="inlineStr">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="R156" s="0" t="inlineStr">
         <is>
-          <t>32000.00</t>
+          <t>3500.00</t>
         </is>
       </c>
       <c r="S156" s="0" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="T156" s="0" t="inlineStr">
         <is>
-          <t>40000.00</t>
+          <t>4500.00</t>
         </is>
       </c>
       <c r="Z156" s="0" t="inlineStr">
@@ -7357,23 +7357,23 @@
         </is>
       </c>
       <c r="AA156" s="0">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AV156" s="0" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>154</t>
         </is>
       </c>
     </row>
     <row r="157" spans="1:48">
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t>SOLARI YARD COLLECTION</t>
+          <t>Sober And Queen VOILE EMBROIDERY </t>
         </is>
       </c>
       <c r="G157" s="0" t="inlineStr">
         <is>
-          <t>YARD</t>
+          <t>VOILE</t>
         </is>
       </c>
       <c r="O157" s="0" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="R157" s="0" t="inlineStr">
         <is>
-          <t>2000.00</t>
+          <t>32000.00</t>
         </is>
       </c>
       <c r="S157" s="0" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="T157" s="0" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>40000.00</t>
         </is>
       </c>
       <c r="Z157" s="0" t="inlineStr">
@@ -7401,26 +7401,24 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA157" s="0" t="inlineStr">
-        <is>
-          <t>550.5</t>
-        </is>
+      <c r="AA157" s="0">
+        <v>9</v>
       </c>
       <c r="AV157" s="0" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="158" spans="1:48">
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t>STONE EMBELLISHED MIX ND MATCH</t>
+          <t>SOLARI YARD COLLECTION</t>
         </is>
       </c>
       <c r="G158" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>YARD</t>
         </is>
       </c>
       <c r="O158" s="0" t="inlineStr">
@@ -7430,7 +7428,7 @@
       </c>
       <c r="R158" s="0" t="inlineStr">
         <is>
-          <t>17000.00</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="S158" s="0" t="inlineStr">
@@ -7440,7 +7438,7 @@
       </c>
       <c r="T158" s="0" t="inlineStr">
         <is>
-          <t>19000.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="Z158" s="0" t="inlineStr">
@@ -7449,18 +7447,18 @@
         </is>
       </c>
       <c r="AA158" s="0">
-        <v>7</v>
+        <v>542</v>
       </c>
       <c r="AV158" s="0" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>190</t>
         </is>
       </c>
     </row>
     <row r="159" spans="1:48">
       <c r="C159" s="0" t="inlineStr">
         <is>
-          <t>SUBLIME COTED'VIORE</t>
+          <t>STONE EMBELLISHED MIX ND MATCH</t>
         </is>
       </c>
       <c r="G159" s="0" t="inlineStr">
@@ -7475,7 +7473,7 @@
       </c>
       <c r="R159" s="0" t="inlineStr">
         <is>
-          <t>18500.00</t>
+          <t>17000.00</t>
         </is>
       </c>
       <c r="S159" s="0" t="inlineStr">
@@ -7485,7 +7483,7 @@
       </c>
       <c r="T159" s="0" t="inlineStr">
         <is>
-          <t>20000.00</t>
+          <t>19000.00</t>
         </is>
       </c>
       <c r="Z159" s="0" t="inlineStr">
@@ -7494,18 +7492,18 @@
         </is>
       </c>
       <c r="AA159" s="0">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AV159" s="0" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>112</t>
         </is>
       </c>
     </row>
     <row r="160" spans="1:48">
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t>SUBLIME STONE EMBELLISHED</t>
+          <t>SUBLIME COTED'VIORE</t>
         </is>
       </c>
       <c r="G160" s="0" t="inlineStr">
@@ -7520,7 +7518,7 @@
       </c>
       <c r="R160" s="0" t="inlineStr">
         <is>
-          <t>18000.00</t>
+          <t>18500.00</t>
         </is>
       </c>
       <c r="S160" s="0" t="inlineStr">
@@ -7539,18 +7537,18 @@
         </is>
       </c>
       <c r="AA160" s="0">
-        <v>150</v>
+        <v>14</v>
       </c>
       <c r="AV160" s="0" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>108</t>
         </is>
       </c>
     </row>
     <row r="161" spans="1:48">
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t>SUPER BRILLIANT </t>
+          <t>SUBLIME STONE EMBELLISHED</t>
         </is>
       </c>
       <c r="G161" s="0" t="inlineStr">
@@ -7565,7 +7563,7 @@
       </c>
       <c r="R161" s="0" t="inlineStr">
         <is>
-          <t>11000.00</t>
+          <t>18000.00</t>
         </is>
       </c>
       <c r="S161" s="0" t="inlineStr">
@@ -7575,7 +7573,7 @@
       </c>
       <c r="T161" s="0" t="inlineStr">
         <is>
-          <t>12000.00</t>
+          <t>20000.00</t>
         </is>
       </c>
       <c r="Z161" s="0" t="inlineStr">
@@ -7584,18 +7582,18 @@
         </is>
       </c>
       <c r="AA161" s="0">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="AV161" s="0" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>95</t>
         </is>
       </c>
     </row>
     <row r="162" spans="1:48">
       <c r="C162" s="0" t="inlineStr">
         <is>
-          <t>SUPER FAMOUS</t>
+          <t>SUPER BRILLIANT </t>
         </is>
       </c>
       <c r="G162" s="0" t="inlineStr">
@@ -7610,7 +7608,7 @@
       </c>
       <c r="R162" s="0" t="inlineStr">
         <is>
-          <t>9008.4040321109</t>
+          <t>11000.00</t>
         </is>
       </c>
       <c r="S162" s="0" t="inlineStr">
@@ -7620,7 +7618,7 @@
       </c>
       <c r="T162" s="0" t="inlineStr">
         <is>
-          <t>10000.00</t>
+          <t>12000.00</t>
         </is>
       </c>
       <c r="Z162" s="0" t="inlineStr">
@@ -7629,18 +7627,18 @@
         </is>
       </c>
       <c r="AA162" s="0">
-        <v>226</v>
+        <v>100</v>
       </c>
       <c r="AV162" s="0" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>127</t>
         </is>
       </c>
     </row>
     <row r="163" spans="1:48">
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t>SUPER FASHION</t>
+          <t>SUPER FAMOUS</t>
         </is>
       </c>
       <c r="G163" s="0" t="inlineStr">
@@ -7655,7 +7653,7 @@
       </c>
       <c r="R163" s="0" t="inlineStr">
         <is>
-          <t>10007.5373258309</t>
+          <t>9008.4040321109</t>
         </is>
       </c>
       <c r="S163" s="0" t="inlineStr">
@@ -7665,7 +7663,7 @@
       </c>
       <c r="T163" s="0" t="inlineStr">
         <is>
-          <t>11000.00</t>
+          <t>10000.00</t>
         </is>
       </c>
       <c r="Z163" s="0" t="inlineStr">
@@ -7674,18 +7672,18 @@
         </is>
       </c>
       <c r="AA163" s="0">
-        <v>119</v>
+        <v>190</v>
       </c>
       <c r="AV163" s="0" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>137</t>
         </is>
       </c>
     </row>
     <row r="164" spans="1:48">
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>SUPER HOLLAND EMBELLISHED</t>
+          <t>SUPER FASHION</t>
         </is>
       </c>
       <c r="G164" s="0" t="inlineStr">
@@ -7700,7 +7698,7 @@
       </c>
       <c r="R164" s="0" t="inlineStr">
         <is>
-          <t>220000.00</t>
+          <t>10007.5373258309</t>
         </is>
       </c>
       <c r="S164" s="0" t="inlineStr">
@@ -7710,7 +7708,7 @@
       </c>
       <c r="T164" s="0" t="inlineStr">
         <is>
-          <t>250000.00</t>
+          <t>11000.00</t>
         </is>
       </c>
       <c r="Z164" s="0" t="inlineStr">
@@ -7719,18 +7717,18 @@
         </is>
       </c>
       <c r="AA164" s="0">
-        <v>9</v>
+        <v>115</v>
       </c>
       <c r="AV164" s="0" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>128</t>
         </is>
       </c>
     </row>
     <row r="165" spans="1:48">
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>SUPER HOLLAND WAX</t>
+          <t>SUPER HOLLAND EMBELLISHED</t>
         </is>
       </c>
       <c r="G165" s="0" t="inlineStr">
@@ -7745,7 +7743,7 @@
       </c>
       <c r="R165" s="0" t="inlineStr">
         <is>
-          <t>166021.934602301</t>
+          <t>220000.00</t>
         </is>
       </c>
       <c r="S165" s="0" t="inlineStr">
@@ -7755,7 +7753,7 @@
       </c>
       <c r="T165" s="0" t="inlineStr">
         <is>
-          <t>195000.00</t>
+          <t>250000.00</t>
         </is>
       </c>
       <c r="Z165" s="0" t="inlineStr">
@@ -7764,18 +7762,18 @@
         </is>
       </c>
       <c r="AA165" s="0">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="AV165" s="0" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
     </row>
     <row r="166" spans="1:48">
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>SUPER WAX EMBELLISHED 4YRDS</t>
+          <t>SUPER HOLLAND WAX</t>
         </is>
       </c>
       <c r="G166" s="0" t="inlineStr">
@@ -7790,7 +7788,7 @@
       </c>
       <c r="R166" s="0" t="inlineStr">
         <is>
-          <t>100000.00</t>
+          <t>166021.934602301</t>
         </is>
       </c>
       <c r="S166" s="0" t="inlineStr">
@@ -7800,7 +7798,7 @@
       </c>
       <c r="T166" s="0" t="inlineStr">
         <is>
-          <t>120000.00</t>
+          <t>195000.00</t>
         </is>
       </c>
       <c r="Z166" s="0" t="inlineStr">
@@ -7809,18 +7807,18 @@
         </is>
       </c>
       <c r="AA166" s="0">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="AV166" s="0" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="167" spans="1:48">
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t>SUPER WAX MEDIUM</t>
+          <t>SUPER WAX EMBELLISHED 4YRDS</t>
         </is>
       </c>
       <c r="G167" s="0" t="inlineStr">
@@ -7835,7 +7833,7 @@
       </c>
       <c r="R167" s="0" t="inlineStr">
         <is>
-          <t>14500.00</t>
+          <t>100000.00</t>
         </is>
       </c>
       <c r="S167" s="0" t="inlineStr">
@@ -7845,7 +7843,7 @@
       </c>
       <c r="T167" s="0" t="inlineStr">
         <is>
-          <t>16000.00</t>
+          <t>120000.00</t>
         </is>
       </c>
       <c r="Z167" s="0" t="inlineStr">
@@ -7854,23 +7852,23 @@
         </is>
       </c>
       <c r="AA167" s="0">
-        <v>257</v>
+        <v>3</v>
       </c>
       <c r="AV167" s="0" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="168" spans="1:48">
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>SUPREME PHANTOM</t>
+          <t>SUPER WAX MEDIUM</t>
         </is>
       </c>
       <c r="G168" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O168" s="0" t="inlineStr">
@@ -7880,7 +7878,7 @@
       </c>
       <c r="R168" s="0" t="inlineStr">
         <is>
-          <t>5500.00</t>
+          <t>14500.00</t>
         </is>
       </c>
       <c r="S168" s="0" t="inlineStr">
@@ -7890,7 +7888,7 @@
       </c>
       <c r="T168" s="0" t="inlineStr">
         <is>
-          <t>7500.00</t>
+          <t>16000.00</t>
         </is>
       </c>
       <c r="Z168" s="0" t="inlineStr">
@@ -7899,23 +7897,23 @@
         </is>
       </c>
       <c r="AA168" s="0">
-        <v>51</v>
+        <v>223</v>
       </c>
       <c r="AV168" s="0" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>119</t>
         </is>
       </c>
     </row>
     <row r="169" spans="1:48">
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t>SWISS LACE A</t>
+          <t>SUPREME PHANTOM</t>
         </is>
       </c>
       <c r="G169" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O169" s="0" t="inlineStr">
@@ -7925,7 +7923,7 @@
       </c>
       <c r="R169" s="0" t="inlineStr">
         <is>
-          <t>85078.125</t>
+          <t>5500.00</t>
         </is>
       </c>
       <c r="S169" s="0" t="inlineStr">
@@ -7935,7 +7933,7 @@
       </c>
       <c r="T169" s="0" t="inlineStr">
         <is>
-          <t>100000.00</t>
+          <t>7500.00</t>
         </is>
       </c>
       <c r="Z169" s="0" t="inlineStr">
@@ -7944,18 +7942,18 @@
         </is>
       </c>
       <c r="AA169" s="0">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="AV169" s="0" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>176</t>
         </is>
       </c>
     </row>
     <row r="170" spans="1:48">
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t>SWISS LACE B</t>
+          <t>SWISS LACE A</t>
         </is>
       </c>
       <c r="G170" s="0" t="inlineStr">
@@ -7970,7 +7968,7 @@
       </c>
       <c r="R170" s="0" t="inlineStr">
         <is>
-          <t>74273.9898989899</t>
+          <t>85078.125</t>
         </is>
       </c>
       <c r="S170" s="0" t="inlineStr">
@@ -7980,7 +7978,7 @@
       </c>
       <c r="T170" s="0" t="inlineStr">
         <is>
-          <t>85000.00</t>
+          <t>100000.00</t>
         </is>
       </c>
       <c r="Z170" s="0" t="inlineStr">
@@ -7989,11 +7987,11 @@
         </is>
       </c>
       <c r="AA170" s="0">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AV170" s="0" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8013,7 @@
       </c>
       <c r="R171" s="0" t="inlineStr">
         <is>
-          <t>75391.3043478261</t>
+          <t>74273.9898989899</t>
         </is>
       </c>
       <c r="S171" s="0" t="inlineStr">
@@ -8034,18 +8032,18 @@
         </is>
       </c>
       <c r="AA171" s="0">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV171" s="0" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="172" spans="1:48">
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>SWISS LACE C</t>
+          <t>SWISS LACE B</t>
         </is>
       </c>
       <c r="G172" s="0" t="inlineStr">
@@ -8060,7 +8058,7 @@
       </c>
       <c r="R172" s="0" t="inlineStr">
         <is>
-          <t>67000.00</t>
+          <t>75391.3043478261</t>
         </is>
       </c>
       <c r="S172" s="0" t="inlineStr">
@@ -8070,7 +8068,7 @@
       </c>
       <c r="T172" s="0" t="inlineStr">
         <is>
-          <t>75000.00</t>
+          <t>85000.00</t>
         </is>
       </c>
       <c r="Z172" s="0" t="inlineStr">
@@ -8079,18 +8077,18 @@
         </is>
       </c>
       <c r="AA172" s="0">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AV172" s="0" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>161</t>
         </is>
       </c>
     </row>
     <row r="173" spans="1:48">
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>SWISS LACE D</t>
+          <t>SWISS LACE C</t>
         </is>
       </c>
       <c r="G173" s="0" t="inlineStr">
@@ -8105,7 +8103,7 @@
       </c>
       <c r="R173" s="0" t="inlineStr">
         <is>
-          <t>53000.00</t>
+          <t>67000.00</t>
         </is>
       </c>
       <c r="S173" s="0" t="inlineStr">
@@ -8115,7 +8113,7 @@
       </c>
       <c r="T173" s="0" t="inlineStr">
         <is>
-          <t>65000.00</t>
+          <t>75000.00</t>
         </is>
       </c>
       <c r="Z173" s="0" t="inlineStr">
@@ -8124,23 +8122,23 @@
         </is>
       </c>
       <c r="AA173" s="0">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AV173" s="0" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="174" spans="1:48">
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>SWISS LAFAYA A</t>
+          <t>SWISS LACE D</t>
         </is>
       </c>
       <c r="G174" s="0" t="inlineStr">
         <is>
-          <t>LAFAYYA</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O174" s="0" t="inlineStr">
@@ -8150,7 +8148,7 @@
       </c>
       <c r="R174" s="0" t="inlineStr">
         <is>
-          <t>45000.00</t>
+          <t>53000.00</t>
         </is>
       </c>
       <c r="S174" s="0" t="inlineStr">
@@ -8160,7 +8158,7 @@
       </c>
       <c r="T174" s="0" t="inlineStr">
         <is>
-          <t>60000.00</t>
+          <t>65000.00</t>
         </is>
       </c>
       <c r="Z174" s="0" t="inlineStr">
@@ -8169,18 +8167,18 @@
         </is>
       </c>
       <c r="AA174" s="0">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="AV174" s="0" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="175" spans="1:48">
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t>SWISS LAFAYA B</t>
+          <t>SWISS LAFAYA A</t>
         </is>
       </c>
       <c r="G175" s="0" t="inlineStr">
@@ -8195,7 +8193,7 @@
       </c>
       <c r="R175" s="0" t="inlineStr">
         <is>
-          <t>48000.00</t>
+          <t>45000.00</t>
         </is>
       </c>
       <c r="S175" s="0" t="inlineStr">
@@ -8205,7 +8203,7 @@
       </c>
       <c r="T175" s="0" t="inlineStr">
         <is>
-          <t>55000.00</t>
+          <t>60000.00</t>
         </is>
       </c>
       <c r="Z175" s="0" t="inlineStr">
@@ -8214,18 +8212,18 @@
         </is>
       </c>
       <c r="AA175" s="0">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="AV175" s="0" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="176" spans="1:48">
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t>SWISS LAFAYA C</t>
+          <t>SWISS LAFAYA B</t>
         </is>
       </c>
       <c r="G176" s="0" t="inlineStr">
@@ -8240,7 +8238,7 @@
       </c>
       <c r="R176" s="0" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>48000.00</t>
         </is>
       </c>
       <c r="S176" s="0" t="inlineStr">
@@ -8250,7 +8248,7 @@
       </c>
       <c r="T176" s="0" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>55000.00</t>
         </is>
       </c>
       <c r="Z176" s="0" t="inlineStr">
@@ -8258,9 +8256,12 @@
           <t>n</t>
         </is>
       </c>
+      <c r="AA176" s="0">
+        <v>29</v>
+      </c>
       <c r="AV176" s="0" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -8282,7 +8283,7 @@
       </c>
       <c r="R177" s="0" t="inlineStr">
         <is>
-          <t>36000.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S177" s="0" t="inlineStr">
@@ -8292,7 +8293,7 @@
       </c>
       <c r="T177" s="0" t="inlineStr">
         <is>
-          <t>45000.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Z177" s="0" t="inlineStr">
@@ -8300,24 +8301,21 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA177" s="0">
-        <v>3</v>
-      </c>
       <c r="AV177" s="0" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="178" spans="1:48">
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY LACE A</t>
+          <t>SWISS LAFAYA C</t>
         </is>
       </c>
       <c r="G178" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>LAFAYYA</t>
         </is>
       </c>
       <c r="O178" s="0" t="inlineStr">
@@ -8327,7 +8325,7 @@
       </c>
       <c r="R178" s="0" t="inlineStr">
         <is>
-          <t>120000.00</t>
+          <t>36000.00</t>
         </is>
       </c>
       <c r="S178" s="0" t="inlineStr">
@@ -8337,7 +8335,7 @@
       </c>
       <c r="T178" s="0" t="inlineStr">
         <is>
-          <t>135000.00</t>
+          <t>45000.00</t>
         </is>
       </c>
       <c r="Z178" s="0" t="inlineStr">
@@ -8346,18 +8344,18 @@
         </is>
       </c>
       <c r="AA178" s="0">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="AV178" s="0" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="179" spans="1:48">
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t>Swiss luxury lace Aplus</t>
+          <t>SWISS LUXURY LACE A</t>
         </is>
       </c>
       <c r="G179" s="0" t="inlineStr">
@@ -8365,11 +8363,6 @@
           <t>LACE</t>
         </is>
       </c>
-      <c r="H179" s="0" t="inlineStr">
-        <is>
-          <t>FAHAD TAHIR</t>
-        </is>
-      </c>
       <c r="O179" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -8377,7 +8370,7 @@
       </c>
       <c r="R179" s="0" t="inlineStr">
         <is>
-          <t>130000.00</t>
+          <t>120000.00</t>
         </is>
       </c>
       <c r="S179" s="0" t="inlineStr">
@@ -8387,7 +8380,7 @@
       </c>
       <c r="T179" s="0" t="inlineStr">
         <is>
-          <t>165000.00</t>
+          <t>135000.00</t>
         </is>
       </c>
       <c r="Z179" s="0" t="inlineStr">
@@ -8396,18 +8389,18 @@
         </is>
       </c>
       <c r="AA179" s="0">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AV179" s="0" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="180" spans="1:48">
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY LACE B</t>
+          <t>Swiss luxury lace Aplus</t>
         </is>
       </c>
       <c r="G180" s="0" t="inlineStr">
@@ -8415,6 +8408,11 @@
           <t>LACE</t>
         </is>
       </c>
+      <c r="H180" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
+        </is>
+      </c>
       <c r="O180" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -8422,7 +8420,7 @@
       </c>
       <c r="R180" s="0" t="inlineStr">
         <is>
-          <t>117202.7972027972</t>
+          <t>130000.00</t>
         </is>
       </c>
       <c r="S180" s="0" t="inlineStr">
@@ -8432,7 +8430,7 @@
       </c>
       <c r="T180" s="0" t="inlineStr">
         <is>
-          <t>130000.00</t>
+          <t>165000.00</t>
         </is>
       </c>
       <c r="Z180" s="0" t="inlineStr">
@@ -8441,18 +8439,18 @@
         </is>
       </c>
       <c r="AA180" s="0">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AV180" s="0" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>198</t>
         </is>
       </c>
     </row>
     <row r="181" spans="1:48">
       <c r="C181" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY LACE BIG A</t>
+          <t>SWISS LUXURY LACE B</t>
         </is>
       </c>
       <c r="G181" s="0" t="inlineStr">
@@ -8467,7 +8465,7 @@
       </c>
       <c r="R181" s="0" t="inlineStr">
         <is>
-          <t>220000.00</t>
+          <t>117202.7972027972</t>
         </is>
       </c>
       <c r="S181" s="0" t="inlineStr">
@@ -8477,7 +8475,7 @@
       </c>
       <c r="T181" s="0" t="inlineStr">
         <is>
-          <t>270000.00</t>
+          <t>130000.00</t>
         </is>
       </c>
       <c r="Z181" s="0" t="inlineStr">
@@ -8486,18 +8484,18 @@
         </is>
       </c>
       <c r="AA181" s="0">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AV181" s="0" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="182" spans="1:48">
       <c r="C182" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY LACE BIG B</t>
+          <t>SWISS LUXURY LACE BIG A</t>
         </is>
       </c>
       <c r="G182" s="0" t="inlineStr">
@@ -8512,7 +8510,7 @@
       </c>
       <c r="R182" s="0" t="inlineStr">
         <is>
-          <t>200000.00</t>
+          <t>220000.00</t>
         </is>
       </c>
       <c r="S182" s="0" t="inlineStr">
@@ -8522,7 +8520,7 @@
       </c>
       <c r="T182" s="0" t="inlineStr">
         <is>
-          <t>250000.00</t>
+          <t>270000.00</t>
         </is>
       </c>
       <c r="Z182" s="0" t="inlineStr">
@@ -8531,18 +8529,18 @@
         </is>
       </c>
       <c r="AA182" s="0">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV182" s="0" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="183" spans="1:48">
       <c r="C183" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY LACE BIG C</t>
+          <t>SWISS LUXURY LACE BIG B</t>
         </is>
       </c>
       <c r="G183" s="0" t="inlineStr">
@@ -8557,7 +8555,7 @@
       </c>
       <c r="R183" s="0" t="inlineStr">
         <is>
-          <t>180000.00</t>
+          <t>200000.00</t>
         </is>
       </c>
       <c r="S183" s="0" t="inlineStr">
@@ -8567,7 +8565,7 @@
       </c>
       <c r="T183" s="0" t="inlineStr">
         <is>
-          <t>230000.00</t>
+          <t>250000.00</t>
         </is>
       </c>
       <c r="Z183" s="0" t="inlineStr">
@@ -8576,18 +8574,18 @@
         </is>
       </c>
       <c r="AA183" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV183" s="0" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="184" spans="1:48">
       <c r="C184" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY LACE BIG D </t>
+          <t>SWISS LUXURY LACE BIG C</t>
         </is>
       </c>
       <c r="G184" s="0" t="inlineStr">
@@ -8602,7 +8600,7 @@
       </c>
       <c r="R184" s="0" t="inlineStr">
         <is>
-          <t>123750.00</t>
+          <t>180000.00</t>
         </is>
       </c>
       <c r="S184" s="0" t="inlineStr">
@@ -8612,7 +8610,7 @@
       </c>
       <c r="T184" s="0" t="inlineStr">
         <is>
-          <t>200000.00</t>
+          <t>230000.00</t>
         </is>
       </c>
       <c r="Z184" s="0" t="inlineStr">
@@ -8621,18 +8619,18 @@
         </is>
       </c>
       <c r="AA184" s="0">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AV184" s="0" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="185" spans="1:48">
       <c r="C185" s="0" t="inlineStr">
         <is>
-          <t>Swiss luxury lace Bplus</t>
+          <t>SWISS LUXURY LACE BIG D </t>
         </is>
       </c>
       <c r="G185" s="0" t="inlineStr">
@@ -8640,11 +8638,6 @@
           <t>LACE</t>
         </is>
       </c>
-      <c r="H185" s="0" t="inlineStr">
-        <is>
-          <t>FAHAD TAHIR</t>
-        </is>
-      </c>
       <c r="O185" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -8652,7 +8645,7 @@
       </c>
       <c r="R185" s="0" t="inlineStr">
         <is>
-          <t>120000.00</t>
+          <t>123750.00</t>
         </is>
       </c>
       <c r="S185" s="0" t="inlineStr">
@@ -8662,7 +8655,7 @@
       </c>
       <c r="T185" s="0" t="inlineStr">
         <is>
-          <t>140000.00</t>
+          <t>200000.00</t>
         </is>
       </c>
       <c r="Z185" s="0" t="inlineStr">
@@ -8671,18 +8664,18 @@
         </is>
       </c>
       <c r="AA185" s="0">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AV185" s="0" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="186" spans="1:48">
       <c r="C186" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY LACE C</t>
+          <t>Swiss luxury lace Bplus</t>
         </is>
       </c>
       <c r="G186" s="0" t="inlineStr">
@@ -8690,6 +8683,11 @@
           <t>LACE</t>
         </is>
       </c>
+      <c r="H186" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
+        </is>
+      </c>
       <c r="O186" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -8697,7 +8695,7 @@
       </c>
       <c r="R186" s="0" t="inlineStr">
         <is>
-          <t>106000.00</t>
+          <t>120000.00</t>
         </is>
       </c>
       <c r="S186" s="0" t="inlineStr">
@@ -8707,7 +8705,7 @@
       </c>
       <c r="T186" s="0" t="inlineStr">
         <is>
-          <t>120000.00</t>
+          <t>140000.00</t>
         </is>
       </c>
       <c r="Z186" s="0" t="inlineStr">
@@ -8716,18 +8714,18 @@
         </is>
       </c>
       <c r="AA186" s="0">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AV186" s="0" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="187" spans="1:48">
       <c r="C187" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY LACE D</t>
+          <t>SWISS LUXURY LACE C</t>
         </is>
       </c>
       <c r="G187" s="0" t="inlineStr">
@@ -8742,7 +8740,7 @@
       </c>
       <c r="R187" s="0" t="inlineStr">
         <is>
-          <t>98164.3888673712</t>
+          <t>106000.00</t>
         </is>
       </c>
       <c r="S187" s="0" t="inlineStr">
@@ -8752,7 +8750,7 @@
       </c>
       <c r="T187" s="0" t="inlineStr">
         <is>
-          <t>110000.00</t>
+          <t>120000.00</t>
         </is>
       </c>
       <c r="Z187" s="0" t="inlineStr">
@@ -8761,23 +8759,23 @@
         </is>
       </c>
       <c r="AA187" s="0">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="AV187" s="0" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="188" spans="1:48">
       <c r="C188" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY VOILE</t>
+          <t>SWISS LUXURY LACE D</t>
         </is>
       </c>
       <c r="G188" s="0" t="inlineStr">
         <is>
-          <t>VOILE</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O188" s="0" t="inlineStr">
@@ -8787,7 +8785,7 @@
       </c>
       <c r="R188" s="0" t="inlineStr">
         <is>
-          <t>48656.00</t>
+          <t>98164.3888673712</t>
         </is>
       </c>
       <c r="S188" s="0" t="inlineStr">
@@ -8797,7 +8795,7 @@
       </c>
       <c r="T188" s="0" t="inlineStr">
         <is>
-          <t>65000.00</t>
+          <t>110000.00</t>
         </is>
       </c>
       <c r="Z188" s="0" t="inlineStr">
@@ -8806,23 +8804,23 @@
         </is>
       </c>
       <c r="AA188" s="0">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="AV188" s="0" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="189" spans="1:48">
       <c r="C189" s="0" t="inlineStr">
         <is>
-          <t>SWISS VOILE LACE A</t>
+          <t>SWISS LUXURY VOILE</t>
         </is>
       </c>
       <c r="G189" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>VOILE</t>
         </is>
       </c>
       <c r="O189" s="0" t="inlineStr">
@@ -8832,7 +8830,7 @@
       </c>
       <c r="R189" s="0" t="inlineStr">
         <is>
-          <t>150000.00</t>
+          <t>48656.00</t>
         </is>
       </c>
       <c r="S189" s="0" t="inlineStr">
@@ -8842,7 +8840,7 @@
       </c>
       <c r="T189" s="0" t="inlineStr">
         <is>
-          <t>280000.00</t>
+          <t>65000.00</t>
         </is>
       </c>
       <c r="Z189" s="0" t="inlineStr">
@@ -8851,18 +8849,18 @@
         </is>
       </c>
       <c r="AA189" s="0">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="AV189" s="0" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="190" spans="1:48">
       <c r="C190" s="0" t="inlineStr">
         <is>
-          <t>SWISS VOILE LACE B</t>
+          <t>SWISS VOILE LACE A</t>
         </is>
       </c>
       <c r="G190" s="0" t="inlineStr">
@@ -8877,7 +8875,7 @@
       </c>
       <c r="R190" s="0" t="inlineStr">
         <is>
-          <t>135000.00</t>
+          <t>150000.00</t>
         </is>
       </c>
       <c r="S190" s="0" t="inlineStr">
@@ -8887,7 +8885,7 @@
       </c>
       <c r="T190" s="0" t="inlineStr">
         <is>
-          <t>180000.00</t>
+          <t>280000.00</t>
         </is>
       </c>
       <c r="Z190" s="0" t="inlineStr">
@@ -8896,23 +8894,23 @@
         </is>
       </c>
       <c r="AA190" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV190" s="0" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="191" spans="1:48">
       <c r="C191" s="0" t="inlineStr">
         <is>
-          <t>TYCOON AND GAZA WOOL</t>
+          <t>SWISS VOILE LACE B</t>
         </is>
       </c>
       <c r="G191" s="0" t="inlineStr">
         <is>
-          <t>YARD</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O191" s="0" t="inlineStr">
@@ -8922,7 +8920,7 @@
       </c>
       <c r="R191" s="0" t="inlineStr">
         <is>
-          <t>4000.00</t>
+          <t>135000.00</t>
         </is>
       </c>
       <c r="S191" s="0" t="inlineStr">
@@ -8932,7 +8930,7 @@
       </c>
       <c r="T191" s="0" t="inlineStr">
         <is>
-          <t>5000.00</t>
+          <t>180000.00</t>
         </is>
       </c>
       <c r="Z191" s="0" t="inlineStr">
@@ -8940,26 +8938,24 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA191" s="0" t="inlineStr">
-        <is>
-          <t>648.5</t>
-        </is>
+      <c r="AA191" s="0">
+        <v>4</v>
       </c>
       <c r="AV191" s="0" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="192" spans="1:48">
       <c r="C192" s="0" t="inlineStr">
         <is>
-          <t>ULTRA SWISS LACE A</t>
+          <t>TYCOON AND GAZA WOOL</t>
         </is>
       </c>
       <c r="G192" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>YARD</t>
         </is>
       </c>
       <c r="O192" s="0" t="inlineStr">
@@ -8969,7 +8965,7 @@
       </c>
       <c r="R192" s="0" t="inlineStr">
         <is>
-          <t>300000.00</t>
+          <t>4000.00</t>
         </is>
       </c>
       <c r="S192" s="0" t="inlineStr">
@@ -8979,7 +8975,7 @@
       </c>
       <c r="T192" s="0" t="inlineStr">
         <is>
-          <t>380000.00</t>
+          <t>5000.00</t>
         </is>
       </c>
       <c r="Z192" s="0" t="inlineStr">
@@ -8988,18 +8984,18 @@
         </is>
       </c>
       <c r="AA192" s="0">
-        <v>0</v>
+        <v>635</v>
       </c>
       <c r="AV192" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>187</t>
         </is>
       </c>
     </row>
     <row r="193" spans="1:48">
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t>ULTRA SWISS LACE B</t>
+          <t>ULTRA SWISS LACE A</t>
         </is>
       </c>
       <c r="G193" s="0" t="inlineStr">
@@ -9014,7 +9010,7 @@
       </c>
       <c r="R193" s="0" t="inlineStr">
         <is>
-          <t>250000.00</t>
+          <t>300000.00</t>
         </is>
       </c>
       <c r="S193" s="0" t="inlineStr">
@@ -9024,7 +9020,7 @@
       </c>
       <c r="T193" s="0" t="inlineStr">
         <is>
-          <t>350000.00</t>
+          <t>380000.00</t>
         </is>
       </c>
       <c r="Z193" s="0" t="inlineStr">
@@ -9033,18 +9029,18 @@
         </is>
       </c>
       <c r="AA193" s="0">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AV193" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="194" spans="1:48">
       <c r="C194" s="0" t="inlineStr">
         <is>
-          <t>ULTRA SWISS LACE C</t>
+          <t>ULTRA SWISS LACE B</t>
         </is>
       </c>
       <c r="G194" s="0" t="inlineStr">
@@ -9059,7 +9055,7 @@
       </c>
       <c r="R194" s="0" t="inlineStr">
         <is>
-          <t>253214.2857142857</t>
+          <t>250000.00</t>
         </is>
       </c>
       <c r="S194" s="0" t="inlineStr">
@@ -9069,7 +9065,7 @@
       </c>
       <c r="T194" s="0" t="inlineStr">
         <is>
-          <t>320000.00</t>
+          <t>350000.00</t>
         </is>
       </c>
       <c r="Z194" s="0" t="inlineStr">
@@ -9078,18 +9074,18 @@
         </is>
       </c>
       <c r="AA194" s="0">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AV194" s="0" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="195" spans="1:48">
       <c r="C195" s="0" t="inlineStr">
         <is>
-          <t>ULTRA SWISS LACE D</t>
+          <t>ULTRA SWISS LACE C</t>
         </is>
       </c>
       <c r="G195" s="0" t="inlineStr">
@@ -9104,7 +9100,7 @@
       </c>
       <c r="R195" s="0" t="inlineStr">
         <is>
-          <t>230000.00</t>
+          <t>253214.2857142857</t>
         </is>
       </c>
       <c r="S195" s="0" t="inlineStr">
@@ -9114,7 +9110,7 @@
       </c>
       <c r="T195" s="0" t="inlineStr">
         <is>
-          <t>300000.00</t>
+          <t>320000.00</t>
         </is>
       </c>
       <c r="Z195" s="0" t="inlineStr">
@@ -9123,23 +9119,23 @@
         </is>
       </c>
       <c r="AA195" s="0">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="AV195" s="0" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="196" spans="1:48">
       <c r="C196" s="0" t="inlineStr">
         <is>
-          <t>VALANTINO</t>
+          <t>ULTRA SWISS LACE D</t>
         </is>
       </c>
       <c r="G196" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O196" s="0" t="inlineStr">
@@ -9149,7 +9145,7 @@
       </c>
       <c r="R196" s="0" t="inlineStr">
         <is>
-          <t>10070.8693671806</t>
+          <t>230000.00</t>
         </is>
       </c>
       <c r="S196" s="0" t="inlineStr">
@@ -9159,7 +9155,7 @@
       </c>
       <c r="T196" s="0" t="inlineStr">
         <is>
-          <t>11000.00</t>
+          <t>300000.00</t>
         </is>
       </c>
       <c r="Z196" s="0" t="inlineStr">
@@ -9168,18 +9164,18 @@
         </is>
       </c>
       <c r="AA196" s="0">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="AV196" s="0" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="197" spans="1:48">
       <c r="C197" s="0" t="inlineStr">
         <is>
-          <t>VALANTINO HOLLAND</t>
+          <t>VALANTINO</t>
         </is>
       </c>
       <c r="G197" s="0" t="inlineStr">
@@ -9194,7 +9190,7 @@
       </c>
       <c r="R197" s="0" t="inlineStr">
         <is>
-          <t>10500.00</t>
+          <t>10070.8693671806</t>
         </is>
       </c>
       <c r="S197" s="0" t="inlineStr">
@@ -9213,18 +9209,18 @@
         </is>
       </c>
       <c r="AA197" s="0">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AV197" s="0" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>135</t>
         </is>
       </c>
     </row>
     <row r="198" spans="1:48">
       <c r="C198" s="0" t="inlineStr">
         <is>
-          <t>Vibes Metallic Cotton Satin</t>
+          <t>VALANTINO HOLLAND</t>
         </is>
       </c>
       <c r="G198" s="0" t="inlineStr">
@@ -9232,11 +9228,6 @@
           <t>ATAMPA</t>
         </is>
       </c>
-      <c r="H198" s="0" t="inlineStr">
-        <is>
-          <t>FAHAD TAHIR</t>
-        </is>
-      </c>
       <c r="O198" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -9244,7 +9235,7 @@
       </c>
       <c r="R198" s="0" t="inlineStr">
         <is>
-          <t>29000.00</t>
+          <t>10500.00</t>
         </is>
       </c>
       <c r="S198" s="0" t="inlineStr">
@@ -9254,7 +9245,7 @@
       </c>
       <c r="T198" s="0" t="inlineStr">
         <is>
-          <t>35000.00</t>
+          <t>11000.00</t>
         </is>
       </c>
       <c r="Z198" s="0" t="inlineStr">
@@ -9263,23 +9254,28 @@
         </is>
       </c>
       <c r="AA198" s="0">
-        <v>343</v>
+        <v>0</v>
       </c>
       <c r="AV198" s="0" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>157</t>
         </is>
       </c>
     </row>
     <row r="199" spans="1:48">
       <c r="C199" s="0" t="inlineStr">
         <is>
-          <t>VICE CHAIRMAN</t>
+          <t>Vibes Metallic Cotton Satin</t>
         </is>
       </c>
       <c r="G199" s="0" t="inlineStr">
         <is>
-          <t>YARD</t>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="H199" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
         </is>
       </c>
       <c r="O199" s="0" t="inlineStr">
@@ -9289,7 +9285,7 @@
       </c>
       <c r="R199" s="0" t="inlineStr">
         <is>
-          <t>8000.00</t>
+          <t>29000.00</t>
         </is>
       </c>
       <c r="S199" s="0" t="inlineStr">
@@ -9299,7 +9295,7 @@
       </c>
       <c r="T199" s="0" t="inlineStr">
         <is>
-          <t>12000.00</t>
+          <t>35000.00</t>
         </is>
       </c>
       <c r="Z199" s="0" t="inlineStr">
@@ -9308,23 +9304,23 @@
         </is>
       </c>
       <c r="AA199" s="0">
-        <v>140</v>
+        <v>342</v>
       </c>
       <c r="AV199" s="0" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>199</t>
         </is>
       </c>
     </row>
     <row r="200" spans="1:48">
       <c r="C200" s="0" t="inlineStr">
         <is>
-          <t>VICTOIRE MAGIC MEDIUM</t>
+          <t>VICE CHAIRMAN</t>
         </is>
       </c>
       <c r="G200" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>YARD</t>
         </is>
       </c>
       <c r="O200" s="0" t="inlineStr">
@@ -9334,7 +9330,7 @@
       </c>
       <c r="R200" s="0" t="inlineStr">
         <is>
-          <t>25000.00</t>
+          <t>8151.5151515152</t>
         </is>
       </c>
       <c r="S200" s="0" t="inlineStr">
@@ -9344,7 +9340,7 @@
       </c>
       <c r="T200" s="0" t="inlineStr">
         <is>
-          <t>30000.00</t>
+          <t>12000.00</t>
         </is>
       </c>
       <c r="Z200" s="0" t="inlineStr">
@@ -9353,23 +9349,23 @@
         </is>
       </c>
       <c r="AA200" s="0">
-        <v>52</v>
+        <v>122</v>
       </c>
       <c r="AV200" s="0" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>181</t>
         </is>
       </c>
     </row>
     <row r="201" spans="1:48">
       <c r="C201" s="0" t="inlineStr">
         <is>
-          <t>VICTOIRE MAGIC PRINCESS</t>
+          <t>VICTOIRE MAGIC MEDIUM</t>
         </is>
       </c>
       <c r="G201" s="0" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O201" s="0" t="inlineStr">
@@ -9379,7 +9375,7 @@
       </c>
       <c r="R201" s="0" t="inlineStr">
         <is>
-          <t>175000.00</t>
+          <t>25000.00</t>
         </is>
       </c>
       <c r="S201" s="0" t="inlineStr">
@@ -9389,7 +9385,7 @@
       </c>
       <c r="T201" s="0" t="inlineStr">
         <is>
-          <t>210000.00</t>
+          <t>30000.00</t>
         </is>
       </c>
       <c r="Z201" s="0" t="inlineStr">
@@ -9398,18 +9394,18 @@
         </is>
       </c>
       <c r="AA201" s="0">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="AV201" s="0" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>56</t>
         </is>
       </c>
     </row>
     <row r="202" spans="1:48">
       <c r="C202" s="0" t="inlineStr">
         <is>
-          <t>VICTORY BROCADE</t>
+          <t>VICTOIRE MAGIC PRINCESS</t>
         </is>
       </c>
       <c r="G202" s="0" t="inlineStr">
@@ -9424,7 +9420,7 @@
       </c>
       <c r="R202" s="0" t="inlineStr">
         <is>
-          <t>8000.00</t>
+          <t>175000.00</t>
         </is>
       </c>
       <c r="S202" s="0" t="inlineStr">
@@ -9434,7 +9430,7 @@
       </c>
       <c r="T202" s="0" t="inlineStr">
         <is>
-          <t>14000.00</t>
+          <t>210000.00</t>
         </is>
       </c>
       <c r="Z202" s="0" t="inlineStr">
@@ -9443,23 +9439,23 @@
         </is>
       </c>
       <c r="AA202" s="0">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AV202" s="0" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="203" spans="1:48">
       <c r="C203" s="0" t="inlineStr">
         <is>
-          <t>VIENNA YARD</t>
+          <t>VICTORY BROCADE</t>
         </is>
       </c>
       <c r="G203" s="0" t="inlineStr">
         <is>
-          <t>YARD</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="O203" s="0" t="inlineStr">
@@ -9469,7 +9465,7 @@
       </c>
       <c r="R203" s="0" t="inlineStr">
         <is>
-          <t>1500.00</t>
+          <t>8000.00</t>
         </is>
       </c>
       <c r="S203" s="0" t="inlineStr">
@@ -9479,7 +9475,7 @@
       </c>
       <c r="T203" s="0" t="inlineStr">
         <is>
-          <t>2500.00</t>
+          <t>14000.00</t>
         </is>
       </c>
       <c r="Z203" s="0" t="inlineStr">
@@ -9487,26 +9483,24 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA203" s="0" t="inlineStr">
-        <is>
-          <t>313.5</t>
-        </is>
+      <c r="AA203" s="0">
+        <v>120</v>
       </c>
       <c r="AV203" s="0" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>53</t>
         </is>
       </c>
     </row>
     <row r="204" spans="1:48">
       <c r="C204" s="0" t="inlineStr">
         <is>
-          <t>VLISCO LACE MIX AND MATCH</t>
+          <t>VIENNA YARD</t>
         </is>
       </c>
       <c r="G204" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>YARD</t>
         </is>
       </c>
       <c r="O204" s="0" t="inlineStr">
@@ -9516,7 +9510,7 @@
       </c>
       <c r="R204" s="0" t="inlineStr">
         <is>
-          <t>370000.00</t>
+          <t>1500.00</t>
         </is>
       </c>
       <c r="S204" s="0" t="inlineStr">
@@ -9526,7 +9520,7 @@
       </c>
       <c r="T204" s="0" t="inlineStr">
         <is>
-          <t>420000.00</t>
+          <t>2500.00</t>
         </is>
       </c>
       <c r="Z204" s="0" t="inlineStr">
@@ -9534,24 +9528,26 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA204" s="0">
-        <v>2</v>
+      <c r="AA204" s="0" t="inlineStr">
+        <is>
+          <t>313.5</t>
+        </is>
       </c>
       <c r="AV204" s="0" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>191</t>
         </is>
       </c>
     </row>
     <row r="205" spans="1:48">
       <c r="C205" s="0" t="inlineStr">
         <is>
-          <t>VOILE EMBROIDERY MIX AND MATCH</t>
+          <t>VLISCO LACE MIX AND MATCH</t>
         </is>
       </c>
       <c r="G205" s="0" t="inlineStr">
         <is>
-          <t>VOILE</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O205" s="0" t="inlineStr">
@@ -9561,7 +9557,7 @@
       </c>
       <c r="R205" s="0" t="inlineStr">
         <is>
-          <t>33229.5081967213</t>
+          <t>370000.00</t>
         </is>
       </c>
       <c r="S205" s="0" t="inlineStr">
@@ -9571,7 +9567,7 @@
       </c>
       <c r="T205" s="0" t="inlineStr">
         <is>
-          <t>40000.00</t>
+          <t>420000.00</t>
         </is>
       </c>
       <c r="Z205" s="0" t="inlineStr">
@@ -9580,18 +9576,18 @@
         </is>
       </c>
       <c r="AA205" s="0">
-        <v>111</v>
+        <v>2</v>
       </c>
       <c r="AV205" s="0" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="206" spans="1:48">
       <c r="C206" s="0" t="inlineStr">
         <is>
-          <t>VOILE MATERIAL </t>
+          <t>VOILE EMBROIDERY MIX AND MATCH</t>
         </is>
       </c>
       <c r="G206" s="0" t="inlineStr">
@@ -9606,7 +9602,7 @@
       </c>
       <c r="R206" s="0" t="inlineStr">
         <is>
-          <t>27000.00</t>
+          <t>33229.5081967213</t>
         </is>
       </c>
       <c r="S206" s="0" t="inlineStr">
@@ -9616,7 +9612,7 @@
       </c>
       <c r="T206" s="0" t="inlineStr">
         <is>
-          <t>32000.00</t>
+          <t>40000.00</t>
         </is>
       </c>
       <c r="Z206" s="0" t="inlineStr">
@@ -9625,23 +9621,23 @@
         </is>
       </c>
       <c r="AA206" s="0">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="AV206" s="0" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="207" spans="1:48">
       <c r="C207" s="0" t="inlineStr">
         <is>
-          <t>WAGAMBARI PLUS SHADDA</t>
+          <t>VOILE MATERIAL </t>
         </is>
       </c>
       <c r="G207" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>VOILE</t>
         </is>
       </c>
       <c r="O207" s="0" t="inlineStr">
@@ -9651,7 +9647,7 @@
       </c>
       <c r="R207" s="0" t="inlineStr">
         <is>
-          <t>35000.00</t>
+          <t>27000.00</t>
         </is>
       </c>
       <c r="S207" s="0" t="inlineStr">
@@ -9661,7 +9657,7 @@
       </c>
       <c r="T207" s="0" t="inlineStr">
         <is>
-          <t>45000.00</t>
+          <t>32000.00</t>
         </is>
       </c>
       <c r="Z207" s="0" t="inlineStr">
@@ -9670,28 +9666,23 @@
         </is>
       </c>
       <c r="AA207" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV207" s="0" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="208" spans="1:48">
       <c r="C208" s="0" t="inlineStr">
         <is>
-          <t>Win wax Holland</t>
+          <t>WAGAMBARI PLUS SHADDA</t>
         </is>
       </c>
       <c r="G208" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
-        </is>
-      </c>
-      <c r="H208" s="0" t="inlineStr">
-        <is>
-          <t>FAHAD TAHIR</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O208" s="0" t="inlineStr">
@@ -9701,7 +9692,7 @@
       </c>
       <c r="R208" s="0" t="inlineStr">
         <is>
-          <t>12000.00</t>
+          <t>35000.00</t>
         </is>
       </c>
       <c r="S208" s="0" t="inlineStr">
@@ -9711,7 +9702,7 @@
       </c>
       <c r="T208" s="0" t="inlineStr">
         <is>
-          <t>13000.00</t>
+          <t>45000.00</t>
         </is>
       </c>
       <c r="Z208" s="0" t="inlineStr">
@@ -9720,18 +9711,18 @@
         </is>
       </c>
       <c r="AA208" s="0">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="AV208" s="0" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>193</t>
         </is>
       </c>
     </row>
     <row r="209" spans="1:48">
       <c r="C209" s="0" t="inlineStr">
         <is>
-          <t>WOODIN LE CREATURE</t>
+          <t>Win wax Holland</t>
         </is>
       </c>
       <c r="G209" s="0" t="inlineStr">
@@ -9739,6 +9730,11 @@
           <t>ATAMPA</t>
         </is>
       </c>
+      <c r="H209" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
+        </is>
+      </c>
       <c r="O209" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -9746,7 +9742,7 @@
       </c>
       <c r="R209" s="0" t="inlineStr">
         <is>
-          <t>13500.00</t>
+          <t>12000.00</t>
         </is>
       </c>
       <c r="S209" s="0" t="inlineStr">
@@ -9756,7 +9752,7 @@
       </c>
       <c r="T209" s="0" t="inlineStr">
         <is>
-          <t>15000.00</t>
+          <t>13000.00</t>
         </is>
       </c>
       <c r="Z209" s="0" t="inlineStr">
@@ -9765,18 +9761,18 @@
         </is>
       </c>
       <c r="AA209" s="0">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="AV209" s="0" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>211</t>
         </is>
       </c>
     </row>
     <row r="210" spans="1:48">
       <c r="C210" s="0" t="inlineStr">
         <is>
-          <t>ZAHRA BATIK</t>
+          <t>WOODIN LE CREATURE</t>
         </is>
       </c>
       <c r="G210" s="0" t="inlineStr">
@@ -9791,7 +9787,7 @@
       </c>
       <c r="R210" s="0" t="inlineStr">
         <is>
-          <t>25000.00</t>
+          <t>13500.00</t>
         </is>
       </c>
       <c r="S210" s="0" t="inlineStr">
@@ -9801,7 +9797,7 @@
       </c>
       <c r="T210" s="0" t="inlineStr">
         <is>
-          <t>26000.00</t>
+          <t>15000.00</t>
         </is>
       </c>
       <c r="Z210" s="0" t="inlineStr">
@@ -9810,54 +9806,99 @@
         </is>
       </c>
       <c r="AA210" s="0">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AV210" s="0" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>121</t>
         </is>
       </c>
     </row>
     <row r="211" spans="1:48">
       <c r="C211" s="0" t="inlineStr">
         <is>
+          <t>ZAHRA BATIK</t>
+        </is>
+      </c>
+      <c r="G211" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="O211" s="0" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R211" s="0" t="inlineStr">
+        <is>
+          <t>25000.00</t>
+        </is>
+      </c>
+      <c r="S211" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="T211" s="0" t="inlineStr">
+        <is>
+          <t>26000.00</t>
+        </is>
+      </c>
+      <c r="Z211" s="0" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="AA211" s="0">
+        <v>43</v>
+      </c>
+      <c r="AV211" s="0" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" spans="1:48">
+      <c r="C212" s="0" t="inlineStr">
+        <is>
           <t>ZAZMA METTALIC </t>
         </is>
       </c>
-      <c r="G211" s="0" t="inlineStr">
-        <is>
-          <t>ATAMPA</t>
-        </is>
-      </c>
-      <c r="O211" s="0" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="R211" s="0" t="inlineStr">
+      <c r="G212" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="O212" s="0" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R212" s="0" t="inlineStr">
         <is>
           <t>32000.00</t>
         </is>
       </c>
-      <c r="S211" s="0" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="T211" s="0" t="inlineStr">
+      <c r="S212" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="T212" s="0" t="inlineStr">
         <is>
           <t>35000.00</t>
         </is>
       </c>
-      <c r="Z211" s="0" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="AA211" s="0">
+      <c r="Z212" s="0" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="AA212" s="0">
         <v>44</v>
       </c>
-      <c r="AV211" s="0" t="inlineStr">
+      <c r="AV212" s="0" t="inlineStr">
         <is>
           <t>88</t>
         </is>

--- a/Excels/Items.xlsx
+++ b/Excels/Items.xlsx
@@ -421,7 +421,7 @@
         </is>
       </c>
       <c r="AA4" s="0">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AV4" s="0" t="inlineStr">
         <is>
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="AA5" s="0">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AV5" s="0" t="inlineStr">
         <is>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="AA6" s="0">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV6" s="0" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="AA7" s="0">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AV7" s="0" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="AA12" s="0">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="AV12" s="0" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="AA13" s="0">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AV13" s="0" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="AA14" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV14" s="0" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="AA18" s="0">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="AV18" s="0" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="AA19" s="0">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AV19" s="0" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="AA20" s="0">
-        <v>580</v>
+        <v>531</v>
       </c>
       <c r="AV20" s="0" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="AA21" s="0">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="AV21" s="0" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="AA26" s="0">
-        <v>178</v>
+        <v>300</v>
       </c>
       <c r="AV26" s="0" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="R27" s="0" t="inlineStr">
         <is>
-          <t>24986.350073268</t>
+          <t>24990.7383745862</t>
         </is>
       </c>
       <c r="S27" s="0" t="inlineStr">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="AA27" s="0">
-        <v>410</v>
+        <v>565</v>
       </c>
       <c r="AV27" s="0" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="AA28" s="0">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AV28" s="0" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="AA29" s="0">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="AV29" s="0" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="AA30" s="0">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="AV30" s="0" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="AA31" s="0">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AV31" s="0" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="AA32" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AV32" s="0" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="AA33" s="0">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AV33" s="0" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         </is>
       </c>
       <c r="AA34" s="0">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV34" s="0" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="AA36" s="0">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AV36" s="0" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         </is>
       </c>
       <c r="AA38" s="0">
-        <v>1181</v>
+        <v>1141</v>
       </c>
       <c r="AV38" s="0" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="AA41" s="0">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AV41" s="0" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="R51" s="0" t="inlineStr">
         <is>
-          <t>8004.9441216316</t>
+          <t>8002.5022386665</t>
         </is>
       </c>
       <c r="S51" s="0" t="inlineStr">
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="AA51" s="0">
-        <v>403</v>
+        <v>719</v>
       </c>
       <c r="AV51" s="0" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="AA55" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV55" s="0" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="AA57" s="0">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="AV57" s="0" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="AA63" s="0">
-        <v>786</v>
+        <v>752</v>
       </c>
       <c r="AV63" s="0" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="AA66" s="0">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="AV66" s="0" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="AA67" s="0">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="AV67" s="0" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="AA70" s="0">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="AV70" s="0" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="AA71" s="0">
-        <v>759</v>
+        <v>740</v>
       </c>
       <c r="AV71" s="0" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
       </c>
       <c r="R77" s="0" t="inlineStr">
         <is>
-          <t>11001.1933174224</t>
+          <t>11001.0892490425</t>
         </is>
       </c>
       <c r="S77" s="0" t="inlineStr">
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="AA77" s="0">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="AV77" s="0" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="AA78" s="0">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AV78" s="0" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="AA80" s="0">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="AV80" s="0" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="AA81" s="0">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="AV81" s="0" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="AA83" s="0">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="AV83" s="0" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="AA84" s="0">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AV84" s="0" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="AA85" s="0">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="AV85" s="0" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="AA86" s="0">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="AV86" s="0" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         </is>
       </c>
       <c r="AA88" s="0">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AV88" s="0" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="AA89" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV89" s="0" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="AA102" s="0">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AV102" s="0" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         </is>
       </c>
       <c r="AA103" s="0">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="AV103" s="0" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="AA106" s="0">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV106" s="0" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="AA110" s="0">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AV110" s="0" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="R111" s="0" t="inlineStr">
         <is>
-          <t>19665.8642629905</t>
+          <t>19725.8886468844</t>
         </is>
       </c>
       <c r="S111" s="0" t="inlineStr">
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="AA111" s="0">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="AV111" s="0" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         </is>
       </c>
       <c r="AA112" s="0">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AV112" s="0" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         </is>
       </c>
       <c r="AA114" s="0">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV114" s="0" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="AA115" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV115" s="0" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="AA116" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV116" s="0" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="AA118" s="0">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="AV118" s="0" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="R119" s="0" t="inlineStr">
         <is>
-          <t>6642.8571428571</t>
+          <t>6592.9070929071</t>
         </is>
       </c>
       <c r="S119" s="0" t="inlineStr">
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="AA119" s="0">
-        <v>558</v>
+        <v>835</v>
       </c>
       <c r="AV119" s="0" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         </is>
       </c>
       <c r="AA122" s="0">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AV122" s="0" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         </is>
       </c>
       <c r="AA123" s="0">
-        <v>935</v>
+        <v>763</v>
       </c>
       <c r="AV123" s="0" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="AA124" s="0">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="AV124" s="0" t="inlineStr">
         <is>
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="AA126" s="0">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="AV126" s="0" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="AA127" s="0">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="AV127" s="0" t="inlineStr">
         <is>
@@ -6222,10 +6222,8 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA131" s="0" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
+      <c r="AA131" s="0">
+        <v>6</v>
       </c>
       <c r="AV131" s="0" t="inlineStr">
         <is>
@@ -6270,7 +6268,7 @@
         </is>
       </c>
       <c r="AA132" s="0">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="AV132" s="0" t="inlineStr">
         <is>
@@ -6405,7 +6403,7 @@
         </is>
       </c>
       <c r="AA135" s="0">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="AV135" s="0" t="inlineStr">
         <is>
@@ -6540,7 +6538,7 @@
         </is>
       </c>
       <c r="AA138" s="0">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="AV138" s="0" t="inlineStr">
         <is>
@@ -6765,7 +6763,7 @@
         </is>
       </c>
       <c r="AA143" s="0">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AV143" s="0" t="inlineStr">
         <is>
@@ -6902,7 +6900,7 @@
         </is>
       </c>
       <c r="AA146" s="0">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="AV146" s="0" t="inlineStr">
         <is>
@@ -6928,7 +6926,7 @@
       </c>
       <c r="R147" s="0" t="inlineStr">
         <is>
-          <t>2700.00</t>
+          <t>2630.00</t>
         </is>
       </c>
       <c r="S147" s="0" t="inlineStr">
@@ -6947,7 +6945,7 @@
         </is>
       </c>
       <c r="AA147" s="0">
-        <v>328</v>
+        <v>757</v>
       </c>
       <c r="AV147" s="0" t="inlineStr">
         <is>
@@ -6997,7 +6995,7 @@
         </is>
       </c>
       <c r="AA148" s="0">
-        <v>134</v>
+        <v>93</v>
       </c>
       <c r="AV148" s="0" t="inlineStr">
         <is>
@@ -7402,7 +7400,7 @@
         </is>
       </c>
       <c r="AA157" s="0">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AV157" s="0" t="inlineStr">
         <is>
@@ -7582,7 +7580,7 @@
         </is>
       </c>
       <c r="AA161" s="0">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="AV161" s="0" t="inlineStr">
         <is>
@@ -7627,7 +7625,7 @@
         </is>
       </c>
       <c r="AA162" s="0">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AV162" s="0" t="inlineStr">
         <is>
@@ -7653,7 +7651,7 @@
       </c>
       <c r="R163" s="0" t="inlineStr">
         <is>
-          <t>9008.4040321109</t>
+          <t>9004.0120613707</t>
         </is>
       </c>
       <c r="S163" s="0" t="inlineStr">
@@ -7672,7 +7670,7 @@
         </is>
       </c>
       <c r="AA163" s="0">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="AV163" s="0" t="inlineStr">
         <is>
@@ -7717,7 +7715,7 @@
         </is>
       </c>
       <c r="AA164" s="0">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="AV164" s="0" t="inlineStr">
         <is>
@@ -7897,7 +7895,7 @@
         </is>
       </c>
       <c r="AA168" s="0">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="AV168" s="0" t="inlineStr">
         <is>
@@ -7987,7 +7985,7 @@
         </is>
       </c>
       <c r="AA170" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV170" s="0" t="inlineStr">
         <is>
@@ -8167,7 +8165,7 @@
         </is>
       </c>
       <c r="AA174" s="0">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AV174" s="0" t="inlineStr">
         <is>
@@ -8257,7 +8255,7 @@
         </is>
       </c>
       <c r="AA176" s="0">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV176" s="0" t="inlineStr">
         <is>
@@ -8389,7 +8387,7 @@
         </is>
       </c>
       <c r="AA179" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV179" s="0" t="inlineStr">
         <is>
@@ -8804,7 +8802,7 @@
         </is>
       </c>
       <c r="AA188" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AV188" s="0" t="inlineStr">
         <is>
@@ -8984,7 +8982,7 @@
         </is>
       </c>
       <c r="AA192" s="0">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="AV192" s="0" t="inlineStr">
         <is>
@@ -9164,7 +9162,7 @@
         </is>
       </c>
       <c r="AA196" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV196" s="0" t="inlineStr">
         <is>
@@ -9209,7 +9207,7 @@
         </is>
       </c>
       <c r="AA197" s="0">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="AV197" s="0" t="inlineStr">
         <is>
@@ -9304,7 +9302,7 @@
         </is>
       </c>
       <c r="AA199" s="0">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="AV199" s="0" t="inlineStr">
         <is>
@@ -9394,7 +9392,7 @@
         </is>
       </c>
       <c r="AA201" s="0">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AV201" s="0" t="inlineStr">
         <is>
@@ -9439,7 +9437,7 @@
         </is>
       </c>
       <c r="AA202" s="0">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AV202" s="0" t="inlineStr">
         <is>
@@ -9621,7 +9619,7 @@
         </is>
       </c>
       <c r="AA206" s="0">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AV206" s="0" t="inlineStr">
         <is>
@@ -9761,7 +9759,7 @@
         </is>
       </c>
       <c r="AA209" s="0">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="AV209" s="0" t="inlineStr">
         <is>
@@ -9806,7 +9804,7 @@
         </is>
       </c>
       <c r="AA210" s="0">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AV210" s="0" t="inlineStr">
         <is>
@@ -9896,7 +9894,7 @@
         </is>
       </c>
       <c r="AA212" s="0">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="AV212" s="0" t="inlineStr">
         <is>

--- a/Excels/Items.xlsx
+++ b/Excels/Items.xlsx
@@ -331,7 +331,7 @@
         </is>
       </c>
       <c r="AA2" s="0">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AV2" s="0" t="inlineStr">
         <is>
@@ -421,7 +421,7 @@
         </is>
       </c>
       <c r="AA4" s="0">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="AV4" s="0" t="inlineStr">
         <is>
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="AA5" s="0">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="AV5" s="0" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="AA8" s="0">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AV8" s="0" t="inlineStr">
         <is>
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="AA10" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV10" s="0" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
       </c>
       <c r="T11" s="0" t="inlineStr">
         <is>
-          <t>250000.00</t>
+          <t>150000.00</t>
         </is>
       </c>
       <c r="Z11" s="0" t="inlineStr">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="AA11" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV11" s="0" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="AA13" s="0">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="AV13" s="0" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="AA17" s="0">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="AV17" s="0" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="AA18" s="0">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="AV18" s="0" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="AA19" s="0">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AV19" s="0" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="AA20" s="0">
-        <v>531</v>
+        <v>518</v>
       </c>
       <c r="AV20" s="0" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="AA21" s="0">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="AV21" s="0" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="AA26" s="0">
-        <v>300</v>
+        <v>263</v>
       </c>
       <c r="AV26" s="0" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="R27" s="0" t="inlineStr">
         <is>
-          <t>24990.7383745862</t>
+          <t>24993.2241505226</t>
         </is>
       </c>
       <c r="S27" s="0" t="inlineStr">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="AA27" s="0">
-        <v>565</v>
+        <v>657</v>
       </c>
       <c r="AV27" s="0" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="AA28" s="0">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AV28" s="0" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="AA29" s="0">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="AV29" s="0" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="AA30" s="0">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AV30" s="0" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="AA33" s="0">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AV33" s="0" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="AA35" s="0">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="AV35" s="0" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="AA37" s="0">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="AV37" s="0" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="R38" s="0" t="inlineStr">
         <is>
-          <t>14904.913275101</t>
+          <t>14776.6946086133</t>
         </is>
       </c>
       <c r="S38" s="0" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="T38" s="0" t="inlineStr">
         <is>
-          <t>18000.00</t>
+          <t>17000.00</t>
         </is>
       </c>
       <c r="Z38" s="0" t="inlineStr">
@@ -1968,7 +1968,7 @@
         </is>
       </c>
       <c r="AA38" s="0">
-        <v>1141</v>
+        <v>1241</v>
       </c>
       <c r="AV38" s="0" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="AA41" s="0">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AV41" s="0" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="AA45" s="0">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV45" s="0" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         </is>
       </c>
       <c r="AA46" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV46" s="0" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="R50" s="0" t="inlineStr">
         <is>
-          <t>6000.00</t>
+          <t>6285.7142857143</t>
         </is>
       </c>
       <c r="S50" s="0" t="inlineStr">
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="AA50" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AV50" s="0" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="R51" s="0" t="inlineStr">
         <is>
-          <t>8002.5022386665</t>
+          <t>8003.099811318</t>
         </is>
       </c>
       <c r="S51" s="0" t="inlineStr">
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="AA51" s="0">
-        <v>719</v>
+        <v>651</v>
       </c>
       <c r="AV51" s="0" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="AA57" s="0">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="AV57" s="0" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="AA62" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV62" s="0" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="AA63" s="0">
-        <v>752</v>
+        <v>682</v>
       </c>
       <c r="AV63" s="0" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="AA64" s="0">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AV64" s="0" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         </is>
       </c>
       <c r="AA65" s="0">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AV65" s="0" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="AA66" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV66" s="0" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="AA67" s="0">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="AV67" s="0" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="AA69" s="0" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="AV69" s="0" t="inlineStr">
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="AA70" s="0">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="AV70" s="0" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="AA71" s="0">
-        <v>740</v>
+        <v>717</v>
       </c>
       <c r="AV71" s="0" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="AA77" s="0">
-        <v>325</v>
+        <v>226</v>
       </c>
       <c r="AV77" s="0" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         </is>
       </c>
       <c r="AA78" s="0">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AV78" s="0" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="AA80" s="0">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="AV80" s="0" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="AA81" s="0">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="AV81" s="0" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="AA83" s="0">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="AV83" s="0" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="AA84" s="0">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="AV84" s="0" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="R85" s="0" t="inlineStr">
         <is>
-          <t>11770.2702702703</t>
+          <t>12952.749490835</t>
         </is>
       </c>
       <c r="S85" s="0" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="T85" s="0" t="inlineStr">
         <is>
-          <t>12500.00</t>
+          <t>15000.00</t>
         </is>
       </c>
       <c r="Z85" s="0" t="inlineStr">
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="AA85" s="0">
-        <v>29</v>
+        <v>214</v>
       </c>
       <c r="AV85" s="0" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="AA86" s="0">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="AV86" s="0" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="AA89" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV89" s="0" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="AA90" s="0">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AV90" s="0" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="AA101" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV101" s="0" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="AA102" s="0">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AV102" s="0" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="R103" s="0" t="inlineStr">
         <is>
-          <t>75041.4291449217</t>
+          <t>75007.0243186892</t>
         </is>
       </c>
       <c r="S103" s="0" t="inlineStr">
@@ -4941,7 +4941,7 @@
         </is>
       </c>
       <c r="AA103" s="0">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="AV103" s="0" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         </is>
       </c>
       <c r="AA107" s="0">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AV107" s="0" t="inlineStr">
         <is>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="R110" s="0" t="inlineStr">
         <is>
-          <t>22027.3934441452</t>
+          <t>22016.1338348697</t>
         </is>
       </c>
       <c r="S110" s="0" t="inlineStr">
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="AA110" s="0">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="AV110" s="0" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="AA111" s="0">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="AV111" s="0" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         </is>
       </c>
       <c r="AA112" s="0">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AV112" s="0" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="AA116" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV116" s="0" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="AA118" s="0">
-        <v>240</v>
+        <v>188</v>
       </c>
       <c r="AV118" s="0" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="AA119" s="0">
-        <v>835</v>
+        <v>805</v>
       </c>
       <c r="AV119" s="0" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AA120" s="0" t="inlineStr">
         <is>
-          <t>234.5</t>
+          <t>384.5</t>
         </is>
       </c>
       <c r="AV120" s="0" t="inlineStr">
@@ -5729,12 +5729,12 @@
     <row r="121" spans="1:48">
       <c r="C121" s="0" t="inlineStr">
         <is>
-          <t>LUXURY AND VEBA PLUS</t>
+          <t>Luxe Embellished MD</t>
         </is>
       </c>
       <c r="G121" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O121" s="0" t="inlineStr">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="R121" s="0" t="inlineStr">
         <is>
-          <t>7000.00</t>
+          <t>14000.00</t>
         </is>
       </c>
       <c r="S121" s="0" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="T121" s="0" t="inlineStr">
         <is>
-          <t>8500.00</t>
+          <t>17000.00</t>
         </is>
       </c>
       <c r="Z121" s="0" t="inlineStr">
@@ -5763,18 +5763,18 @@
         </is>
       </c>
       <c r="AA121" s="0">
-        <v>188</v>
+        <v>371</v>
       </c>
       <c r="AV121" s="0" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>216</t>
         </is>
       </c>
     </row>
     <row r="122" spans="1:48">
       <c r="C122" s="0" t="inlineStr">
         <is>
-          <t>Madam Getzner Gold edition</t>
+          <t>LUXURY AND VEBA PLUS</t>
         </is>
       </c>
       <c r="G122" s="0" t="inlineStr">
@@ -5782,11 +5782,6 @@
           <t>SHADDA</t>
         </is>
       </c>
-      <c r="H122" s="0" t="inlineStr">
-        <is>
-          <t>FAHAD TAHIR</t>
-        </is>
-      </c>
       <c r="O122" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -5794,7 +5789,7 @@
       </c>
       <c r="R122" s="0" t="inlineStr">
         <is>
-          <t>30000.00</t>
+          <t>7000.00</t>
         </is>
       </c>
       <c r="S122" s="0" t="inlineStr">
@@ -5804,7 +5799,7 @@
       </c>
       <c r="T122" s="0" t="inlineStr">
         <is>
-          <t>45000.00</t>
+          <t>8500.00</t>
         </is>
       </c>
       <c r="Z122" s="0" t="inlineStr">
@@ -5813,18 +5808,18 @@
         </is>
       </c>
       <c r="AA122" s="0">
-        <v>94</v>
+        <v>188</v>
       </c>
       <c r="AV122" s="0" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>175</t>
         </is>
       </c>
     </row>
     <row r="123" spans="1:48">
       <c r="C123" s="0" t="inlineStr">
         <is>
-          <t>MADAM GRTZNER MEDIUM</t>
+          <t>Madam Getzner Gold edition</t>
         </is>
       </c>
       <c r="G123" s="0" t="inlineStr">
@@ -5832,6 +5827,11 @@
           <t>SHADDA</t>
         </is>
       </c>
+      <c r="H123" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
+        </is>
+      </c>
       <c r="O123" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="R123" s="0" t="inlineStr">
         <is>
-          <t>5500.00</t>
+          <t>30000.00</t>
         </is>
       </c>
       <c r="S123" s="0" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="T123" s="0" t="inlineStr">
         <is>
-          <t>7500.00</t>
+          <t>45000.00</t>
         </is>
       </c>
       <c r="Z123" s="0" t="inlineStr">
@@ -5858,28 +5858,23 @@
         </is>
       </c>
       <c r="AA123" s="0">
-        <v>763</v>
+        <v>90</v>
       </c>
       <c r="AV123" s="0" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>207</t>
         </is>
       </c>
     </row>
     <row r="124" spans="1:48">
       <c r="C124" s="0" t="inlineStr">
         <is>
-          <t>Magic holland</t>
+          <t>MADAM GRTZNER MEDIUM</t>
         </is>
       </c>
       <c r="G124" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
-        </is>
-      </c>
-      <c r="H124" s="0" t="inlineStr">
-        <is>
-          <t>YAYA SANI</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O124" s="0" t="inlineStr">
@@ -5889,7 +5884,7 @@
       </c>
       <c r="R124" s="0" t="inlineStr">
         <is>
-          <t>9500.00</t>
+          <t>5500.00</t>
         </is>
       </c>
       <c r="S124" s="0" t="inlineStr">
@@ -5899,7 +5894,7 @@
       </c>
       <c r="T124" s="0" t="inlineStr">
         <is>
-          <t>10500.00</t>
+          <t>7500.00</t>
         </is>
       </c>
       <c r="Z124" s="0" t="inlineStr">
@@ -5908,18 +5903,18 @@
         </is>
       </c>
       <c r="AA124" s="0">
-        <v>158</v>
+        <v>741</v>
       </c>
       <c r="AV124" s="0" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="125" spans="1:48">
       <c r="C125" s="0" t="inlineStr">
         <is>
-          <t>MEDIUM EMBELLISHED </t>
+          <t>Magic holland</t>
         </is>
       </c>
       <c r="G125" s="0" t="inlineStr">
@@ -5927,6 +5922,11 @@
           <t>ATAMPA</t>
         </is>
       </c>
+      <c r="H125" s="0" t="inlineStr">
+        <is>
+          <t>YAYA SANI</t>
+        </is>
+      </c>
       <c r="O125" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="R125" s="0" t="inlineStr">
         <is>
-          <t>18000.00</t>
+          <t>9500.00</t>
         </is>
       </c>
       <c r="S125" s="0" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="T125" s="0" t="inlineStr">
         <is>
-          <t>20000.00</t>
+          <t>10500.00</t>
         </is>
       </c>
       <c r="Z125" s="0" t="inlineStr">
@@ -5953,18 +5953,18 @@
         </is>
       </c>
       <c r="AA125" s="0">
-        <v>9</v>
+        <v>136</v>
       </c>
       <c r="AV125" s="0" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>206</t>
         </is>
       </c>
     </row>
     <row r="126" spans="1:48">
       <c r="C126" s="0" t="inlineStr">
         <is>
-          <t>MEDIUM GLITTER</t>
+          <t>Mandela kente Gold</t>
         </is>
       </c>
       <c r="G126" s="0" t="inlineStr">
@@ -5972,6 +5972,11 @@
           <t>ATAMPA</t>
         </is>
       </c>
+      <c r="H126" s="0" t="inlineStr">
+        <is>
+          <t>HAFIZU TAHIR SHOP</t>
+        </is>
+      </c>
       <c r="O126" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -5979,7 +5984,7 @@
       </c>
       <c r="R126" s="0" t="inlineStr">
         <is>
-          <t>14500.00</t>
+          <t>14072.8155339806</t>
         </is>
       </c>
       <c r="S126" s="0" t="inlineStr">
@@ -5989,7 +5994,7 @@
       </c>
       <c r="T126" s="0" t="inlineStr">
         <is>
-          <t>18000.00</t>
+          <t>15000.00</t>
         </is>
       </c>
       <c r="Z126" s="0" t="inlineStr">
@@ -5998,18 +6003,18 @@
         </is>
       </c>
       <c r="AA126" s="0">
-        <v>306</v>
+        <v>70</v>
       </c>
       <c r="AV126" s="0" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>219</t>
         </is>
       </c>
     </row>
     <row r="127" spans="1:48">
       <c r="C127" s="0" t="inlineStr">
         <is>
-          <t>MEDIUM SUPER </t>
+          <t>MEDIUM EMBELLISHED </t>
         </is>
       </c>
       <c r="G127" s="0" t="inlineStr">
@@ -6024,7 +6029,7 @@
       </c>
       <c r="R127" s="0" t="inlineStr">
         <is>
-          <t>12541.1181181036</t>
+          <t>18000.00</t>
         </is>
       </c>
       <c r="S127" s="0" t="inlineStr">
@@ -6034,7 +6039,7 @@
       </c>
       <c r="T127" s="0" t="inlineStr">
         <is>
-          <t>14000.00</t>
+          <t>20000.00</t>
         </is>
       </c>
       <c r="Z127" s="0" t="inlineStr">
@@ -6043,18 +6048,18 @@
         </is>
       </c>
       <c r="AA127" s="0">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="AV127" s="0" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>113</t>
         </is>
       </c>
     </row>
     <row r="128" spans="1:48">
       <c r="C128" s="0" t="inlineStr">
         <is>
-          <t>MITEX HOLLAND </t>
+          <t>MEDIUM GLITTER</t>
         </is>
       </c>
       <c r="G128" s="0" t="inlineStr">
@@ -6069,7 +6074,7 @@
       </c>
       <c r="R128" s="0" t="inlineStr">
         <is>
-          <t>47000.00</t>
+          <t>14500.00</t>
         </is>
       </c>
       <c r="S128" s="0" t="inlineStr">
@@ -6079,7 +6084,7 @@
       </c>
       <c r="T128" s="0" t="inlineStr">
         <is>
-          <t>55000.00</t>
+          <t>18000.00</t>
         </is>
       </c>
       <c r="Z128" s="0" t="inlineStr">
@@ -6088,23 +6093,23 @@
         </is>
       </c>
       <c r="AA128" s="0">
-        <v>2</v>
+        <v>294</v>
       </c>
       <c r="AV128" s="0" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>116</t>
         </is>
       </c>
     </row>
     <row r="129" spans="1:48">
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t>MOONLIGHT AND SUPREME FOLDER</t>
+          <t>MEDIUM SUPER </t>
         </is>
       </c>
       <c r="G129" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O129" s="0" t="inlineStr">
@@ -6114,7 +6119,7 @@
       </c>
       <c r="R129" s="0" t="inlineStr">
         <is>
-          <t>5000.00</t>
+          <t>12541.1181181036</t>
         </is>
       </c>
       <c r="S129" s="0" t="inlineStr">
@@ -6124,7 +6129,7 @@
       </c>
       <c r="T129" s="0" t="inlineStr">
         <is>
-          <t>6500.00</t>
+          <t>14000.00</t>
         </is>
       </c>
       <c r="Z129" s="0" t="inlineStr">
@@ -6133,23 +6138,28 @@
         </is>
       </c>
       <c r="AA129" s="0">
-        <v>187</v>
+        <v>83</v>
       </c>
       <c r="AV129" s="0" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>123</t>
         </is>
       </c>
     </row>
     <row r="130" spans="1:48">
       <c r="C130" s="0" t="inlineStr">
         <is>
-          <t>MUHANTEX EMBELLISHED</t>
+          <t>Mesh luxury lace</t>
         </is>
       </c>
       <c r="G130" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>LACE</t>
+        </is>
+      </c>
+      <c r="H130" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
         </is>
       </c>
       <c r="O130" s="0" t="inlineStr">
@@ -6159,7 +6169,7 @@
       </c>
       <c r="R130" s="0" t="inlineStr">
         <is>
-          <t>15500.00</t>
+          <t>170000.00</t>
         </is>
       </c>
       <c r="S130" s="0" t="inlineStr">
@@ -6169,7 +6179,7 @@
       </c>
       <c r="T130" s="0" t="inlineStr">
         <is>
-          <t>18000.00</t>
+          <t>280000.00</t>
         </is>
       </c>
       <c r="Z130" s="0" t="inlineStr">
@@ -6178,23 +6188,23 @@
         </is>
       </c>
       <c r="AA130" s="0">
-        <v>86</v>
+        <v>11</v>
       </c>
       <c r="AV130" s="0" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>217</t>
         </is>
       </c>
     </row>
     <row r="131" spans="1:48">
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t>NBTX 400</t>
+          <t>MITEX HOLLAND </t>
         </is>
       </c>
       <c r="G131" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O131" s="0" t="inlineStr">
@@ -6204,7 +6214,7 @@
       </c>
       <c r="R131" s="0" t="inlineStr">
         <is>
-          <t>22000.00</t>
+          <t>47000.00</t>
         </is>
       </c>
       <c r="S131" s="0" t="inlineStr">
@@ -6214,7 +6224,7 @@
       </c>
       <c r="T131" s="0" t="inlineStr">
         <is>
-          <t>25000.00</t>
+          <t>55000.00</t>
         </is>
       </c>
       <c r="Z131" s="0" t="inlineStr">
@@ -6223,23 +6233,23 @@
         </is>
       </c>
       <c r="AA131" s="0">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AV131" s="0" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="132" spans="1:48">
       <c r="C132" s="0" t="inlineStr">
         <is>
-          <t>NEW JULIUS HOLLAND</t>
+          <t>MOONLIGHT AND SUPREME FOLDER</t>
         </is>
       </c>
       <c r="G132" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O132" s="0" t="inlineStr">
@@ -6249,7 +6259,7 @@
       </c>
       <c r="R132" s="0" t="inlineStr">
         <is>
-          <t>62000.00</t>
+          <t>5000.00</t>
         </is>
       </c>
       <c r="S132" s="0" t="inlineStr">
@@ -6259,7 +6269,7 @@
       </c>
       <c r="T132" s="0" t="inlineStr">
         <is>
-          <t>70000.00</t>
+          <t>6500.00</t>
         </is>
       </c>
       <c r="Z132" s="0" t="inlineStr">
@@ -6268,23 +6278,23 @@
         </is>
       </c>
       <c r="AA132" s="0">
-        <v>61</v>
+        <v>167</v>
       </c>
       <c r="AV132" s="0" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>177</t>
         </is>
       </c>
     </row>
     <row r="133" spans="1:48">
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t>NEW MADAM MEDIUM GETZNER</t>
+          <t>MUHANTEX EMBELLISHED</t>
         </is>
       </c>
       <c r="G133" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O133" s="0" t="inlineStr">
@@ -6294,7 +6304,7 @@
       </c>
       <c r="R133" s="0" t="inlineStr">
         <is>
-          <t>7000.00</t>
+          <t>15500.00</t>
         </is>
       </c>
       <c r="S133" s="0" t="inlineStr">
@@ -6304,7 +6314,7 @@
       </c>
       <c r="T133" s="0" t="inlineStr">
         <is>
-          <t>10000.00</t>
+          <t>18000.00</t>
         </is>
       </c>
       <c r="Z133" s="0" t="inlineStr">
@@ -6313,23 +6323,23 @@
         </is>
       </c>
       <c r="AA133" s="0">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="AV133" s="0" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>155</t>
         </is>
       </c>
     </row>
     <row r="134" spans="1:48">
       <c r="C134" s="0" t="inlineStr">
         <is>
-          <t>NEW MEDIUM GLITTER </t>
+          <t>NBTX 400</t>
         </is>
       </c>
       <c r="G134" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O134" s="0" t="inlineStr">
@@ -6339,7 +6349,7 @@
       </c>
       <c r="R134" s="0" t="inlineStr">
         <is>
-          <t>19000.00</t>
+          <t>22000.00</t>
         </is>
       </c>
       <c r="S134" s="0" t="inlineStr">
@@ -6349,7 +6359,7 @@
       </c>
       <c r="T134" s="0" t="inlineStr">
         <is>
-          <t>22000.00</t>
+          <t>25000.00</t>
         </is>
       </c>
       <c r="Z134" s="0" t="inlineStr">
@@ -6358,18 +6368,18 @@
         </is>
       </c>
       <c r="AA134" s="0">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="AV134" s="0" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>185</t>
         </is>
       </c>
     </row>
     <row r="135" spans="1:48">
       <c r="C135" s="0" t="inlineStr">
         <is>
-          <t>NEW POPULAR</t>
+          <t>NEW JULIUS HOLLAND</t>
         </is>
       </c>
       <c r="G135" s="0" t="inlineStr">
@@ -6384,7 +6394,7 @@
       </c>
       <c r="R135" s="0" t="inlineStr">
         <is>
-          <t>9000.00</t>
+          <t>62000.00</t>
         </is>
       </c>
       <c r="S135" s="0" t="inlineStr">
@@ -6394,7 +6404,7 @@
       </c>
       <c r="T135" s="0" t="inlineStr">
         <is>
-          <t>10000.00</t>
+          <t>70000.00</t>
         </is>
       </c>
       <c r="Z135" s="0" t="inlineStr">
@@ -6403,23 +6413,23 @@
         </is>
       </c>
       <c r="AA135" s="0">
-        <v>254</v>
+        <v>86</v>
       </c>
       <c r="AV135" s="0" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>82</t>
         </is>
       </c>
     </row>
     <row r="136" spans="1:48">
       <c r="C136" s="0" t="inlineStr">
         <is>
-          <t>NEW SHERATON SATIN WAX</t>
+          <t>NEW MADAM MEDIUM GETZNER</t>
         </is>
       </c>
       <c r="G136" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O136" s="0" t="inlineStr">
@@ -6429,7 +6439,7 @@
       </c>
       <c r="R136" s="0" t="inlineStr">
         <is>
-          <t>230000.00</t>
+          <t>7000.00</t>
         </is>
       </c>
       <c r="S136" s="0" t="inlineStr">
@@ -6439,7 +6449,7 @@
       </c>
       <c r="T136" s="0" t="inlineStr">
         <is>
-          <t>250000.00</t>
+          <t>10000.00</t>
         </is>
       </c>
       <c r="Z136" s="0" t="inlineStr">
@@ -6448,18 +6458,18 @@
         </is>
       </c>
       <c r="AA136" s="0">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="AV136" s="0" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>54</t>
         </is>
       </c>
     </row>
     <row r="137" spans="1:48">
       <c r="C137" s="0" t="inlineStr">
         <is>
-          <t>NEW SUPER HOLLAND EMBELLISHED</t>
+          <t>NEW MEDIUM GLITTER </t>
         </is>
       </c>
       <c r="G137" s="0" t="inlineStr">
@@ -6474,7 +6484,7 @@
       </c>
       <c r="R137" s="0" t="inlineStr">
         <is>
-          <t>230000.00</t>
+          <t>19000.00</t>
         </is>
       </c>
       <c r="S137" s="0" t="inlineStr">
@@ -6484,7 +6494,7 @@
       </c>
       <c r="T137" s="0" t="inlineStr">
         <is>
-          <t>260000.00</t>
+          <t>22000.00</t>
         </is>
       </c>
       <c r="Z137" s="0" t="inlineStr">
@@ -6493,23 +6503,23 @@
         </is>
       </c>
       <c r="AA137" s="0">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="AV137" s="0" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>110</t>
         </is>
       </c>
     </row>
     <row r="138" spans="1:48">
       <c r="C138" s="0" t="inlineStr">
         <is>
-          <t>NEW TRAVELLING AND SUPER POLISH</t>
+          <t>NEW POPULAR</t>
         </is>
       </c>
       <c r="G138" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O138" s="0" t="inlineStr">
@@ -6519,7 +6529,7 @@
       </c>
       <c r="R138" s="0" t="inlineStr">
         <is>
-          <t>4000.00</t>
+          <t>9000.00</t>
         </is>
       </c>
       <c r="S138" s="0" t="inlineStr">
@@ -6529,7 +6539,7 @@
       </c>
       <c r="T138" s="0" t="inlineStr">
         <is>
-          <t>5000.00</t>
+          <t>10000.00</t>
         </is>
       </c>
       <c r="Z138" s="0" t="inlineStr">
@@ -6538,18 +6548,18 @@
         </is>
       </c>
       <c r="AA138" s="0">
-        <v>65</v>
+        <v>233</v>
       </c>
       <c r="AV138" s="0" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>133</t>
         </is>
       </c>
     </row>
     <row r="139" spans="1:48">
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t>NEW ULTRA EMBELLISHED</t>
+          <t>NEW SHERATON SATIN WAX</t>
         </is>
       </c>
       <c r="G139" s="0" t="inlineStr">
@@ -6564,7 +6574,7 @@
       </c>
       <c r="R139" s="0" t="inlineStr">
         <is>
-          <t>30532.1100917431</t>
+          <t>230000.00</t>
         </is>
       </c>
       <c r="S139" s="0" t="inlineStr">
@@ -6574,7 +6584,7 @@
       </c>
       <c r="T139" s="0" t="inlineStr">
         <is>
-          <t>35000.00</t>
+          <t>250000.00</t>
         </is>
       </c>
       <c r="Z139" s="0" t="inlineStr">
@@ -6583,18 +6593,18 @@
         </is>
       </c>
       <c r="AA139" s="0">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="AV139" s="0" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="140" spans="1:48">
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t>PATCHWORK ATAMPA </t>
+          <t>NEW SUPER HOLLAND EMBELLISHED</t>
         </is>
       </c>
       <c r="G140" s="0" t="inlineStr">
@@ -6609,7 +6619,7 @@
       </c>
       <c r="R140" s="0" t="inlineStr">
         <is>
-          <t>70000.00</t>
+          <t>230000.00</t>
         </is>
       </c>
       <c r="S140" s="0" t="inlineStr">
@@ -6619,7 +6629,7 @@
       </c>
       <c r="T140" s="0" t="inlineStr">
         <is>
-          <t>85000.00</t>
+          <t>260000.00</t>
         </is>
       </c>
       <c r="Z140" s="0" t="inlineStr">
@@ -6628,23 +6638,23 @@
         </is>
       </c>
       <c r="AA140" s="0">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="AV140" s="0" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>72</t>
         </is>
       </c>
     </row>
     <row r="141" spans="1:48">
       <c r="C141" s="0" t="inlineStr">
         <is>
-          <t>PATCHWORK ATAMPA MIX AND MATCH</t>
+          <t>NEW TRAVELLING AND SUPER POLISH</t>
         </is>
       </c>
       <c r="G141" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O141" s="0" t="inlineStr">
@@ -6654,7 +6664,7 @@
       </c>
       <c r="R141" s="0" t="inlineStr">
         <is>
-          <t>54000.00</t>
+          <t>4000.00</t>
         </is>
       </c>
       <c r="S141" s="0" t="inlineStr">
@@ -6664,7 +6674,7 @@
       </c>
       <c r="T141" s="0" t="inlineStr">
         <is>
-          <t>60000.00</t>
+          <t>5000.00</t>
         </is>
       </c>
       <c r="Z141" s="0" t="inlineStr">
@@ -6673,18 +6683,18 @@
         </is>
       </c>
       <c r="AA141" s="0">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="AV141" s="0" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>179</t>
         </is>
       </c>
     </row>
     <row r="142" spans="1:48">
       <c r="C142" s="0" t="inlineStr">
         <is>
-          <t>PERFECT ROYAL JAVA</t>
+          <t>NEW ULTRA EMBELLISHED</t>
         </is>
       </c>
       <c r="G142" s="0" t="inlineStr">
@@ -6699,7 +6709,7 @@
       </c>
       <c r="R142" s="0" t="inlineStr">
         <is>
-          <t>30000.00</t>
+          <t>30532.1100917431</t>
         </is>
       </c>
       <c r="S142" s="0" t="inlineStr">
@@ -6718,18 +6728,18 @@
         </is>
       </c>
       <c r="AA142" s="0">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AV142" s="0" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>156</t>
         </is>
       </c>
     </row>
     <row r="143" spans="1:48">
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t>PRESTIGE EMBELLISHED</t>
+          <t>PATCHWORK ATAMPA </t>
         </is>
       </c>
       <c r="G143" s="0" t="inlineStr">
@@ -6744,7 +6754,7 @@
       </c>
       <c r="R143" s="0" t="inlineStr">
         <is>
-          <t>15502.427184466</t>
+          <t>70000.00</t>
         </is>
       </c>
       <c r="S143" s="0" t="inlineStr">
@@ -6754,7 +6764,7 @@
       </c>
       <c r="T143" s="0" t="inlineStr">
         <is>
-          <t>17500.00</t>
+          <t>85000.00</t>
         </is>
       </c>
       <c r="Z143" s="0" t="inlineStr">
@@ -6763,23 +6773,23 @@
         </is>
       </c>
       <c r="AA143" s="0">
-        <v>188</v>
+        <v>27</v>
       </c>
       <c r="AV143" s="0" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>60</t>
         </is>
       </c>
     </row>
     <row r="144" spans="1:48">
       <c r="C144" s="0" t="inlineStr">
         <is>
-          <t>RIEDMAN MENLACE</t>
+          <t>PATCHWORK ATAMPA MIX AND MATCH</t>
         </is>
       </c>
       <c r="G144" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O144" s="0" t="inlineStr">
@@ -6789,7 +6799,7 @@
       </c>
       <c r="R144" s="0" t="inlineStr">
         <is>
-          <t>410000.00</t>
+          <t>54000.00</t>
         </is>
       </c>
       <c r="S144" s="0" t="inlineStr">
@@ -6799,7 +6809,7 @@
       </c>
       <c r="T144" s="0" t="inlineStr">
         <is>
-          <t>500000.00</t>
+          <t>60000.00</t>
         </is>
       </c>
       <c r="Z144" s="0" t="inlineStr">
@@ -6808,23 +6818,23 @@
         </is>
       </c>
       <c r="AA144" s="0">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AV144" s="0" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>145</t>
         </is>
       </c>
     </row>
     <row r="145" spans="1:48">
       <c r="C145" s="0" t="inlineStr">
         <is>
-          <t>RIEDMAN TAIWO ATIKU</t>
+          <t>PERFECT ROYAL JAVA</t>
         </is>
       </c>
       <c r="G145" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O145" s="0" t="inlineStr">
@@ -6834,7 +6844,7 @@
       </c>
       <c r="R145" s="0" t="inlineStr">
         <is>
-          <t>260000.00</t>
+          <t>30000.00</t>
         </is>
       </c>
       <c r="S145" s="0" t="inlineStr">
@@ -6844,7 +6854,7 @@
       </c>
       <c r="T145" s="0" t="inlineStr">
         <is>
-          <t>380000.00</t>
+          <t>35000.00</t>
         </is>
       </c>
       <c r="Z145" s="0" t="inlineStr">
@@ -6852,26 +6862,24 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA145" s="0" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
+      <c r="AA145" s="0">
+        <v>0</v>
       </c>
       <c r="AV145" s="0" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="146" spans="1:48">
       <c r="C146" s="0" t="inlineStr">
         <is>
-          <t>RIGHTMAN AND WISEMAN</t>
+          <t>PRESTIGE EMBELLISHED</t>
         </is>
       </c>
       <c r="G146" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O146" s="0" t="inlineStr">
@@ -6881,7 +6889,7 @@
       </c>
       <c r="R146" s="0" t="inlineStr">
         <is>
-          <t>4000.00</t>
+          <t>15502.427184466</t>
         </is>
       </c>
       <c r="S146" s="0" t="inlineStr">
@@ -6891,7 +6899,7 @@
       </c>
       <c r="T146" s="0" t="inlineStr">
         <is>
-          <t>5500.00</t>
+          <t>17500.00</t>
         </is>
       </c>
       <c r="Z146" s="0" t="inlineStr">
@@ -6900,23 +6908,23 @@
         </is>
       </c>
       <c r="AA146" s="0">
-        <v>518</v>
+        <v>166</v>
       </c>
       <c r="AV146" s="0" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>118</t>
         </is>
       </c>
     </row>
     <row r="147" spans="1:48">
       <c r="C147" s="0" t="inlineStr">
         <is>
-          <t>ROBA ATAMPA</t>
+          <t>RIEDMAN MENLACE</t>
         </is>
       </c>
       <c r="G147" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O147" s="0" t="inlineStr">
@@ -6926,7 +6934,7 @@
       </c>
       <c r="R147" s="0" t="inlineStr">
         <is>
-          <t>2630.00</t>
+          <t>410000.00</t>
         </is>
       </c>
       <c r="S147" s="0" t="inlineStr">
@@ -6936,7 +6944,7 @@
       </c>
       <c r="T147" s="0" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>500000.00</t>
         </is>
       </c>
       <c r="Z147" s="0" t="inlineStr">
@@ -6945,28 +6953,23 @@
         </is>
       </c>
       <c r="AA147" s="0">
-        <v>757</v>
+        <v>6</v>
       </c>
       <c r="AV147" s="0" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>162</t>
         </is>
       </c>
     </row>
     <row r="148" spans="1:48">
       <c r="C148" s="0" t="inlineStr">
         <is>
-          <t>Rotana holland</t>
+          <t>RIEDMAN TAIWO ATIKU</t>
         </is>
       </c>
       <c r="G148" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
-        </is>
-      </c>
-      <c r="H148" s="0" t="inlineStr">
-        <is>
-          <t>YAYA SANI</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O148" s="0" t="inlineStr">
@@ -6976,7 +6979,7 @@
       </c>
       <c r="R148" s="0" t="inlineStr">
         <is>
-          <t>8021.5189873418</t>
+          <t>260000.00</t>
         </is>
       </c>
       <c r="S148" s="0" t="inlineStr">
@@ -6986,7 +6989,7 @@
       </c>
       <c r="T148" s="0" t="inlineStr">
         <is>
-          <t>8500.00</t>
+          <t>380000.00</t>
         </is>
       </c>
       <c r="Z148" s="0" t="inlineStr">
@@ -6994,19 +6997,21 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA148" s="0">
-        <v>93</v>
+      <c r="AA148" s="0" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
       </c>
       <c r="AV148" s="0" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>164</t>
         </is>
       </c>
     </row>
     <row r="149" spans="1:48">
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t>Shadda lace</t>
+          <t>RIGHTMAN AND WISEMAN</t>
         </is>
       </c>
       <c r="G149" s="0" t="inlineStr">
@@ -7021,7 +7026,7 @@
       </c>
       <c r="R149" s="0" t="inlineStr">
         <is>
-          <t>25000.00</t>
+          <t>4000.00</t>
         </is>
       </c>
       <c r="S149" s="0" t="inlineStr">
@@ -7031,7 +7036,7 @@
       </c>
       <c r="T149" s="0" t="inlineStr">
         <is>
-          <t>32000.00</t>
+          <t>5500.00</t>
         </is>
       </c>
       <c r="Z149" s="0" t="inlineStr">
@@ -7040,23 +7045,23 @@
         </is>
       </c>
       <c r="AA149" s="0">
-        <v>10</v>
+        <v>488</v>
       </c>
       <c r="AV149" s="0" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>178</t>
         </is>
       </c>
     </row>
     <row r="150" spans="1:48">
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t>SHERATON BROCADE</t>
+          <t>ROBA ATAMPA</t>
         </is>
       </c>
       <c r="G150" s="0" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O150" s="0" t="inlineStr">
@@ -7066,7 +7071,7 @@
       </c>
       <c r="R150" s="0" t="inlineStr">
         <is>
-          <t>80000.00</t>
+          <t>2630.00</t>
         </is>
       </c>
       <c r="S150" s="0" t="inlineStr">
@@ -7076,7 +7081,7 @@
       </c>
       <c r="T150" s="0" t="inlineStr">
         <is>
-          <t>100000.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="Z150" s="0" t="inlineStr">
@@ -7085,18 +7090,18 @@
         </is>
       </c>
       <c r="AA150" s="0">
-        <v>3</v>
+        <v>721</v>
       </c>
       <c r="AV150" s="0" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>143</t>
         </is>
       </c>
     </row>
     <row r="151" spans="1:48">
       <c r="C151" s="0" t="inlineStr">
         <is>
-          <t>SHERATON EXCLUSIVE EMBELLISHED</t>
+          <t>Rotana holland</t>
         </is>
       </c>
       <c r="G151" s="0" t="inlineStr">
@@ -7104,6 +7109,11 @@
           <t>ATAMPA</t>
         </is>
       </c>
+      <c r="H151" s="0" t="inlineStr">
+        <is>
+          <t>YAYA SANI</t>
+        </is>
+      </c>
       <c r="O151" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -7111,7 +7121,7 @@
       </c>
       <c r="R151" s="0" t="inlineStr">
         <is>
-          <t>244006.0851926978</t>
+          <t>8021.5189873418</t>
         </is>
       </c>
       <c r="S151" s="0" t="inlineStr">
@@ -7121,7 +7131,7 @@
       </c>
       <c r="T151" s="0" t="inlineStr">
         <is>
-          <t>280000.00</t>
+          <t>8500.00</t>
         </is>
       </c>
       <c r="Z151" s="0" t="inlineStr">
@@ -7130,23 +7140,23 @@
         </is>
       </c>
       <c r="AA151" s="0">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="AV151" s="0" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>214</t>
         </is>
       </c>
     </row>
     <row r="152" spans="1:48">
       <c r="C152" s="0" t="inlineStr">
         <is>
-          <t>SHERATON EXCLUSIVE PLAIN </t>
+          <t>Shadda lace</t>
         </is>
       </c>
       <c r="G152" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O152" s="0" t="inlineStr">
@@ -7156,7 +7166,7 @@
       </c>
       <c r="R152" s="0" t="inlineStr">
         <is>
-          <t>200000.00</t>
+          <t>25000.00</t>
         </is>
       </c>
       <c r="S152" s="0" t="inlineStr">
@@ -7166,7 +7176,7 @@
       </c>
       <c r="T152" s="0" t="inlineStr">
         <is>
-          <t>220000.00</t>
+          <t>32000.00</t>
         </is>
       </c>
       <c r="Z152" s="0" t="inlineStr">
@@ -7175,23 +7185,23 @@
         </is>
       </c>
       <c r="AA152" s="0">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AV152" s="0" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>205</t>
         </is>
       </c>
     </row>
     <row r="153" spans="1:48">
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t>SHERATON HOLLAND EMBELLISHED</t>
+          <t>SHERATON BROCADE</t>
         </is>
       </c>
       <c r="G153" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="O153" s="0" t="inlineStr">
@@ -7201,7 +7211,7 @@
       </c>
       <c r="R153" s="0" t="inlineStr">
         <is>
-          <t>210000.00</t>
+          <t>80000.00</t>
         </is>
       </c>
       <c r="S153" s="0" t="inlineStr">
@@ -7211,7 +7221,7 @@
       </c>
       <c r="T153" s="0" t="inlineStr">
         <is>
-          <t>240000.00</t>
+          <t>100000.00</t>
         </is>
       </c>
       <c r="Z153" s="0" t="inlineStr">
@@ -7220,18 +7230,18 @@
         </is>
       </c>
       <c r="AA153" s="0">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="AV153" s="0" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="154" spans="1:48">
       <c r="C154" s="0" t="inlineStr">
         <is>
-          <t>SHERATON HOLLAND PLAIN</t>
+          <t>SHERATON EXCLUSIVE EMBELLISHED</t>
         </is>
       </c>
       <c r="G154" s="0" t="inlineStr">
@@ -7246,7 +7256,7 @@
       </c>
       <c r="R154" s="0" t="inlineStr">
         <is>
-          <t>150000.00</t>
+          <t>244006.0851926978</t>
         </is>
       </c>
       <c r="S154" s="0" t="inlineStr">
@@ -7256,7 +7266,7 @@
       </c>
       <c r="T154" s="0" t="inlineStr">
         <is>
-          <t>180000.00</t>
+          <t>280000.00</t>
         </is>
       </c>
       <c r="Z154" s="0" t="inlineStr">
@@ -7265,18 +7275,18 @@
         </is>
       </c>
       <c r="AA154" s="0">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AV154" s="0" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="155" spans="1:48">
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t>SHERATON SATIN WAX</t>
+          <t>SHERATON EXCLUSIVE PLAIN </t>
         </is>
       </c>
       <c r="G155" s="0" t="inlineStr">
@@ -7291,7 +7301,7 @@
       </c>
       <c r="R155" s="0" t="inlineStr">
         <is>
-          <t>160000.00</t>
+          <t>200000.00</t>
         </is>
       </c>
       <c r="S155" s="0" t="inlineStr">
@@ -7301,7 +7311,7 @@
       </c>
       <c r="T155" s="0" t="inlineStr">
         <is>
-          <t>200000.00</t>
+          <t>220000.00</t>
         </is>
       </c>
       <c r="Z155" s="0" t="inlineStr">
@@ -7310,23 +7320,23 @@
         </is>
       </c>
       <c r="AA155" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV155" s="0" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>71</t>
         </is>
       </c>
     </row>
     <row r="156" spans="1:48">
       <c r="C156" s="0" t="inlineStr">
         <is>
-          <t>SMALL KAMPALA</t>
+          <t>SHERATON HOLLAND EMBELLISHED</t>
         </is>
       </c>
       <c r="G156" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O156" s="0" t="inlineStr">
@@ -7336,7 +7346,7 @@
       </c>
       <c r="R156" s="0" t="inlineStr">
         <is>
-          <t>3500.00</t>
+          <t>210000.00</t>
         </is>
       </c>
       <c r="S156" s="0" t="inlineStr">
@@ -7346,7 +7356,7 @@
       </c>
       <c r="T156" s="0" t="inlineStr">
         <is>
-          <t>4500.00</t>
+          <t>240000.00</t>
         </is>
       </c>
       <c r="Z156" s="0" t="inlineStr">
@@ -7355,23 +7365,23 @@
         </is>
       </c>
       <c r="AA156" s="0">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AV156" s="0" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>74</t>
         </is>
       </c>
     </row>
     <row r="157" spans="1:48">
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t>Sober And Queen VOILE EMBROIDERY </t>
+          <t>SHERATON HOLLAND PLAIN</t>
         </is>
       </c>
       <c r="G157" s="0" t="inlineStr">
         <is>
-          <t>VOILE</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O157" s="0" t="inlineStr">
@@ -7381,7 +7391,7 @@
       </c>
       <c r="R157" s="0" t="inlineStr">
         <is>
-          <t>32000.00</t>
+          <t>150000.00</t>
         </is>
       </c>
       <c r="S157" s="0" t="inlineStr">
@@ -7391,7 +7401,7 @@
       </c>
       <c r="T157" s="0" t="inlineStr">
         <is>
-          <t>40000.00</t>
+          <t>180000.00</t>
         </is>
       </c>
       <c r="Z157" s="0" t="inlineStr">
@@ -7400,23 +7410,23 @@
         </is>
       </c>
       <c r="AA157" s="0">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AV157" s="0" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>75</t>
         </is>
       </c>
     </row>
     <row r="158" spans="1:48">
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t>SOLARI YARD COLLECTION</t>
+          <t>SHERATON SATIN WAX</t>
         </is>
       </c>
       <c r="G158" s="0" t="inlineStr">
         <is>
-          <t>YARD</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O158" s="0" t="inlineStr">
@@ -7426,7 +7436,7 @@
       </c>
       <c r="R158" s="0" t="inlineStr">
         <is>
-          <t>2000.00</t>
+          <t>160000.00</t>
         </is>
       </c>
       <c r="S158" s="0" t="inlineStr">
@@ -7436,7 +7446,7 @@
       </c>
       <c r="T158" s="0" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>200000.00</t>
         </is>
       </c>
       <c r="Z158" s="0" t="inlineStr">
@@ -7445,23 +7455,23 @@
         </is>
       </c>
       <c r="AA158" s="0">
-        <v>542</v>
+        <v>3</v>
       </c>
       <c r="AV158" s="0" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>69</t>
         </is>
       </c>
     </row>
     <row r="159" spans="1:48">
       <c r="C159" s="0" t="inlineStr">
         <is>
-          <t>STONE EMBELLISHED MIX ND MATCH</t>
+          <t>SMALL KAMPALA</t>
         </is>
       </c>
       <c r="G159" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O159" s="0" t="inlineStr">
@@ -7471,7 +7481,7 @@
       </c>
       <c r="R159" s="0" t="inlineStr">
         <is>
-          <t>17000.00</t>
+          <t>3500.00</t>
         </is>
       </c>
       <c r="S159" s="0" t="inlineStr">
@@ -7481,7 +7491,7 @@
       </c>
       <c r="T159" s="0" t="inlineStr">
         <is>
-          <t>19000.00</t>
+          <t>4500.00</t>
         </is>
       </c>
       <c r="Z159" s="0" t="inlineStr">
@@ -7490,23 +7500,23 @@
         </is>
       </c>
       <c r="AA159" s="0">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AV159" s="0" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>154</t>
         </is>
       </c>
     </row>
     <row r="160" spans="1:48">
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t>SUBLIME COTED'VIORE</t>
+          <t>Sober And Queen VOILE EMBROIDERY </t>
         </is>
       </c>
       <c r="G160" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>VOILE</t>
         </is>
       </c>
       <c r="O160" s="0" t="inlineStr">
@@ -7516,7 +7526,7 @@
       </c>
       <c r="R160" s="0" t="inlineStr">
         <is>
-          <t>18500.00</t>
+          <t>32000.00</t>
         </is>
       </c>
       <c r="S160" s="0" t="inlineStr">
@@ -7526,7 +7536,7 @@
       </c>
       <c r="T160" s="0" t="inlineStr">
         <is>
-          <t>20000.00</t>
+          <t>40000.00</t>
         </is>
       </c>
       <c r="Z160" s="0" t="inlineStr">
@@ -7535,23 +7545,23 @@
         </is>
       </c>
       <c r="AA160" s="0">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AV160" s="0" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="161" spans="1:48">
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t>SUBLIME STONE EMBELLISHED</t>
+          <t>SOLARI YARD COLLECTION</t>
         </is>
       </c>
       <c r="G161" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>YARD</t>
         </is>
       </c>
       <c r="O161" s="0" t="inlineStr">
@@ -7561,7 +7571,7 @@
       </c>
       <c r="R161" s="0" t="inlineStr">
         <is>
-          <t>18000.00</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="S161" s="0" t="inlineStr">
@@ -7571,7 +7581,7 @@
       </c>
       <c r="T161" s="0" t="inlineStr">
         <is>
-          <t>20000.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="Z161" s="0" t="inlineStr">
@@ -7580,18 +7590,18 @@
         </is>
       </c>
       <c r="AA161" s="0">
-        <v>146</v>
+        <v>542</v>
       </c>
       <c r="AV161" s="0" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>190</t>
         </is>
       </c>
     </row>
     <row r="162" spans="1:48">
       <c r="C162" s="0" t="inlineStr">
         <is>
-          <t>SUPER BRILLIANT </t>
+          <t>STONE EMBELLISHED MIX ND MATCH</t>
         </is>
       </c>
       <c r="G162" s="0" t="inlineStr">
@@ -7606,7 +7616,7 @@
       </c>
       <c r="R162" s="0" t="inlineStr">
         <is>
-          <t>11000.00</t>
+          <t>17000.00</t>
         </is>
       </c>
       <c r="S162" s="0" t="inlineStr">
@@ -7616,7 +7626,7 @@
       </c>
       <c r="T162" s="0" t="inlineStr">
         <is>
-          <t>12000.00</t>
+          <t>19000.00</t>
         </is>
       </c>
       <c r="Z162" s="0" t="inlineStr">
@@ -7625,18 +7635,18 @@
         </is>
       </c>
       <c r="AA162" s="0">
-        <v>95</v>
+        <v>7</v>
       </c>
       <c r="AV162" s="0" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>112</t>
         </is>
       </c>
     </row>
     <row r="163" spans="1:48">
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t>SUPER FAMOUS</t>
+          <t>SUBLIME COTED'VIORE</t>
         </is>
       </c>
       <c r="G163" s="0" t="inlineStr">
@@ -7651,7 +7661,7 @@
       </c>
       <c r="R163" s="0" t="inlineStr">
         <is>
-          <t>9004.0120613707</t>
+          <t>18500.00</t>
         </is>
       </c>
       <c r="S163" s="0" t="inlineStr">
@@ -7661,7 +7671,7 @@
       </c>
       <c r="T163" s="0" t="inlineStr">
         <is>
-          <t>10000.00</t>
+          <t>20000.00</t>
         </is>
       </c>
       <c r="Z163" s="0" t="inlineStr">
@@ -7670,18 +7680,18 @@
         </is>
       </c>
       <c r="AA163" s="0">
-        <v>176</v>
+        <v>14</v>
       </c>
       <c r="AV163" s="0" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>108</t>
         </is>
       </c>
     </row>
     <row r="164" spans="1:48">
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>SUPER FASHION</t>
+          <t>SUBLIME STONE EMBELLISHED</t>
         </is>
       </c>
       <c r="G164" s="0" t="inlineStr">
@@ -7696,7 +7706,7 @@
       </c>
       <c r="R164" s="0" t="inlineStr">
         <is>
-          <t>10007.5373258309</t>
+          <t>18000.00</t>
         </is>
       </c>
       <c r="S164" s="0" t="inlineStr">
@@ -7706,7 +7716,7 @@
       </c>
       <c r="T164" s="0" t="inlineStr">
         <is>
-          <t>11000.00</t>
+          <t>20000.00</t>
         </is>
       </c>
       <c r="Z164" s="0" t="inlineStr">
@@ -7715,18 +7725,18 @@
         </is>
       </c>
       <c r="AA164" s="0">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="AV164" s="0" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>95</t>
         </is>
       </c>
     </row>
     <row r="165" spans="1:48">
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>SUPER HOLLAND EMBELLISHED</t>
+          <t>SUPER BRILLIANT </t>
         </is>
       </c>
       <c r="G165" s="0" t="inlineStr">
@@ -7741,7 +7751,7 @@
       </c>
       <c r="R165" s="0" t="inlineStr">
         <is>
-          <t>220000.00</t>
+          <t>11000.00</t>
         </is>
       </c>
       <c r="S165" s="0" t="inlineStr">
@@ -7751,7 +7761,7 @@
       </c>
       <c r="T165" s="0" t="inlineStr">
         <is>
-          <t>250000.00</t>
+          <t>12000.00</t>
         </is>
       </c>
       <c r="Z165" s="0" t="inlineStr">
@@ -7760,18 +7770,18 @@
         </is>
       </c>
       <c r="AA165" s="0">
-        <v>7</v>
+        <v>86</v>
       </c>
       <c r="AV165" s="0" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>127</t>
         </is>
       </c>
     </row>
     <row r="166" spans="1:48">
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>SUPER HOLLAND WAX</t>
+          <t>SUPER FAMOUS</t>
         </is>
       </c>
       <c r="G166" s="0" t="inlineStr">
@@ -7786,7 +7796,7 @@
       </c>
       <c r="R166" s="0" t="inlineStr">
         <is>
-          <t>166021.934602301</t>
+          <t>9003.4277805886</t>
         </is>
       </c>
       <c r="S166" s="0" t="inlineStr">
@@ -7796,7 +7806,7 @@
       </c>
       <c r="T166" s="0" t="inlineStr">
         <is>
-          <t>195000.00</t>
+          <t>10000.00</t>
         </is>
       </c>
       <c r="Z166" s="0" t="inlineStr">
@@ -7805,18 +7815,18 @@
         </is>
       </c>
       <c r="AA166" s="0">
-        <v>33</v>
+        <v>158</v>
       </c>
       <c r="AV166" s="0" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>137</t>
         </is>
       </c>
     </row>
     <row r="167" spans="1:48">
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t>SUPER WAX EMBELLISHED 4YRDS</t>
+          <t>SUPER FASHION</t>
         </is>
       </c>
       <c r="G167" s="0" t="inlineStr">
@@ -7831,7 +7841,7 @@
       </c>
       <c r="R167" s="0" t="inlineStr">
         <is>
-          <t>100000.00</t>
+          <t>10007.5373258309</t>
         </is>
       </c>
       <c r="S167" s="0" t="inlineStr">
@@ -7841,7 +7851,7 @@
       </c>
       <c r="T167" s="0" t="inlineStr">
         <is>
-          <t>120000.00</t>
+          <t>11000.00</t>
         </is>
       </c>
       <c r="Z167" s="0" t="inlineStr">
@@ -7850,18 +7860,18 @@
         </is>
       </c>
       <c r="AA167" s="0">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="AV167" s="0" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>128</t>
         </is>
       </c>
     </row>
     <row r="168" spans="1:48">
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>SUPER WAX MEDIUM</t>
+          <t>SUPER HOLLAND EMBELLISHED</t>
         </is>
       </c>
       <c r="G168" s="0" t="inlineStr">
@@ -7876,7 +7886,7 @@
       </c>
       <c r="R168" s="0" t="inlineStr">
         <is>
-          <t>14500.00</t>
+          <t>220000.00</t>
         </is>
       </c>
       <c r="S168" s="0" t="inlineStr">
@@ -7886,7 +7896,7 @@
       </c>
       <c r="T168" s="0" t="inlineStr">
         <is>
-          <t>16000.00</t>
+          <t>250000.00</t>
         </is>
       </c>
       <c r="Z168" s="0" t="inlineStr">
@@ -7895,23 +7905,23 @@
         </is>
       </c>
       <c r="AA168" s="0">
-        <v>217</v>
+        <v>4</v>
       </c>
       <c r="AV168" s="0" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>73</t>
         </is>
       </c>
     </row>
     <row r="169" spans="1:48">
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t>SUPREME PHANTOM</t>
+          <t>SUPER HOLLAND WAX</t>
         </is>
       </c>
       <c r="G169" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O169" s="0" t="inlineStr">
@@ -7921,7 +7931,7 @@
       </c>
       <c r="R169" s="0" t="inlineStr">
         <is>
-          <t>5500.00</t>
+          <t>165381.0572182089</t>
         </is>
       </c>
       <c r="S169" s="0" t="inlineStr">
@@ -7931,7 +7941,7 @@
       </c>
       <c r="T169" s="0" t="inlineStr">
         <is>
-          <t>7500.00</t>
+          <t>195000.00</t>
         </is>
       </c>
       <c r="Z169" s="0" t="inlineStr">
@@ -7940,23 +7950,23 @@
         </is>
       </c>
       <c r="AA169" s="0">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="AV169" s="0" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="170" spans="1:48">
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t>SWISS LACE A</t>
+          <t>SUPER WAX EMBELLISHED 4YRDS</t>
         </is>
       </c>
       <c r="G170" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O170" s="0" t="inlineStr">
@@ -7966,7 +7976,7 @@
       </c>
       <c r="R170" s="0" t="inlineStr">
         <is>
-          <t>85078.125</t>
+          <t>100000.00</t>
         </is>
       </c>
       <c r="S170" s="0" t="inlineStr">
@@ -7976,7 +7986,7 @@
       </c>
       <c r="T170" s="0" t="inlineStr">
         <is>
-          <t>100000.00</t>
+          <t>120000.00</t>
         </is>
       </c>
       <c r="Z170" s="0" t="inlineStr">
@@ -7985,23 +7995,23 @@
         </is>
       </c>
       <c r="AA170" s="0">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AV170" s="0" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="171" spans="1:48">
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t>SWISS LACE B</t>
+          <t>SUPER WAX MEDIUM</t>
         </is>
       </c>
       <c r="G171" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O171" s="0" t="inlineStr">
@@ -8011,7 +8021,7 @@
       </c>
       <c r="R171" s="0" t="inlineStr">
         <is>
-          <t>74273.9898989899</t>
+          <t>14500.00</t>
         </is>
       </c>
       <c r="S171" s="0" t="inlineStr">
@@ -8021,7 +8031,7 @@
       </c>
       <c r="T171" s="0" t="inlineStr">
         <is>
-          <t>85000.00</t>
+          <t>16000.00</t>
         </is>
       </c>
       <c r="Z171" s="0" t="inlineStr">
@@ -8030,23 +8040,23 @@
         </is>
       </c>
       <c r="AA171" s="0">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="AV171" s="0" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>119</t>
         </is>
       </c>
     </row>
     <row r="172" spans="1:48">
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>SWISS LACE B</t>
+          <t>SUPREME PHANTOM</t>
         </is>
       </c>
       <c r="G172" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O172" s="0" t="inlineStr">
@@ -8056,7 +8066,7 @@
       </c>
       <c r="R172" s="0" t="inlineStr">
         <is>
-          <t>75391.3043478261</t>
+          <t>5500.00</t>
         </is>
       </c>
       <c r="S172" s="0" t="inlineStr">
@@ -8066,7 +8076,7 @@
       </c>
       <c r="T172" s="0" t="inlineStr">
         <is>
-          <t>85000.00</t>
+          <t>7500.00</t>
         </is>
       </c>
       <c r="Z172" s="0" t="inlineStr">
@@ -8075,18 +8085,18 @@
         </is>
       </c>
       <c r="AA172" s="0">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="AV172" s="0" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>176</t>
         </is>
       </c>
     </row>
     <row r="173" spans="1:48">
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>SWISS LACE C</t>
+          <t>SWISS LACE A</t>
         </is>
       </c>
       <c r="G173" s="0" t="inlineStr">
@@ -8101,7 +8111,7 @@
       </c>
       <c r="R173" s="0" t="inlineStr">
         <is>
-          <t>67000.00</t>
+          <t>85078.125</t>
         </is>
       </c>
       <c r="S173" s="0" t="inlineStr">
@@ -8111,7 +8121,7 @@
       </c>
       <c r="T173" s="0" t="inlineStr">
         <is>
-          <t>75000.00</t>
+          <t>100000.00</t>
         </is>
       </c>
       <c r="Z173" s="0" t="inlineStr">
@@ -8120,18 +8130,18 @@
         </is>
       </c>
       <c r="AA173" s="0">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV173" s="0" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="174" spans="1:48">
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>SWISS LACE D</t>
+          <t>SWISS LACE B</t>
         </is>
       </c>
       <c r="G174" s="0" t="inlineStr">
@@ -8146,7 +8156,7 @@
       </c>
       <c r="R174" s="0" t="inlineStr">
         <is>
-          <t>53000.00</t>
+          <t>74273.9898989899</t>
         </is>
       </c>
       <c r="S174" s="0" t="inlineStr">
@@ -8156,7 +8166,7 @@
       </c>
       <c r="T174" s="0" t="inlineStr">
         <is>
-          <t>65000.00</t>
+          <t>85000.00</t>
         </is>
       </c>
       <c r="Z174" s="0" t="inlineStr">
@@ -8165,23 +8175,23 @@
         </is>
       </c>
       <c r="AA174" s="0">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AV174" s="0" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="175" spans="1:48">
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t>SWISS LAFAYA A</t>
+          <t>SWISS LACE B</t>
         </is>
       </c>
       <c r="G175" s="0" t="inlineStr">
         <is>
-          <t>LAFAYYA</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O175" s="0" t="inlineStr">
@@ -8191,7 +8201,7 @@
       </c>
       <c r="R175" s="0" t="inlineStr">
         <is>
-          <t>45000.00</t>
+          <t>75391.3043478261</t>
         </is>
       </c>
       <c r="S175" s="0" t="inlineStr">
@@ -8201,7 +8211,7 @@
       </c>
       <c r="T175" s="0" t="inlineStr">
         <is>
-          <t>60000.00</t>
+          <t>85000.00</t>
         </is>
       </c>
       <c r="Z175" s="0" t="inlineStr">
@@ -8210,23 +8220,23 @@
         </is>
       </c>
       <c r="AA175" s="0">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="AV175" s="0" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>161</t>
         </is>
       </c>
     </row>
     <row r="176" spans="1:48">
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t>SWISS LAFAYA B</t>
+          <t>SWISS LACE C</t>
         </is>
       </c>
       <c r="G176" s="0" t="inlineStr">
         <is>
-          <t>LAFAYYA</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O176" s="0" t="inlineStr">
@@ -8236,7 +8246,7 @@
       </c>
       <c r="R176" s="0" t="inlineStr">
         <is>
-          <t>48000.00</t>
+          <t>67000.00</t>
         </is>
       </c>
       <c r="S176" s="0" t="inlineStr">
@@ -8246,7 +8256,7 @@
       </c>
       <c r="T176" s="0" t="inlineStr">
         <is>
-          <t>55000.00</t>
+          <t>75000.00</t>
         </is>
       </c>
       <c r="Z176" s="0" t="inlineStr">
@@ -8255,23 +8265,23 @@
         </is>
       </c>
       <c r="AA176" s="0">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AV176" s="0" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="177" spans="1:48">
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t>SWISS LAFAYA C</t>
+          <t>SWISS LACE D</t>
         </is>
       </c>
       <c r="G177" s="0" t="inlineStr">
         <is>
-          <t>LAFAYYA</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O177" s="0" t="inlineStr">
@@ -8281,7 +8291,7 @@
       </c>
       <c r="R177" s="0" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>53000.00</t>
         </is>
       </c>
       <c r="S177" s="0" t="inlineStr">
@@ -8291,7 +8301,7 @@
       </c>
       <c r="T177" s="0" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>65000.00</t>
         </is>
       </c>
       <c r="Z177" s="0" t="inlineStr">
@@ -8299,16 +8309,19 @@
           <t>n</t>
         </is>
       </c>
+      <c r="AA177" s="0">
+        <v>10</v>
+      </c>
       <c r="AV177" s="0" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="178" spans="1:48">
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t>SWISS LAFAYA C</t>
+          <t>SWISS LAFAYA A</t>
         </is>
       </c>
       <c r="G178" s="0" t="inlineStr">
@@ -8323,7 +8336,7 @@
       </c>
       <c r="R178" s="0" t="inlineStr">
         <is>
-          <t>36000.00</t>
+          <t>45000.00</t>
         </is>
       </c>
       <c r="S178" s="0" t="inlineStr">
@@ -8333,7 +8346,7 @@
       </c>
       <c r="T178" s="0" t="inlineStr">
         <is>
-          <t>45000.00</t>
+          <t>60000.00</t>
         </is>
       </c>
       <c r="Z178" s="0" t="inlineStr">
@@ -8342,23 +8355,23 @@
         </is>
       </c>
       <c r="AA178" s="0">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="AV178" s="0" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="179" spans="1:48">
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY LACE A</t>
+          <t>SWISS LAFAYA B</t>
         </is>
       </c>
       <c r="G179" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>LAFAYYA</t>
         </is>
       </c>
       <c r="O179" s="0" t="inlineStr">
@@ -8368,7 +8381,7 @@
       </c>
       <c r="R179" s="0" t="inlineStr">
         <is>
-          <t>120000.00</t>
+          <t>48000.00</t>
         </is>
       </c>
       <c r="S179" s="0" t="inlineStr">
@@ -8378,7 +8391,7 @@
       </c>
       <c r="T179" s="0" t="inlineStr">
         <is>
-          <t>135000.00</t>
+          <t>55000.00</t>
         </is>
       </c>
       <c r="Z179" s="0" t="inlineStr">
@@ -8387,28 +8400,23 @@
         </is>
       </c>
       <c r="AA179" s="0">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AV179" s="0" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="180" spans="1:48">
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t>Swiss luxury lace Aplus</t>
+          <t>SWISS LAFAYA C</t>
         </is>
       </c>
       <c r="G180" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
-        </is>
-      </c>
-      <c r="H180" s="0" t="inlineStr">
-        <is>
-          <t>FAHAD TAHIR</t>
+          <t>LAFAYYA</t>
         </is>
       </c>
       <c r="O180" s="0" t="inlineStr">
@@ -8418,7 +8426,7 @@
       </c>
       <c r="R180" s="0" t="inlineStr">
         <is>
-          <t>130000.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S180" s="0" t="inlineStr">
@@ -8428,7 +8436,7 @@
       </c>
       <c r="T180" s="0" t="inlineStr">
         <is>
-          <t>165000.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Z180" s="0" t="inlineStr">
@@ -8436,24 +8444,21 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA180" s="0">
-        <v>0</v>
-      </c>
       <c r="AV180" s="0" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="181" spans="1:48">
       <c r="C181" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY LACE B</t>
+          <t>SWISS LAFAYA C</t>
         </is>
       </c>
       <c r="G181" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>LAFAYYA</t>
         </is>
       </c>
       <c r="O181" s="0" t="inlineStr">
@@ -8463,7 +8468,7 @@
       </c>
       <c r="R181" s="0" t="inlineStr">
         <is>
-          <t>117202.7972027972</t>
+          <t>36000.00</t>
         </is>
       </c>
       <c r="S181" s="0" t="inlineStr">
@@ -8473,7 +8478,7 @@
       </c>
       <c r="T181" s="0" t="inlineStr">
         <is>
-          <t>130000.00</t>
+          <t>45000.00</t>
         </is>
       </c>
       <c r="Z181" s="0" t="inlineStr">
@@ -8482,18 +8487,18 @@
         </is>
       </c>
       <c r="AA181" s="0">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AV181" s="0" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="182" spans="1:48">
       <c r="C182" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY LACE BIG A</t>
+          <t>SWISS LUXURY LACE A</t>
         </is>
       </c>
       <c r="G182" s="0" t="inlineStr">
@@ -8508,7 +8513,7 @@
       </c>
       <c r="R182" s="0" t="inlineStr">
         <is>
-          <t>220000.00</t>
+          <t>120000.00</t>
         </is>
       </c>
       <c r="S182" s="0" t="inlineStr">
@@ -8518,7 +8523,7 @@
       </c>
       <c r="T182" s="0" t="inlineStr">
         <is>
-          <t>270000.00</t>
+          <t>135000.00</t>
         </is>
       </c>
       <c r="Z182" s="0" t="inlineStr">
@@ -8527,18 +8532,18 @@
         </is>
       </c>
       <c r="AA182" s="0">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AV182" s="0" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="183" spans="1:48">
       <c r="C183" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY LACE BIG B</t>
+          <t>Swiss luxury lace Aplus</t>
         </is>
       </c>
       <c r="G183" s="0" t="inlineStr">
@@ -8546,6 +8551,11 @@
           <t>LACE</t>
         </is>
       </c>
+      <c r="H183" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
+        </is>
+      </c>
       <c r="O183" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -8553,7 +8563,7 @@
       </c>
       <c r="R183" s="0" t="inlineStr">
         <is>
-          <t>200000.00</t>
+          <t>130000.00</t>
         </is>
       </c>
       <c r="S183" s="0" t="inlineStr">
@@ -8563,7 +8573,7 @@
       </c>
       <c r="T183" s="0" t="inlineStr">
         <is>
-          <t>250000.00</t>
+          <t>165000.00</t>
         </is>
       </c>
       <c r="Z183" s="0" t="inlineStr">
@@ -8576,14 +8586,14 @@
       </c>
       <c r="AV183" s="0" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>198</t>
         </is>
       </c>
     </row>
     <row r="184" spans="1:48">
       <c r="C184" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY LACE BIG C</t>
+          <t>SWISS LUXURY LACE B</t>
         </is>
       </c>
       <c r="G184" s="0" t="inlineStr">
@@ -8598,7 +8608,7 @@
       </c>
       <c r="R184" s="0" t="inlineStr">
         <is>
-          <t>180000.00</t>
+          <t>117202.7972027972</t>
         </is>
       </c>
       <c r="S184" s="0" t="inlineStr">
@@ -8608,7 +8618,7 @@
       </c>
       <c r="T184" s="0" t="inlineStr">
         <is>
-          <t>230000.00</t>
+          <t>130000.00</t>
         </is>
       </c>
       <c r="Z184" s="0" t="inlineStr">
@@ -8617,18 +8627,18 @@
         </is>
       </c>
       <c r="AA184" s="0">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AV184" s="0" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="185" spans="1:48">
       <c r="C185" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY LACE BIG D </t>
+          <t>SWISS LUXURY LACE BIG A</t>
         </is>
       </c>
       <c r="G185" s="0" t="inlineStr">
@@ -8643,7 +8653,7 @@
       </c>
       <c r="R185" s="0" t="inlineStr">
         <is>
-          <t>123750.00</t>
+          <t>220000.00</t>
         </is>
       </c>
       <c r="S185" s="0" t="inlineStr">
@@ -8653,7 +8663,7 @@
       </c>
       <c r="T185" s="0" t="inlineStr">
         <is>
-          <t>200000.00</t>
+          <t>270000.00</t>
         </is>
       </c>
       <c r="Z185" s="0" t="inlineStr">
@@ -8662,18 +8672,18 @@
         </is>
       </c>
       <c r="AA185" s="0">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AV185" s="0" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="186" spans="1:48">
       <c r="C186" s="0" t="inlineStr">
         <is>
-          <t>Swiss luxury lace Bplus</t>
+          <t>SWISS LUXURY LACE BIG B</t>
         </is>
       </c>
       <c r="G186" s="0" t="inlineStr">
@@ -8681,11 +8691,6 @@
           <t>LACE</t>
         </is>
       </c>
-      <c r="H186" s="0" t="inlineStr">
-        <is>
-          <t>FAHAD TAHIR</t>
-        </is>
-      </c>
       <c r="O186" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -8693,7 +8698,7 @@
       </c>
       <c r="R186" s="0" t="inlineStr">
         <is>
-          <t>120000.00</t>
+          <t>180000.00</t>
         </is>
       </c>
       <c r="S186" s="0" t="inlineStr">
@@ -8703,7 +8708,7 @@
       </c>
       <c r="T186" s="0" t="inlineStr">
         <is>
-          <t>140000.00</t>
+          <t>250000.00</t>
         </is>
       </c>
       <c r="Z186" s="0" t="inlineStr">
@@ -8712,18 +8717,18 @@
         </is>
       </c>
       <c r="AA186" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV186" s="0" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="187" spans="1:48">
       <c r="C187" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY LACE C</t>
+          <t>SWISS LUXURY LACE BIG C</t>
         </is>
       </c>
       <c r="G187" s="0" t="inlineStr">
@@ -8738,7 +8743,7 @@
       </c>
       <c r="R187" s="0" t="inlineStr">
         <is>
-          <t>106000.00</t>
+          <t>180000.00</t>
         </is>
       </c>
       <c r="S187" s="0" t="inlineStr">
@@ -8748,7 +8753,7 @@
       </c>
       <c r="T187" s="0" t="inlineStr">
         <is>
-          <t>120000.00</t>
+          <t>230000.00</t>
         </is>
       </c>
       <c r="Z187" s="0" t="inlineStr">
@@ -8757,18 +8762,18 @@
         </is>
       </c>
       <c r="AA187" s="0">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AV187" s="0" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="188" spans="1:48">
       <c r="C188" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY LACE D</t>
+          <t>SWISS LUXURY LACE BIG D </t>
         </is>
       </c>
       <c r="G188" s="0" t="inlineStr">
@@ -8783,7 +8788,7 @@
       </c>
       <c r="R188" s="0" t="inlineStr">
         <is>
-          <t>98164.3888673712</t>
+          <t>123750.00</t>
         </is>
       </c>
       <c r="S188" s="0" t="inlineStr">
@@ -8793,7 +8798,7 @@
       </c>
       <c r="T188" s="0" t="inlineStr">
         <is>
-          <t>110000.00</t>
+          <t>200000.00</t>
         </is>
       </c>
       <c r="Z188" s="0" t="inlineStr">
@@ -8802,23 +8807,28 @@
         </is>
       </c>
       <c r="AA188" s="0">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="AV188" s="0" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="189" spans="1:48">
       <c r="C189" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY VOILE</t>
+          <t>Swiss luxury lace Bplus</t>
         </is>
       </c>
       <c r="G189" s="0" t="inlineStr">
         <is>
-          <t>VOILE</t>
+          <t>LACE</t>
+        </is>
+      </c>
+      <c r="H189" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
         </is>
       </c>
       <c r="O189" s="0" t="inlineStr">
@@ -8828,7 +8838,7 @@
       </c>
       <c r="R189" s="0" t="inlineStr">
         <is>
-          <t>48656.00</t>
+          <t>120000.00</t>
         </is>
       </c>
       <c r="S189" s="0" t="inlineStr">
@@ -8838,7 +8848,7 @@
       </c>
       <c r="T189" s="0" t="inlineStr">
         <is>
-          <t>65000.00</t>
+          <t>140000.00</t>
         </is>
       </c>
       <c r="Z189" s="0" t="inlineStr">
@@ -8847,18 +8857,18 @@
         </is>
       </c>
       <c r="AA189" s="0">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="AV189" s="0" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="190" spans="1:48">
       <c r="C190" s="0" t="inlineStr">
         <is>
-          <t>SWISS VOILE LACE A</t>
+          <t>SWISS LUXURY LACE C</t>
         </is>
       </c>
       <c r="G190" s="0" t="inlineStr">
@@ -8873,7 +8883,7 @@
       </c>
       <c r="R190" s="0" t="inlineStr">
         <is>
-          <t>150000.00</t>
+          <t>106000.00</t>
         </is>
       </c>
       <c r="S190" s="0" t="inlineStr">
@@ -8883,7 +8893,7 @@
       </c>
       <c r="T190" s="0" t="inlineStr">
         <is>
-          <t>280000.00</t>
+          <t>120000.00</t>
         </is>
       </c>
       <c r="Z190" s="0" t="inlineStr">
@@ -8896,14 +8906,14 @@
       </c>
       <c r="AV190" s="0" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="191" spans="1:48">
       <c r="C191" s="0" t="inlineStr">
         <is>
-          <t>SWISS VOILE LACE B</t>
+          <t>SWISS LUXURY LACE D</t>
         </is>
       </c>
       <c r="G191" s="0" t="inlineStr">
@@ -8918,7 +8928,7 @@
       </c>
       <c r="R191" s="0" t="inlineStr">
         <is>
-          <t>135000.00</t>
+          <t>98164.3888673712</t>
         </is>
       </c>
       <c r="S191" s="0" t="inlineStr">
@@ -8928,7 +8938,7 @@
       </c>
       <c r="T191" s="0" t="inlineStr">
         <is>
-          <t>180000.00</t>
+          <t>110000.00</t>
         </is>
       </c>
       <c r="Z191" s="0" t="inlineStr">
@@ -8937,23 +8947,23 @@
         </is>
       </c>
       <c r="AA191" s="0">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="AV191" s="0" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="192" spans="1:48">
       <c r="C192" s="0" t="inlineStr">
         <is>
-          <t>TYCOON AND GAZA WOOL</t>
+          <t>SWISS LUXURY VOILE</t>
         </is>
       </c>
       <c r="G192" s="0" t="inlineStr">
         <is>
-          <t>YARD</t>
+          <t>VOILE</t>
         </is>
       </c>
       <c r="O192" s="0" t="inlineStr">
@@ -8963,7 +8973,7 @@
       </c>
       <c r="R192" s="0" t="inlineStr">
         <is>
-          <t>4000.00</t>
+          <t>48656.00</t>
         </is>
       </c>
       <c r="S192" s="0" t="inlineStr">
@@ -8973,7 +8983,7 @@
       </c>
       <c r="T192" s="0" t="inlineStr">
         <is>
-          <t>5000.00</t>
+          <t>65000.00</t>
         </is>
       </c>
       <c r="Z192" s="0" t="inlineStr">
@@ -8982,18 +8992,18 @@
         </is>
       </c>
       <c r="AA192" s="0">
-        <v>632</v>
+        <v>53</v>
       </c>
       <c r="AV192" s="0" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="193" spans="1:48">
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t>ULTRA SWISS LACE A</t>
+          <t>SWISS VOILE LACE A</t>
         </is>
       </c>
       <c r="G193" s="0" t="inlineStr">
@@ -9008,7 +9018,7 @@
       </c>
       <c r="R193" s="0" t="inlineStr">
         <is>
-          <t>300000.00</t>
+          <t>150000.00</t>
         </is>
       </c>
       <c r="S193" s="0" t="inlineStr">
@@ -9018,7 +9028,7 @@
       </c>
       <c r="T193" s="0" t="inlineStr">
         <is>
-          <t>380000.00</t>
+          <t>280000.00</t>
         </is>
       </c>
       <c r="Z193" s="0" t="inlineStr">
@@ -9027,18 +9037,18 @@
         </is>
       </c>
       <c r="AA193" s="0">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV193" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="194" spans="1:48">
       <c r="C194" s="0" t="inlineStr">
         <is>
-          <t>ULTRA SWISS LACE B</t>
+          <t>SWISS VOILE LACE B</t>
         </is>
       </c>
       <c r="G194" s="0" t="inlineStr">
@@ -9053,7 +9063,7 @@
       </c>
       <c r="R194" s="0" t="inlineStr">
         <is>
-          <t>250000.00</t>
+          <t>135000.00</t>
         </is>
       </c>
       <c r="S194" s="0" t="inlineStr">
@@ -9063,7 +9073,7 @@
       </c>
       <c r="T194" s="0" t="inlineStr">
         <is>
-          <t>350000.00</t>
+          <t>180000.00</t>
         </is>
       </c>
       <c r="Z194" s="0" t="inlineStr">
@@ -9072,23 +9082,28 @@
         </is>
       </c>
       <c r="AA194" s="0">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="AV194" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="195" spans="1:48">
       <c r="C195" s="0" t="inlineStr">
         <is>
-          <t>ULTRA SWISS LACE C</t>
+          <t>Two Color Mesh Lace</t>
         </is>
       </c>
       <c r="G195" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="H195" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
         </is>
       </c>
       <c r="O195" s="0" t="inlineStr">
@@ -9098,7 +9113,7 @@
       </c>
       <c r="R195" s="0" t="inlineStr">
         <is>
-          <t>253214.2857142857</t>
+          <t>190000.00</t>
         </is>
       </c>
       <c r="S195" s="0" t="inlineStr">
@@ -9108,7 +9123,7 @@
       </c>
       <c r="T195" s="0" t="inlineStr">
         <is>
-          <t>320000.00</t>
+          <t>300000.00</t>
         </is>
       </c>
       <c r="Z195" s="0" t="inlineStr">
@@ -9117,23 +9132,23 @@
         </is>
       </c>
       <c r="AA195" s="0">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="AV195" s="0" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>218</t>
         </is>
       </c>
     </row>
     <row r="196" spans="1:48">
       <c r="C196" s="0" t="inlineStr">
         <is>
-          <t>ULTRA SWISS LACE D</t>
+          <t>TYCOON AND GAZA WOOL</t>
         </is>
       </c>
       <c r="G196" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>YARD</t>
         </is>
       </c>
       <c r="O196" s="0" t="inlineStr">
@@ -9143,7 +9158,7 @@
       </c>
       <c r="R196" s="0" t="inlineStr">
         <is>
-          <t>230000.00</t>
+          <t>4000.00</t>
         </is>
       </c>
       <c r="S196" s="0" t="inlineStr">
@@ -9153,7 +9168,7 @@
       </c>
       <c r="T196" s="0" t="inlineStr">
         <is>
-          <t>300000.00</t>
+          <t>5000.00</t>
         </is>
       </c>
       <c r="Z196" s="0" t="inlineStr">
@@ -9162,23 +9177,23 @@
         </is>
       </c>
       <c r="AA196" s="0">
-        <v>9</v>
+        <v>598</v>
       </c>
       <c r="AV196" s="0" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>187</t>
         </is>
       </c>
     </row>
     <row r="197" spans="1:48">
       <c r="C197" s="0" t="inlineStr">
         <is>
-          <t>VALANTINO</t>
+          <t>ULTRA SWISS LACE A</t>
         </is>
       </c>
       <c r="G197" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O197" s="0" t="inlineStr">
@@ -9188,7 +9203,7 @@
       </c>
       <c r="R197" s="0" t="inlineStr">
         <is>
-          <t>10070.8693671806</t>
+          <t>300000.00</t>
         </is>
       </c>
       <c r="S197" s="0" t="inlineStr">
@@ -9198,7 +9213,7 @@
       </c>
       <c r="T197" s="0" t="inlineStr">
         <is>
-          <t>11000.00</t>
+          <t>380000.00</t>
         </is>
       </c>
       <c r="Z197" s="0" t="inlineStr">
@@ -9207,23 +9222,23 @@
         </is>
       </c>
       <c r="AA197" s="0">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AV197" s="0" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="198" spans="1:48">
       <c r="C198" s="0" t="inlineStr">
         <is>
-          <t>VALANTINO HOLLAND</t>
+          <t>ULTRA SWISS LACE B</t>
         </is>
       </c>
       <c r="G198" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O198" s="0" t="inlineStr">
@@ -9233,7 +9248,7 @@
       </c>
       <c r="R198" s="0" t="inlineStr">
         <is>
-          <t>10500.00</t>
+          <t>250000.00</t>
         </is>
       </c>
       <c r="S198" s="0" t="inlineStr">
@@ -9243,7 +9258,7 @@
       </c>
       <c r="T198" s="0" t="inlineStr">
         <is>
-          <t>11000.00</t>
+          <t>350000.00</t>
         </is>
       </c>
       <c r="Z198" s="0" t="inlineStr">
@@ -9252,28 +9267,23 @@
         </is>
       </c>
       <c r="AA198" s="0">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AV198" s="0" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="199" spans="1:48">
       <c r="C199" s="0" t="inlineStr">
         <is>
-          <t>Vibes Metallic Cotton Satin</t>
+          <t>ULTRA SWISS LACE C</t>
         </is>
       </c>
       <c r="G199" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
-        </is>
-      </c>
-      <c r="H199" s="0" t="inlineStr">
-        <is>
-          <t>FAHAD TAHIR</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O199" s="0" t="inlineStr">
@@ -9283,7 +9293,7 @@
       </c>
       <c r="R199" s="0" t="inlineStr">
         <is>
-          <t>29000.00</t>
+          <t>253214.2857142857</t>
         </is>
       </c>
       <c r="S199" s="0" t="inlineStr">
@@ -9293,7 +9303,7 @@
       </c>
       <c r="T199" s="0" t="inlineStr">
         <is>
-          <t>35000.00</t>
+          <t>320000.00</t>
         </is>
       </c>
       <c r="Z199" s="0" t="inlineStr">
@@ -9302,23 +9312,23 @@
         </is>
       </c>
       <c r="AA199" s="0">
-        <v>332</v>
+        <v>28</v>
       </c>
       <c r="AV199" s="0" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="200" spans="1:48">
       <c r="C200" s="0" t="inlineStr">
         <is>
-          <t>VICE CHAIRMAN</t>
+          <t>ULTRA SWISS LACE D</t>
         </is>
       </c>
       <c r="G200" s="0" t="inlineStr">
         <is>
-          <t>YARD</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O200" s="0" t="inlineStr">
@@ -9328,7 +9338,7 @@
       </c>
       <c r="R200" s="0" t="inlineStr">
         <is>
-          <t>8151.5151515152</t>
+          <t>230000.00</t>
         </is>
       </c>
       <c r="S200" s="0" t="inlineStr">
@@ -9338,7 +9348,7 @@
       </c>
       <c r="T200" s="0" t="inlineStr">
         <is>
-          <t>12000.00</t>
+          <t>300000.00</t>
         </is>
       </c>
       <c r="Z200" s="0" t="inlineStr">
@@ -9347,23 +9357,23 @@
         </is>
       </c>
       <c r="AA200" s="0">
-        <v>122</v>
+        <v>9</v>
       </c>
       <c r="AV200" s="0" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="201" spans="1:48">
       <c r="C201" s="0" t="inlineStr">
         <is>
-          <t>VICTOIRE MAGIC MEDIUM</t>
+          <t>VALANTINO</t>
         </is>
       </c>
       <c r="G201" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O201" s="0" t="inlineStr">
@@ -9373,7 +9383,7 @@
       </c>
       <c r="R201" s="0" t="inlineStr">
         <is>
-          <t>25000.00</t>
+          <t>10070.8693671806</t>
         </is>
       </c>
       <c r="S201" s="0" t="inlineStr">
@@ -9383,7 +9393,7 @@
       </c>
       <c r="T201" s="0" t="inlineStr">
         <is>
-          <t>30000.00</t>
+          <t>11000.00</t>
         </is>
       </c>
       <c r="Z201" s="0" t="inlineStr">
@@ -9392,23 +9402,23 @@
         </is>
       </c>
       <c r="AA201" s="0">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="AV201" s="0" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>135</t>
         </is>
       </c>
     </row>
     <row r="202" spans="1:48">
       <c r="C202" s="0" t="inlineStr">
         <is>
-          <t>VICTOIRE MAGIC PRINCESS</t>
+          <t>VALANTINO HOLLAND</t>
         </is>
       </c>
       <c r="G202" s="0" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O202" s="0" t="inlineStr">
@@ -9418,7 +9428,7 @@
       </c>
       <c r="R202" s="0" t="inlineStr">
         <is>
-          <t>175000.00</t>
+          <t>10500.00</t>
         </is>
       </c>
       <c r="S202" s="0" t="inlineStr">
@@ -9428,7 +9438,7 @@
       </c>
       <c r="T202" s="0" t="inlineStr">
         <is>
-          <t>210000.00</t>
+          <t>11000.00</t>
         </is>
       </c>
       <c r="Z202" s="0" t="inlineStr">
@@ -9437,23 +9447,28 @@
         </is>
       </c>
       <c r="AA202" s="0">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="AV202" s="0" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>157</t>
         </is>
       </c>
     </row>
     <row r="203" spans="1:48">
       <c r="C203" s="0" t="inlineStr">
         <is>
-          <t>VICTORY BROCADE</t>
+          <t>Vibes Metallic Cotton Satin</t>
         </is>
       </c>
       <c r="G203" s="0" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="H203" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
         </is>
       </c>
       <c r="O203" s="0" t="inlineStr">
@@ -9463,7 +9478,7 @@
       </c>
       <c r="R203" s="0" t="inlineStr">
         <is>
-          <t>8000.00</t>
+          <t>29000.00</t>
         </is>
       </c>
       <c r="S203" s="0" t="inlineStr">
@@ -9473,7 +9488,7 @@
       </c>
       <c r="T203" s="0" t="inlineStr">
         <is>
-          <t>14000.00</t>
+          <t>35000.00</t>
         </is>
       </c>
       <c r="Z203" s="0" t="inlineStr">
@@ -9482,18 +9497,18 @@
         </is>
       </c>
       <c r="AA203" s="0">
-        <v>120</v>
+        <v>322</v>
       </c>
       <c r="AV203" s="0" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>199</t>
         </is>
       </c>
     </row>
     <row r="204" spans="1:48">
       <c r="C204" s="0" t="inlineStr">
         <is>
-          <t>VIENNA YARD</t>
+          <t>VICE CHAIRMAN</t>
         </is>
       </c>
       <c r="G204" s="0" t="inlineStr">
@@ -9508,7 +9523,7 @@
       </c>
       <c r="R204" s="0" t="inlineStr">
         <is>
-          <t>1500.00</t>
+          <t>8151.5151515152</t>
         </is>
       </c>
       <c r="S204" s="0" t="inlineStr">
@@ -9518,7 +9533,7 @@
       </c>
       <c r="T204" s="0" t="inlineStr">
         <is>
-          <t>2500.00</t>
+          <t>12000.00</t>
         </is>
       </c>
       <c r="Z204" s="0" t="inlineStr">
@@ -9526,26 +9541,24 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA204" s="0" t="inlineStr">
-        <is>
-          <t>313.5</t>
-        </is>
+      <c r="AA204" s="0">
+        <v>122</v>
       </c>
       <c r="AV204" s="0" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>181</t>
         </is>
       </c>
     </row>
     <row r="205" spans="1:48">
       <c r="C205" s="0" t="inlineStr">
         <is>
-          <t>VLISCO LACE MIX AND MATCH</t>
+          <t>VICTOIRE MAGIC MEDIUM</t>
         </is>
       </c>
       <c r="G205" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O205" s="0" t="inlineStr">
@@ -9555,7 +9568,7 @@
       </c>
       <c r="R205" s="0" t="inlineStr">
         <is>
-          <t>370000.00</t>
+          <t>25000.00</t>
         </is>
       </c>
       <c r="S205" s="0" t="inlineStr">
@@ -9565,7 +9578,7 @@
       </c>
       <c r="T205" s="0" t="inlineStr">
         <is>
-          <t>420000.00</t>
+          <t>30000.00</t>
         </is>
       </c>
       <c r="Z205" s="0" t="inlineStr">
@@ -9574,23 +9587,23 @@
         </is>
       </c>
       <c r="AA205" s="0">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="AV205" s="0" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>56</t>
         </is>
       </c>
     </row>
     <row r="206" spans="1:48">
       <c r="C206" s="0" t="inlineStr">
         <is>
-          <t>VOILE EMBROIDERY MIX AND MATCH</t>
+          <t>VICTOIRE MAGIC PRINCESS</t>
         </is>
       </c>
       <c r="G206" s="0" t="inlineStr">
         <is>
-          <t>VOILE</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="O206" s="0" t="inlineStr">
@@ -9600,7 +9613,7 @@
       </c>
       <c r="R206" s="0" t="inlineStr">
         <is>
-          <t>33229.5081967213</t>
+          <t>175000.00</t>
         </is>
       </c>
       <c r="S206" s="0" t="inlineStr">
@@ -9610,7 +9623,7 @@
       </c>
       <c r="T206" s="0" t="inlineStr">
         <is>
-          <t>40000.00</t>
+          <t>210000.00</t>
         </is>
       </c>
       <c r="Z206" s="0" t="inlineStr">
@@ -9619,23 +9632,23 @@
         </is>
       </c>
       <c r="AA206" s="0">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AV206" s="0" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="207" spans="1:48">
       <c r="C207" s="0" t="inlineStr">
         <is>
-          <t>VOILE MATERIAL </t>
+          <t>VICTORY BROCADE</t>
         </is>
       </c>
       <c r="G207" s="0" t="inlineStr">
         <is>
-          <t>VOILE</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="O207" s="0" t="inlineStr">
@@ -9645,7 +9658,7 @@
       </c>
       <c r="R207" s="0" t="inlineStr">
         <is>
-          <t>27000.00</t>
+          <t>8000.00</t>
         </is>
       </c>
       <c r="S207" s="0" t="inlineStr">
@@ -9655,7 +9668,7 @@
       </c>
       <c r="T207" s="0" t="inlineStr">
         <is>
-          <t>32000.00</t>
+          <t>14000.00</t>
         </is>
       </c>
       <c r="Z207" s="0" t="inlineStr">
@@ -9664,23 +9677,23 @@
         </is>
       </c>
       <c r="AA207" s="0">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="AV207" s="0" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
     </row>
     <row r="208" spans="1:48">
       <c r="C208" s="0" t="inlineStr">
         <is>
-          <t>WAGAMBARI PLUS SHADDA</t>
+          <t>VIENNA YARD</t>
         </is>
       </c>
       <c r="G208" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>YARD</t>
         </is>
       </c>
       <c r="O208" s="0" t="inlineStr">
@@ -9690,7 +9703,7 @@
       </c>
       <c r="R208" s="0" t="inlineStr">
         <is>
-          <t>35000.00</t>
+          <t>1500.00</t>
         </is>
       </c>
       <c r="S208" s="0" t="inlineStr">
@@ -9700,7 +9713,7 @@
       </c>
       <c r="T208" s="0" t="inlineStr">
         <is>
-          <t>45000.00</t>
+          <t>2500.00</t>
         </is>
       </c>
       <c r="Z208" s="0" t="inlineStr">
@@ -9708,29 +9721,26 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA208" s="0">
-        <v>2</v>
+      <c r="AA208" s="0" t="inlineStr">
+        <is>
+          <t>313.5</t>
+        </is>
       </c>
       <c r="AV208" s="0" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>191</t>
         </is>
       </c>
     </row>
     <row r="209" spans="1:48">
       <c r="C209" s="0" t="inlineStr">
         <is>
-          <t>Win wax Holland</t>
+          <t>VLISCO LACE MIX AND MATCH</t>
         </is>
       </c>
       <c r="G209" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
-        </is>
-      </c>
-      <c r="H209" s="0" t="inlineStr">
-        <is>
-          <t>FAHAD TAHIR</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O209" s="0" t="inlineStr">
@@ -9740,7 +9750,7 @@
       </c>
       <c r="R209" s="0" t="inlineStr">
         <is>
-          <t>12000.00</t>
+          <t>370000.00</t>
         </is>
       </c>
       <c r="S209" s="0" t="inlineStr">
@@ -9750,7 +9760,7 @@
       </c>
       <c r="T209" s="0" t="inlineStr">
         <is>
-          <t>13000.00</t>
+          <t>420000.00</t>
         </is>
       </c>
       <c r="Z209" s="0" t="inlineStr">
@@ -9759,23 +9769,23 @@
         </is>
       </c>
       <c r="AA209" s="0">
-        <v>83</v>
+        <v>2</v>
       </c>
       <c r="AV209" s="0" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="210" spans="1:48">
       <c r="C210" s="0" t="inlineStr">
         <is>
-          <t>WOODIN LE CREATURE</t>
+          <t>VOILE EMBROIDERY MIX AND MATCH</t>
         </is>
       </c>
       <c r="G210" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>VOILE</t>
         </is>
       </c>
       <c r="O210" s="0" t="inlineStr">
@@ -9785,7 +9795,7 @@
       </c>
       <c r="R210" s="0" t="inlineStr">
         <is>
-          <t>13500.00</t>
+          <t>33229.5081967213</t>
         </is>
       </c>
       <c r="S210" s="0" t="inlineStr">
@@ -9795,7 +9805,7 @@
       </c>
       <c r="T210" s="0" t="inlineStr">
         <is>
-          <t>15000.00</t>
+          <t>40000.00</t>
         </is>
       </c>
       <c r="Z210" s="0" t="inlineStr">
@@ -9804,23 +9814,23 @@
         </is>
       </c>
       <c r="AA210" s="0">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="AV210" s="0" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="211" spans="1:48">
       <c r="C211" s="0" t="inlineStr">
         <is>
-          <t>ZAHRA BATIK</t>
+          <t>VOILE MATERIAL </t>
         </is>
       </c>
       <c r="G211" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>VOILE</t>
         </is>
       </c>
       <c r="O211" s="0" t="inlineStr">
@@ -9830,7 +9840,7 @@
       </c>
       <c r="R211" s="0" t="inlineStr">
         <is>
-          <t>25000.00</t>
+          <t>27000.00</t>
         </is>
       </c>
       <c r="S211" s="0" t="inlineStr">
@@ -9840,7 +9850,7 @@
       </c>
       <c r="T211" s="0" t="inlineStr">
         <is>
-          <t>26000.00</t>
+          <t>32000.00</t>
         </is>
       </c>
       <c r="Z211" s="0" t="inlineStr">
@@ -9849,54 +9859,239 @@
         </is>
       </c>
       <c r="AA211" s="0">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="AV211" s="0" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="212" spans="1:48">
       <c r="C212" s="0" t="inlineStr">
         <is>
+          <t>WAGAMBARI PLUS SHADDA</t>
+        </is>
+      </c>
+      <c r="G212" s="0" t="inlineStr">
+        <is>
+          <t>SHADDA</t>
+        </is>
+      </c>
+      <c r="O212" s="0" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R212" s="0" t="inlineStr">
+        <is>
+          <t>35000.00</t>
+        </is>
+      </c>
+      <c r="S212" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="T212" s="0" t="inlineStr">
+        <is>
+          <t>45000.00</t>
+        </is>
+      </c>
+      <c r="Z212" s="0" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="AA212" s="0">
+        <v>2</v>
+      </c>
+      <c r="AV212" s="0" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" spans="1:48">
+      <c r="C213" s="0" t="inlineStr">
+        <is>
+          <t>Win wax Holland</t>
+        </is>
+      </c>
+      <c r="G213" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="H213" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
+        </is>
+      </c>
+      <c r="O213" s="0" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R213" s="0" t="inlineStr">
+        <is>
+          <t>12000.00</t>
+        </is>
+      </c>
+      <c r="S213" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="T213" s="0" t="inlineStr">
+        <is>
+          <t>13000.00</t>
+        </is>
+      </c>
+      <c r="Z213" s="0" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="AA213" s="0">
+        <v>78</v>
+      </c>
+      <c r="AV213" s="0" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" spans="1:48">
+      <c r="C214" s="0" t="inlineStr">
+        <is>
+          <t>WOODIN LE CREATURE</t>
+        </is>
+      </c>
+      <c r="G214" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="O214" s="0" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R214" s="0" t="inlineStr">
+        <is>
+          <t>13500.00</t>
+        </is>
+      </c>
+      <c r="S214" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="T214" s="0" t="inlineStr">
+        <is>
+          <t>15000.00</t>
+        </is>
+      </c>
+      <c r="Z214" s="0" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="AA214" s="0">
+        <v>41</v>
+      </c>
+      <c r="AV214" s="0" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" spans="1:48">
+      <c r="C215" s="0" t="inlineStr">
+        <is>
+          <t>ZAHRA BATIK</t>
+        </is>
+      </c>
+      <c r="G215" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="O215" s="0" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R215" s="0" t="inlineStr">
+        <is>
+          <t>25000.00</t>
+        </is>
+      </c>
+      <c r="S215" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="T215" s="0" t="inlineStr">
+        <is>
+          <t>26000.00</t>
+        </is>
+      </c>
+      <c r="Z215" s="0" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="AA215" s="0">
+        <v>35</v>
+      </c>
+      <c r="AV215" s="0" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" spans="1:48">
+      <c r="C216" s="0" t="inlineStr">
+        <is>
           <t>ZAZMA METTALIC </t>
         </is>
       </c>
-      <c r="G212" s="0" t="inlineStr">
-        <is>
-          <t>ATAMPA</t>
-        </is>
-      </c>
-      <c r="O212" s="0" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="R212" s="0" t="inlineStr">
+      <c r="G216" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="O216" s="0" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R216" s="0" t="inlineStr">
         <is>
           <t>32000.00</t>
         </is>
       </c>
-      <c r="S212" s="0" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="T212" s="0" t="inlineStr">
+      <c r="S216" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="T216" s="0" t="inlineStr">
         <is>
           <t>35000.00</t>
         </is>
       </c>
-      <c r="Z212" s="0" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="AA212" s="0">
+      <c r="Z216" s="0" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="AA216" s="0">
         <v>41</v>
       </c>
-      <c r="AV212" s="0" t="inlineStr">
+      <c r="AV216" s="0" t="inlineStr">
         <is>
           <t>88</t>
         </is>

--- a/Excels/Items.xlsx
+++ b/Excels/Items.xlsx
@@ -331,7 +331,7 @@
         </is>
       </c>
       <c r="AA2" s="0">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AV2" s="0" t="inlineStr">
         <is>
@@ -376,7 +376,7 @@
         </is>
       </c>
       <c r="AA3" s="0">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AV3" s="0" t="inlineStr">
         <is>
@@ -421,7 +421,7 @@
         </is>
       </c>
       <c r="AA4" s="0">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="AV4" s="0" t="inlineStr">
         <is>
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="AA5" s="0">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="AV5" s="0" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="AA7" s="0">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AV7" s="0" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="AA9" s="0">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AV9" s="0" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="AA13" s="0">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AV13" s="0" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="AA17" s="0">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="AV17" s="0" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="AA18" s="0">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AV18" s="0" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="R19" s="0" t="inlineStr">
         <is>
-          <t>11501.0829302672</t>
+          <t>11500.0984482061</t>
         </is>
       </c>
       <c r="S19" s="0" t="inlineStr">
@@ -1101,7 +1101,7 @@
         </is>
       </c>
       <c r="AA19" s="0">
-        <v>15</v>
+        <v>165</v>
       </c>
       <c r="AV19" s="0" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="AA20" s="0">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="AV20" s="0" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="AA21" s="0">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="AV21" s="0" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="AA26" s="0">
-        <v>263</v>
+        <v>230</v>
       </c>
       <c r="AV26" s="0" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="AA27" s="0">
-        <v>657</v>
+        <v>627</v>
       </c>
       <c r="AV27" s="0" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="AA28" s="0">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AV28" s="0" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="R29" s="0" t="inlineStr">
         <is>
-          <t>7105.0495076194</t>
+          <t>6910.447761194</t>
         </is>
       </c>
       <c r="S29" s="0" t="inlineStr">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="AA29" s="0">
-        <v>38</v>
+        <v>307</v>
       </c>
       <c r="AV29" s="0" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="AA30" s="0">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="AV30" s="0" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="AA31" s="0">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AV31" s="0" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="AA32" s="0">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="AV32" s="0" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="AA33" s="0">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AV33" s="0" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="AA37" s="0">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AV37" s="0" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         </is>
       </c>
       <c r="AA38" s="0">
-        <v>1241</v>
+        <v>1203</v>
       </c>
       <c r="AV38" s="0" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="AA51" s="0">
-        <v>651</v>
+        <v>591</v>
       </c>
       <c r="AV51" s="0" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         </is>
       </c>
       <c r="AA63" s="0">
-        <v>682</v>
+        <v>665</v>
       </c>
       <c r="AV63" s="0" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="AA64" s="0">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AV64" s="0" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="AA66" s="0">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="AV66" s="0" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="AA67" s="0">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AV67" s="0" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="AA70" s="0">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AV70" s="0" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="AA71" s="0">
-        <v>717</v>
+        <v>640</v>
       </c>
       <c r="AV71" s="0" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="AA77" s="0">
-        <v>226</v>
+        <v>201</v>
       </c>
       <c r="AV77" s="0" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="AA80" s="0">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="AV80" s="0" t="inlineStr">
         <is>
@@ -3946,7 +3946,7 @@
         </is>
       </c>
       <c r="AA81" s="0">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AV81" s="0" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         </is>
       </c>
       <c r="AA83" s="0">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="AV83" s="0" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="AA84" s="0">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="AV84" s="0" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="AA85" s="0">
-        <v>214</v>
+        <v>175</v>
       </c>
       <c r="AV85" s="0" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="AA86" s="0">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="AV86" s="0" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         </is>
       </c>
       <c r="AA88" s="0">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="AV88" s="0" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         </is>
       </c>
       <c r="AA90" s="0">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV90" s="0" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="AA106" s="0">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AV106" s="0" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         </is>
       </c>
       <c r="AA107" s="0">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV107" s="0" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="AA110" s="0">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="AV110" s="0" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="AA111" s="0">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AV111" s="0" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         </is>
       </c>
       <c r="AA112" s="0">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="AV112" s="0" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
     <row r="114" spans="1:48">
       <c r="C114" s="0" t="inlineStr">
         <is>
-          <t>LAGOS LAFFAYA LACE A</t>
+          <t>Lagos lace G</t>
         </is>
       </c>
       <c r="G114" s="0" t="inlineStr">
@@ -5415,6 +5415,11 @@
           <t>LACE</t>
         </is>
       </c>
+      <c r="H114" s="0" t="inlineStr">
+        <is>
+          <t>Abba Tahir </t>
+        </is>
+      </c>
       <c r="O114" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -5422,7 +5427,7 @@
       </c>
       <c r="R114" s="0" t="inlineStr">
         <is>
-          <t>23000.00</t>
+          <t>12000.00</t>
         </is>
       </c>
       <c r="S114" s="0" t="inlineStr">
@@ -5432,7 +5437,7 @@
       </c>
       <c r="T114" s="0" t="inlineStr">
         <is>
-          <t>28000.00</t>
+          <t>15000.00</t>
         </is>
       </c>
       <c r="Z114" s="0" t="inlineStr">
@@ -5441,28 +5446,23 @@
         </is>
       </c>
       <c r="AA114" s="0">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AV114" s="0" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>222</t>
         </is>
       </c>
     </row>
     <row r="115" spans="1:48">
       <c r="C115" s="0" t="inlineStr">
         <is>
-          <t>Lagos laffaya lace B</t>
+          <t>LAGOS LAFFAYA LACE A</t>
         </is>
       </c>
       <c r="G115" s="0" t="inlineStr">
         <is>
-          <t>LAFAYYA</t>
-        </is>
-      </c>
-      <c r="H115" s="0" t="inlineStr">
-        <is>
-          <t>FAHAD TAHIR</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O115" s="0" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="R115" s="0" t="inlineStr">
         <is>
-          <t>16000.00</t>
+          <t>23000.00</t>
         </is>
       </c>
       <c r="S115" s="0" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="T115" s="0" t="inlineStr">
         <is>
-          <t>21000.00</t>
+          <t>28000.00</t>
         </is>
       </c>
       <c r="Z115" s="0" t="inlineStr">
@@ -5491,23 +5491,28 @@
         </is>
       </c>
       <c r="AA115" s="0">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AV115" s="0" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>149</t>
         </is>
       </c>
     </row>
     <row r="116" spans="1:48">
       <c r="C116" s="0" t="inlineStr">
         <is>
-          <t>LATEST ATAMPA APPLIQUE</t>
+          <t>Lagos laffaya lace B</t>
         </is>
       </c>
       <c r="G116" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>LAFAYYA</t>
+        </is>
+      </c>
+      <c r="H116" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
         </is>
       </c>
       <c r="O116" s="0" t="inlineStr">
@@ -5517,7 +5522,7 @@
       </c>
       <c r="R116" s="0" t="inlineStr">
         <is>
-          <t>280000.00</t>
+          <t>16000.00</t>
         </is>
       </c>
       <c r="S116" s="0" t="inlineStr">
@@ -5527,7 +5532,7 @@
       </c>
       <c r="T116" s="0" t="inlineStr">
         <is>
-          <t>350000.00</t>
+          <t>21000.00</t>
         </is>
       </c>
       <c r="Z116" s="0" t="inlineStr">
@@ -5536,18 +5541,18 @@
         </is>
       </c>
       <c r="AA116" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AV116" s="0" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>197</t>
         </is>
       </c>
     </row>
     <row r="117" spans="1:48">
       <c r="C117" s="0" t="inlineStr">
         <is>
-          <t>LATEST SHERATON SATIN WAX</t>
+          <t>LATEST ATAMPA APPLIQUE</t>
         </is>
       </c>
       <c r="G117" s="0" t="inlineStr">
@@ -5562,7 +5567,7 @@
       </c>
       <c r="R117" s="0" t="inlineStr">
         <is>
-          <t>265000.00</t>
+          <t>280000.00</t>
         </is>
       </c>
       <c r="S117" s="0" t="inlineStr">
@@ -5572,7 +5577,7 @@
       </c>
       <c r="T117" s="0" t="inlineStr">
         <is>
-          <t>300000.00</t>
+          <t>350000.00</t>
         </is>
       </c>
       <c r="Z117" s="0" t="inlineStr">
@@ -5581,18 +5586,18 @@
         </is>
       </c>
       <c r="AA117" s="0">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV117" s="0" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>57</t>
         </is>
       </c>
     </row>
     <row r="118" spans="1:48">
       <c r="C118" s="0" t="inlineStr">
         <is>
-          <t>LATEST ULTRA EMBELLISHED </t>
+          <t>LATEST SHERATON SATIN WAX</t>
         </is>
       </c>
       <c r="G118" s="0" t="inlineStr">
@@ -5607,7 +5612,7 @@
       </c>
       <c r="R118" s="0" t="inlineStr">
         <is>
-          <t>35124.0694789082</t>
+          <t>265000.00</t>
         </is>
       </c>
       <c r="S118" s="0" t="inlineStr">
@@ -5617,7 +5622,7 @@
       </c>
       <c r="T118" s="0" t="inlineStr">
         <is>
-          <t>40000.00</t>
+          <t>300000.00</t>
         </is>
       </c>
       <c r="Z118" s="0" t="inlineStr">
@@ -5626,23 +5631,23 @@
         </is>
       </c>
       <c r="AA118" s="0">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="AV118" s="0" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="119" spans="1:48">
       <c r="C119" s="0" t="inlineStr">
         <is>
-          <t>LEXIS AIR</t>
+          <t>LATEST ULTRA EMBELLISHED </t>
         </is>
       </c>
       <c r="G119" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O119" s="0" t="inlineStr">
@@ -5652,7 +5657,7 @@
       </c>
       <c r="R119" s="0" t="inlineStr">
         <is>
-          <t>6592.9070929071</t>
+          <t>35124.0694789082</t>
         </is>
       </c>
       <c r="S119" s="0" t="inlineStr">
@@ -5662,7 +5667,7 @@
       </c>
       <c r="T119" s="0" t="inlineStr">
         <is>
-          <t>9500.00</t>
+          <t>40000.00</t>
         </is>
       </c>
       <c r="Z119" s="0" t="inlineStr">
@@ -5671,23 +5676,23 @@
         </is>
       </c>
       <c r="AA119" s="0">
-        <v>805</v>
+        <v>178</v>
       </c>
       <c r="AV119" s="0" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>86</t>
         </is>
       </c>
     </row>
     <row r="120" spans="1:48">
       <c r="C120" s="0" t="inlineStr">
         <is>
-          <t>LONGHUA YARD COLLECTION</t>
+          <t>LEXIS AIR</t>
         </is>
       </c>
       <c r="G120" s="0" t="inlineStr">
         <is>
-          <t>YARD</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O120" s="0" t="inlineStr">
@@ -5697,7 +5702,7 @@
       </c>
       <c r="R120" s="0" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>6592.9070929071</t>
         </is>
       </c>
       <c r="S120" s="0" t="inlineStr">
@@ -5707,7 +5712,7 @@
       </c>
       <c r="T120" s="0" t="inlineStr">
         <is>
-          <t>4000.00</t>
+          <t>9500.00</t>
         </is>
       </c>
       <c r="Z120" s="0" t="inlineStr">
@@ -5715,26 +5720,24 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA120" s="0" t="inlineStr">
-        <is>
-          <t>384.5</t>
-        </is>
+      <c r="AA120" s="0">
+        <v>802</v>
       </c>
       <c r="AV120" s="0" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>173</t>
         </is>
       </c>
     </row>
     <row r="121" spans="1:48">
       <c r="C121" s="0" t="inlineStr">
         <is>
-          <t>Luxe Embellished MD</t>
+          <t>LONGHUA YARD COLLECTION</t>
         </is>
       </c>
       <c r="G121" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>YARD</t>
         </is>
       </c>
       <c r="O121" s="0" t="inlineStr">
@@ -5744,7 +5747,7 @@
       </c>
       <c r="R121" s="0" t="inlineStr">
         <is>
-          <t>14000.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="S121" s="0" t="inlineStr">
@@ -5754,7 +5757,7 @@
       </c>
       <c r="T121" s="0" t="inlineStr">
         <is>
-          <t>17000.00</t>
+          <t>4000.00</t>
         </is>
       </c>
       <c r="Z121" s="0" t="inlineStr">
@@ -5762,24 +5765,26 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA121" s="0">
-        <v>371</v>
+      <c r="AA121" s="0" t="inlineStr">
+        <is>
+          <t>380.5</t>
+        </is>
       </c>
       <c r="AV121" s="0" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>189</t>
         </is>
       </c>
     </row>
     <row r="122" spans="1:48">
       <c r="C122" s="0" t="inlineStr">
         <is>
-          <t>LUXURY AND VEBA PLUS</t>
+          <t>Luxe Embellished MD</t>
         </is>
       </c>
       <c r="G122" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O122" s="0" t="inlineStr">
@@ -5789,7 +5794,7 @@
       </c>
       <c r="R122" s="0" t="inlineStr">
         <is>
-          <t>7000.00</t>
+          <t>14000.00</t>
         </is>
       </c>
       <c r="S122" s="0" t="inlineStr">
@@ -5799,7 +5804,7 @@
       </c>
       <c r="T122" s="0" t="inlineStr">
         <is>
-          <t>8500.00</t>
+          <t>17000.00</t>
         </is>
       </c>
       <c r="Z122" s="0" t="inlineStr">
@@ -5808,18 +5813,18 @@
         </is>
       </c>
       <c r="AA122" s="0">
-        <v>188</v>
+        <v>309</v>
       </c>
       <c r="AV122" s="0" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>216</t>
         </is>
       </c>
     </row>
     <row r="123" spans="1:48">
       <c r="C123" s="0" t="inlineStr">
         <is>
-          <t>Madam Getzner Gold edition</t>
+          <t>LUXURY AND VEBA PLUS</t>
         </is>
       </c>
       <c r="G123" s="0" t="inlineStr">
@@ -5827,11 +5832,6 @@
           <t>SHADDA</t>
         </is>
       </c>
-      <c r="H123" s="0" t="inlineStr">
-        <is>
-          <t>FAHAD TAHIR</t>
-        </is>
-      </c>
       <c r="O123" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="R123" s="0" t="inlineStr">
         <is>
-          <t>30000.00</t>
+          <t>7000.00</t>
         </is>
       </c>
       <c r="S123" s="0" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="T123" s="0" t="inlineStr">
         <is>
-          <t>45000.00</t>
+          <t>8500.00</t>
         </is>
       </c>
       <c r="Z123" s="0" t="inlineStr">
@@ -5858,18 +5858,18 @@
         </is>
       </c>
       <c r="AA123" s="0">
-        <v>90</v>
+        <v>188</v>
       </c>
       <c r="AV123" s="0" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>175</t>
         </is>
       </c>
     </row>
     <row r="124" spans="1:48">
       <c r="C124" s="0" t="inlineStr">
         <is>
-          <t>MADAM GRTZNER MEDIUM</t>
+          <t>Madam Getzner Gold edition</t>
         </is>
       </c>
       <c r="G124" s="0" t="inlineStr">
@@ -5877,6 +5877,11 @@
           <t>SHADDA</t>
         </is>
       </c>
+      <c r="H124" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
+        </is>
+      </c>
       <c r="O124" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -5884,7 +5889,7 @@
       </c>
       <c r="R124" s="0" t="inlineStr">
         <is>
-          <t>5500.00</t>
+          <t>30000.00</t>
         </is>
       </c>
       <c r="S124" s="0" t="inlineStr">
@@ -5894,7 +5899,7 @@
       </c>
       <c r="T124" s="0" t="inlineStr">
         <is>
-          <t>7500.00</t>
+          <t>45000.00</t>
         </is>
       </c>
       <c r="Z124" s="0" t="inlineStr">
@@ -5903,28 +5908,23 @@
         </is>
       </c>
       <c r="AA124" s="0">
-        <v>741</v>
+        <v>86</v>
       </c>
       <c r="AV124" s="0" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>207</t>
         </is>
       </c>
     </row>
     <row r="125" spans="1:48">
       <c r="C125" s="0" t="inlineStr">
         <is>
-          <t>Magic holland</t>
+          <t>MADAM GRTZNER MEDIUM</t>
         </is>
       </c>
       <c r="G125" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
-        </is>
-      </c>
-      <c r="H125" s="0" t="inlineStr">
-        <is>
-          <t>YAYA SANI</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O125" s="0" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="R125" s="0" t="inlineStr">
         <is>
-          <t>9500.00</t>
+          <t>5500.00</t>
         </is>
       </c>
       <c r="S125" s="0" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="T125" s="0" t="inlineStr">
         <is>
-          <t>10500.00</t>
+          <t>7500.00</t>
         </is>
       </c>
       <c r="Z125" s="0" t="inlineStr">
@@ -5953,18 +5953,18 @@
         </is>
       </c>
       <c r="AA125" s="0">
-        <v>136</v>
+        <v>690</v>
       </c>
       <c r="AV125" s="0" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>55</t>
         </is>
       </c>
     </row>
     <row r="126" spans="1:48">
       <c r="C126" s="0" t="inlineStr">
         <is>
-          <t>Mandela kente Gold</t>
+          <t>Magic holland</t>
         </is>
       </c>
       <c r="G126" s="0" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="H126" s="0" t="inlineStr">
         <is>
-          <t>HAFIZU TAHIR SHOP</t>
+          <t>YAYA SANI</t>
         </is>
       </c>
       <c r="O126" s="0" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="R126" s="0" t="inlineStr">
         <is>
-          <t>14072.8155339806</t>
+          <t>9500.00</t>
         </is>
       </c>
       <c r="S126" s="0" t="inlineStr">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="T126" s="0" t="inlineStr">
         <is>
-          <t>15000.00</t>
+          <t>10500.00</t>
         </is>
       </c>
       <c r="Z126" s="0" t="inlineStr">
@@ -6003,18 +6003,18 @@
         </is>
       </c>
       <c r="AA126" s="0">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="AV126" s="0" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>206</t>
         </is>
       </c>
     </row>
     <row r="127" spans="1:48">
       <c r="C127" s="0" t="inlineStr">
         <is>
-          <t>MEDIUM EMBELLISHED </t>
+          <t>Mandela kente Gold</t>
         </is>
       </c>
       <c r="G127" s="0" t="inlineStr">
@@ -6022,6 +6022,11 @@
           <t>ATAMPA</t>
         </is>
       </c>
+      <c r="H127" s="0" t="inlineStr">
+        <is>
+          <t>HAFIZU TAHIR SHOP</t>
+        </is>
+      </c>
       <c r="O127" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -6029,7 +6034,7 @@
       </c>
       <c r="R127" s="0" t="inlineStr">
         <is>
-          <t>18000.00</t>
+          <t>14072.8155339806</t>
         </is>
       </c>
       <c r="S127" s="0" t="inlineStr">
@@ -6039,7 +6044,7 @@
       </c>
       <c r="T127" s="0" t="inlineStr">
         <is>
-          <t>20000.00</t>
+          <t>15000.00</t>
         </is>
       </c>
       <c r="Z127" s="0" t="inlineStr">
@@ -6048,18 +6053,18 @@
         </is>
       </c>
       <c r="AA127" s="0">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="AV127" s="0" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>219</t>
         </is>
       </c>
     </row>
     <row r="128" spans="1:48">
       <c r="C128" s="0" t="inlineStr">
         <is>
-          <t>MEDIUM GLITTER</t>
+          <t>MEDIUM EMBELLISHED </t>
         </is>
       </c>
       <c r="G128" s="0" t="inlineStr">
@@ -6074,7 +6079,7 @@
       </c>
       <c r="R128" s="0" t="inlineStr">
         <is>
-          <t>14500.00</t>
+          <t>18000.00</t>
         </is>
       </c>
       <c r="S128" s="0" t="inlineStr">
@@ -6084,7 +6089,7 @@
       </c>
       <c r="T128" s="0" t="inlineStr">
         <is>
-          <t>18000.00</t>
+          <t>20000.00</t>
         </is>
       </c>
       <c r="Z128" s="0" t="inlineStr">
@@ -6093,18 +6098,18 @@
         </is>
       </c>
       <c r="AA128" s="0">
-        <v>294</v>
+        <v>9</v>
       </c>
       <c r="AV128" s="0" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>113</t>
         </is>
       </c>
     </row>
     <row r="129" spans="1:48">
       <c r="C129" s="0" t="inlineStr">
         <is>
-          <t>MEDIUM SUPER </t>
+          <t>MEDIUM GLITTER</t>
         </is>
       </c>
       <c r="G129" s="0" t="inlineStr">
@@ -6119,7 +6124,7 @@
       </c>
       <c r="R129" s="0" t="inlineStr">
         <is>
-          <t>12541.1181181036</t>
+          <t>14500.00</t>
         </is>
       </c>
       <c r="S129" s="0" t="inlineStr">
@@ -6129,7 +6134,7 @@
       </c>
       <c r="T129" s="0" t="inlineStr">
         <is>
-          <t>14000.00</t>
+          <t>18000.00</t>
         </is>
       </c>
       <c r="Z129" s="0" t="inlineStr">
@@ -6138,28 +6143,23 @@
         </is>
       </c>
       <c r="AA129" s="0">
-        <v>83</v>
+        <v>281</v>
       </c>
       <c r="AV129" s="0" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>116</t>
         </is>
       </c>
     </row>
     <row r="130" spans="1:48">
       <c r="C130" s="0" t="inlineStr">
         <is>
-          <t>Mesh luxury lace</t>
+          <t>MEDIUM SUPER </t>
         </is>
       </c>
       <c r="G130" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
-        </is>
-      </c>
-      <c r="H130" s="0" t="inlineStr">
-        <is>
-          <t>FAHAD TAHIR</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O130" s="0" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="R130" s="0" t="inlineStr">
         <is>
-          <t>170000.00</t>
+          <t>12541.1181181036</t>
         </is>
       </c>
       <c r="S130" s="0" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="T130" s="0" t="inlineStr">
         <is>
-          <t>280000.00</t>
+          <t>14000.00</t>
         </is>
       </c>
       <c r="Z130" s="0" t="inlineStr">
@@ -6188,18 +6188,18 @@
         </is>
       </c>
       <c r="AA130" s="0">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="AV130" s="0" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>123</t>
         </is>
       </c>
     </row>
     <row r="131" spans="1:48">
       <c r="C131" s="0" t="inlineStr">
         <is>
-          <t>MITEX HOLLAND </t>
+          <t>Medium Super Embellished </t>
         </is>
       </c>
       <c r="G131" s="0" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="R131" s="0" t="inlineStr">
         <is>
-          <t>47000.00</t>
+          <t>13000.00</t>
         </is>
       </c>
       <c r="S131" s="0" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="T131" s="0" t="inlineStr">
         <is>
-          <t>55000.00</t>
+          <t>16000.00</t>
         </is>
       </c>
       <c r="Z131" s="0" t="inlineStr">
@@ -6233,23 +6233,28 @@
         </is>
       </c>
       <c r="AA131" s="0">
-        <v>2</v>
+        <v>345</v>
       </c>
       <c r="AV131" s="0" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>220</t>
         </is>
       </c>
     </row>
     <row r="132" spans="1:48">
       <c r="C132" s="0" t="inlineStr">
         <is>
-          <t>MOONLIGHT AND SUPREME FOLDER</t>
+          <t>Mesh luxury lace</t>
         </is>
       </c>
       <c r="G132" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>LACE</t>
+        </is>
+      </c>
+      <c r="H132" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
         </is>
       </c>
       <c r="O132" s="0" t="inlineStr">
@@ -6259,7 +6264,7 @@
       </c>
       <c r="R132" s="0" t="inlineStr">
         <is>
-          <t>5000.00</t>
+          <t>170000.00</t>
         </is>
       </c>
       <c r="S132" s="0" t="inlineStr">
@@ -6269,7 +6274,7 @@
       </c>
       <c r="T132" s="0" t="inlineStr">
         <is>
-          <t>6500.00</t>
+          <t>280000.00</t>
         </is>
       </c>
       <c r="Z132" s="0" t="inlineStr">
@@ -6278,18 +6283,18 @@
         </is>
       </c>
       <c r="AA132" s="0">
-        <v>167</v>
+        <v>11</v>
       </c>
       <c r="AV132" s="0" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>217</t>
         </is>
       </c>
     </row>
     <row r="133" spans="1:48">
       <c r="C133" s="0" t="inlineStr">
         <is>
-          <t>MUHANTEX EMBELLISHED</t>
+          <t>MITEX HOLLAND </t>
         </is>
       </c>
       <c r="G133" s="0" t="inlineStr">
@@ -6304,7 +6309,7 @@
       </c>
       <c r="R133" s="0" t="inlineStr">
         <is>
-          <t>15500.00</t>
+          <t>47000.00</t>
         </is>
       </c>
       <c r="S133" s="0" t="inlineStr">
@@ -6314,7 +6319,7 @@
       </c>
       <c r="T133" s="0" t="inlineStr">
         <is>
-          <t>18000.00</t>
+          <t>55000.00</t>
         </is>
       </c>
       <c r="Z133" s="0" t="inlineStr">
@@ -6323,18 +6328,18 @@
         </is>
       </c>
       <c r="AA133" s="0">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="AV133" s="0" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>84</t>
         </is>
       </c>
     </row>
     <row r="134" spans="1:48">
       <c r="C134" s="0" t="inlineStr">
         <is>
-          <t>NBTX 400</t>
+          <t>MOONLIGHT AND SUPREME FOLDER</t>
         </is>
       </c>
       <c r="G134" s="0" t="inlineStr">
@@ -6349,7 +6354,7 @@
       </c>
       <c r="R134" s="0" t="inlineStr">
         <is>
-          <t>22000.00</t>
+          <t>5000.00</t>
         </is>
       </c>
       <c r="S134" s="0" t="inlineStr">
@@ -6359,7 +6364,7 @@
       </c>
       <c r="T134" s="0" t="inlineStr">
         <is>
-          <t>25000.00</t>
+          <t>6500.00</t>
         </is>
       </c>
       <c r="Z134" s="0" t="inlineStr">
@@ -6368,18 +6373,18 @@
         </is>
       </c>
       <c r="AA134" s="0">
-        <v>6</v>
+        <v>135</v>
       </c>
       <c r="AV134" s="0" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>177</t>
         </is>
       </c>
     </row>
     <row r="135" spans="1:48">
       <c r="C135" s="0" t="inlineStr">
         <is>
-          <t>NEW JULIUS HOLLAND</t>
+          <t>MUHANTEX EMBELLISHED</t>
         </is>
       </c>
       <c r="G135" s="0" t="inlineStr">
@@ -6394,7 +6399,7 @@
       </c>
       <c r="R135" s="0" t="inlineStr">
         <is>
-          <t>62000.00</t>
+          <t>15500.00</t>
         </is>
       </c>
       <c r="S135" s="0" t="inlineStr">
@@ -6404,7 +6409,7 @@
       </c>
       <c r="T135" s="0" t="inlineStr">
         <is>
-          <t>70000.00</t>
+          <t>18000.00</t>
         </is>
       </c>
       <c r="Z135" s="0" t="inlineStr">
@@ -6417,14 +6422,14 @@
       </c>
       <c r="AV135" s="0" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>155</t>
         </is>
       </c>
     </row>
     <row r="136" spans="1:48">
       <c r="C136" s="0" t="inlineStr">
         <is>
-          <t>NEW MADAM MEDIUM GETZNER</t>
+          <t>NBTX 400</t>
         </is>
       </c>
       <c r="G136" s="0" t="inlineStr">
@@ -6439,7 +6444,7 @@
       </c>
       <c r="R136" s="0" t="inlineStr">
         <is>
-          <t>7000.00</t>
+          <t>22000.00</t>
         </is>
       </c>
       <c r="S136" s="0" t="inlineStr">
@@ -6449,7 +6454,7 @@
       </c>
       <c r="T136" s="0" t="inlineStr">
         <is>
-          <t>10000.00</t>
+          <t>25000.00</t>
         </is>
       </c>
       <c r="Z136" s="0" t="inlineStr">
@@ -6458,18 +6463,18 @@
         </is>
       </c>
       <c r="AA136" s="0">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="AV136" s="0" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>185</t>
         </is>
       </c>
     </row>
     <row r="137" spans="1:48">
       <c r="C137" s="0" t="inlineStr">
         <is>
-          <t>NEW MEDIUM GLITTER </t>
+          <t>NEW JULIUS HOLLAND</t>
         </is>
       </c>
       <c r="G137" s="0" t="inlineStr">
@@ -6484,7 +6489,7 @@
       </c>
       <c r="R137" s="0" t="inlineStr">
         <is>
-          <t>19000.00</t>
+          <t>62000.00</t>
         </is>
       </c>
       <c r="S137" s="0" t="inlineStr">
@@ -6494,7 +6499,7 @@
       </c>
       <c r="T137" s="0" t="inlineStr">
         <is>
-          <t>22000.00</t>
+          <t>70000.00</t>
         </is>
       </c>
       <c r="Z137" s="0" t="inlineStr">
@@ -6503,23 +6508,23 @@
         </is>
       </c>
       <c r="AA137" s="0">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="AV137" s="0" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>82</t>
         </is>
       </c>
     </row>
     <row r="138" spans="1:48">
       <c r="C138" s="0" t="inlineStr">
         <is>
-          <t>NEW POPULAR</t>
+          <t>NEW MADAM MEDIUM GETZNER</t>
         </is>
       </c>
       <c r="G138" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O138" s="0" t="inlineStr">
@@ -6529,7 +6534,7 @@
       </c>
       <c r="R138" s="0" t="inlineStr">
         <is>
-          <t>9000.00</t>
+          <t>7000.00</t>
         </is>
       </c>
       <c r="S138" s="0" t="inlineStr">
@@ -6548,18 +6553,18 @@
         </is>
       </c>
       <c r="AA138" s="0">
-        <v>233</v>
+        <v>21</v>
       </c>
       <c r="AV138" s="0" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>54</t>
         </is>
       </c>
     </row>
     <row r="139" spans="1:48">
       <c r="C139" s="0" t="inlineStr">
         <is>
-          <t>NEW SHERATON SATIN WAX</t>
+          <t>NEW MEDIUM GLITTER </t>
         </is>
       </c>
       <c r="G139" s="0" t="inlineStr">
@@ -6574,7 +6579,7 @@
       </c>
       <c r="R139" s="0" t="inlineStr">
         <is>
-          <t>230000.00</t>
+          <t>19000.00</t>
         </is>
       </c>
       <c r="S139" s="0" t="inlineStr">
@@ -6584,7 +6589,7 @@
       </c>
       <c r="T139" s="0" t="inlineStr">
         <is>
-          <t>250000.00</t>
+          <t>22000.00</t>
         </is>
       </c>
       <c r="Z139" s="0" t="inlineStr">
@@ -6593,18 +6598,18 @@
         </is>
       </c>
       <c r="AA139" s="0">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="AV139" s="0" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>110</t>
         </is>
       </c>
     </row>
     <row r="140" spans="1:48">
       <c r="C140" s="0" t="inlineStr">
         <is>
-          <t>NEW SUPER HOLLAND EMBELLISHED</t>
+          <t>NEW POPULAR</t>
         </is>
       </c>
       <c r="G140" s="0" t="inlineStr">
@@ -6619,7 +6624,7 @@
       </c>
       <c r="R140" s="0" t="inlineStr">
         <is>
-          <t>230000.00</t>
+          <t>9000.00</t>
         </is>
       </c>
       <c r="S140" s="0" t="inlineStr">
@@ -6629,7 +6634,7 @@
       </c>
       <c r="T140" s="0" t="inlineStr">
         <is>
-          <t>260000.00</t>
+          <t>10000.00</t>
         </is>
       </c>
       <c r="Z140" s="0" t="inlineStr">
@@ -6638,23 +6643,23 @@
         </is>
       </c>
       <c r="AA140" s="0">
-        <v>2</v>
+        <v>220</v>
       </c>
       <c r="AV140" s="0" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>133</t>
         </is>
       </c>
     </row>
     <row r="141" spans="1:48">
       <c r="C141" s="0" t="inlineStr">
         <is>
-          <t>NEW TRAVELLING AND SUPER POLISH</t>
+          <t>NEW SHERATON SATIN WAX</t>
         </is>
       </c>
       <c r="G141" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O141" s="0" t="inlineStr">
@@ -6664,7 +6669,7 @@
       </c>
       <c r="R141" s="0" t="inlineStr">
         <is>
-          <t>4000.00</t>
+          <t>230000.00</t>
         </is>
       </c>
       <c r="S141" s="0" t="inlineStr">
@@ -6674,7 +6679,7 @@
       </c>
       <c r="T141" s="0" t="inlineStr">
         <is>
-          <t>5000.00</t>
+          <t>250000.00</t>
         </is>
       </c>
       <c r="Z141" s="0" t="inlineStr">
@@ -6683,18 +6688,18 @@
         </is>
       </c>
       <c r="AA141" s="0">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="AV141" s="0" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="142" spans="1:48">
       <c r="C142" s="0" t="inlineStr">
         <is>
-          <t>NEW ULTRA EMBELLISHED</t>
+          <t>NEW SUPER HOLLAND EMBELLISHED</t>
         </is>
       </c>
       <c r="G142" s="0" t="inlineStr">
@@ -6709,7 +6714,7 @@
       </c>
       <c r="R142" s="0" t="inlineStr">
         <is>
-          <t>30532.1100917431</t>
+          <t>230000.00</t>
         </is>
       </c>
       <c r="S142" s="0" t="inlineStr">
@@ -6719,7 +6724,7 @@
       </c>
       <c r="T142" s="0" t="inlineStr">
         <is>
-          <t>35000.00</t>
+          <t>260000.00</t>
         </is>
       </c>
       <c r="Z142" s="0" t="inlineStr">
@@ -6728,23 +6733,23 @@
         </is>
       </c>
       <c r="AA142" s="0">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="AV142" s="0" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>72</t>
         </is>
       </c>
     </row>
     <row r="143" spans="1:48">
       <c r="C143" s="0" t="inlineStr">
         <is>
-          <t>PATCHWORK ATAMPA </t>
+          <t>NEW TRAVELLING AND SUPER POLISH</t>
         </is>
       </c>
       <c r="G143" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O143" s="0" t="inlineStr">
@@ -6754,7 +6759,7 @@
       </c>
       <c r="R143" s="0" t="inlineStr">
         <is>
-          <t>70000.00</t>
+          <t>4000.00</t>
         </is>
       </c>
       <c r="S143" s="0" t="inlineStr">
@@ -6764,7 +6769,7 @@
       </c>
       <c r="T143" s="0" t="inlineStr">
         <is>
-          <t>85000.00</t>
+          <t>5000.00</t>
         </is>
       </c>
       <c r="Z143" s="0" t="inlineStr">
@@ -6773,18 +6778,18 @@
         </is>
       </c>
       <c r="AA143" s="0">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AV143" s="0" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>179</t>
         </is>
       </c>
     </row>
     <row r="144" spans="1:48">
       <c r="C144" s="0" t="inlineStr">
         <is>
-          <t>PATCHWORK ATAMPA MIX AND MATCH</t>
+          <t>NEW ULTRA EMBELLISHED</t>
         </is>
       </c>
       <c r="G144" s="0" t="inlineStr">
@@ -6799,7 +6804,7 @@
       </c>
       <c r="R144" s="0" t="inlineStr">
         <is>
-          <t>54000.00</t>
+          <t>30532.1100917431</t>
         </is>
       </c>
       <c r="S144" s="0" t="inlineStr">
@@ -6809,7 +6814,7 @@
       </c>
       <c r="T144" s="0" t="inlineStr">
         <is>
-          <t>60000.00</t>
+          <t>35000.00</t>
         </is>
       </c>
       <c r="Z144" s="0" t="inlineStr">
@@ -6818,18 +6823,18 @@
         </is>
       </c>
       <c r="AA144" s="0">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="AV144" s="0" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>156</t>
         </is>
       </c>
     </row>
     <row r="145" spans="1:48">
       <c r="C145" s="0" t="inlineStr">
         <is>
-          <t>PERFECT ROYAL JAVA</t>
+          <t>PATCHWORK ATAMPA </t>
         </is>
       </c>
       <c r="G145" s="0" t="inlineStr">
@@ -6844,7 +6849,7 @@
       </c>
       <c r="R145" s="0" t="inlineStr">
         <is>
-          <t>30000.00</t>
+          <t>70000.00</t>
         </is>
       </c>
       <c r="S145" s="0" t="inlineStr">
@@ -6854,7 +6859,7 @@
       </c>
       <c r="T145" s="0" t="inlineStr">
         <is>
-          <t>35000.00</t>
+          <t>85000.00</t>
         </is>
       </c>
       <c r="Z145" s="0" t="inlineStr">
@@ -6863,18 +6868,18 @@
         </is>
       </c>
       <c r="AA145" s="0">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AV145" s="0" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>60</t>
         </is>
       </c>
     </row>
     <row r="146" spans="1:48">
       <c r="C146" s="0" t="inlineStr">
         <is>
-          <t>PRESTIGE EMBELLISHED</t>
+          <t>PATCHWORK ATAMPA MIX AND MATCH</t>
         </is>
       </c>
       <c r="G146" s="0" t="inlineStr">
@@ -6889,7 +6894,7 @@
       </c>
       <c r="R146" s="0" t="inlineStr">
         <is>
-          <t>15502.427184466</t>
+          <t>54000.00</t>
         </is>
       </c>
       <c r="S146" s="0" t="inlineStr">
@@ -6899,7 +6904,7 @@
       </c>
       <c r="T146" s="0" t="inlineStr">
         <is>
-          <t>17500.00</t>
+          <t>60000.00</t>
         </is>
       </c>
       <c r="Z146" s="0" t="inlineStr">
@@ -6908,23 +6913,23 @@
         </is>
       </c>
       <c r="AA146" s="0">
-        <v>166</v>
+        <v>11</v>
       </c>
       <c r="AV146" s="0" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>145</t>
         </is>
       </c>
     </row>
     <row r="147" spans="1:48">
       <c r="C147" s="0" t="inlineStr">
         <is>
-          <t>RIEDMAN MENLACE</t>
+          <t>PERFECT ROYAL JAVA</t>
         </is>
       </c>
       <c r="G147" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O147" s="0" t="inlineStr">
@@ -6934,7 +6939,7 @@
       </c>
       <c r="R147" s="0" t="inlineStr">
         <is>
-          <t>410000.00</t>
+          <t>30000.00</t>
         </is>
       </c>
       <c r="S147" s="0" t="inlineStr">
@@ -6944,7 +6949,7 @@
       </c>
       <c r="T147" s="0" t="inlineStr">
         <is>
-          <t>500000.00</t>
+          <t>35000.00</t>
         </is>
       </c>
       <c r="Z147" s="0" t="inlineStr">
@@ -6953,23 +6958,23 @@
         </is>
       </c>
       <c r="AA147" s="0">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AV147" s="0" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>94</t>
         </is>
       </c>
     </row>
     <row r="148" spans="1:48">
       <c r="C148" s="0" t="inlineStr">
         <is>
-          <t>RIEDMAN TAIWO ATIKU</t>
+          <t>PRESTIGE EMBELLISHED</t>
         </is>
       </c>
       <c r="G148" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O148" s="0" t="inlineStr">
@@ -6979,7 +6984,7 @@
       </c>
       <c r="R148" s="0" t="inlineStr">
         <is>
-          <t>260000.00</t>
+          <t>15502.427184466</t>
         </is>
       </c>
       <c r="S148" s="0" t="inlineStr">
@@ -6989,7 +6994,7 @@
       </c>
       <c r="T148" s="0" t="inlineStr">
         <is>
-          <t>380000.00</t>
+          <t>17500.00</t>
         </is>
       </c>
       <c r="Z148" s="0" t="inlineStr">
@@ -6997,26 +7002,24 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA148" s="0" t="inlineStr">
-        <is>
-          <t>19.5</t>
-        </is>
+      <c r="AA148" s="0">
+        <v>162</v>
       </c>
       <c r="AV148" s="0" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>118</t>
         </is>
       </c>
     </row>
     <row r="149" spans="1:48">
       <c r="C149" s="0" t="inlineStr">
         <is>
-          <t>RIGHTMAN AND WISEMAN</t>
+          <t>RIEDMAN MENLACE</t>
         </is>
       </c>
       <c r="G149" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O149" s="0" t="inlineStr">
@@ -7026,7 +7029,7 @@
       </c>
       <c r="R149" s="0" t="inlineStr">
         <is>
-          <t>4000.00</t>
+          <t>410000.00</t>
         </is>
       </c>
       <c r="S149" s="0" t="inlineStr">
@@ -7036,7 +7039,7 @@
       </c>
       <c r="T149" s="0" t="inlineStr">
         <is>
-          <t>5500.00</t>
+          <t>500000.00</t>
         </is>
       </c>
       <c r="Z149" s="0" t="inlineStr">
@@ -7045,23 +7048,23 @@
         </is>
       </c>
       <c r="AA149" s="0">
-        <v>488</v>
+        <v>6</v>
       </c>
       <c r="AV149" s="0" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>162</t>
         </is>
       </c>
     </row>
     <row r="150" spans="1:48">
       <c r="C150" s="0" t="inlineStr">
         <is>
-          <t>ROBA ATAMPA</t>
+          <t>RIEDMAN TAIWO ATIKU</t>
         </is>
       </c>
       <c r="G150" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O150" s="0" t="inlineStr">
@@ -7071,7 +7074,7 @@
       </c>
       <c r="R150" s="0" t="inlineStr">
         <is>
-          <t>2630.00</t>
+          <t>260000.00</t>
         </is>
       </c>
       <c r="S150" s="0" t="inlineStr">
@@ -7081,7 +7084,7 @@
       </c>
       <c r="T150" s="0" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>380000.00</t>
         </is>
       </c>
       <c r="Z150" s="0" t="inlineStr">
@@ -7089,29 +7092,26 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA150" s="0">
-        <v>721</v>
+      <c r="AA150" s="0" t="inlineStr">
+        <is>
+          <t>19.5</t>
+        </is>
       </c>
       <c r="AV150" s="0" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>164</t>
         </is>
       </c>
     </row>
     <row r="151" spans="1:48">
       <c r="C151" s="0" t="inlineStr">
         <is>
-          <t>Rotana holland</t>
+          <t>RIGHTMAN AND WISEMAN</t>
         </is>
       </c>
       <c r="G151" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
-        </is>
-      </c>
-      <c r="H151" s="0" t="inlineStr">
-        <is>
-          <t>YAYA SANI</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O151" s="0" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="R151" s="0" t="inlineStr">
         <is>
-          <t>8021.5189873418</t>
+          <t>4000.00</t>
         </is>
       </c>
       <c r="S151" s="0" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="T151" s="0" t="inlineStr">
         <is>
-          <t>8500.00</t>
+          <t>5500.00</t>
         </is>
       </c>
       <c r="Z151" s="0" t="inlineStr">
@@ -7140,23 +7140,23 @@
         </is>
       </c>
       <c r="AA151" s="0">
-        <v>67</v>
+        <v>473</v>
       </c>
       <c r="AV151" s="0" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>178</t>
         </is>
       </c>
     </row>
     <row r="152" spans="1:48">
       <c r="C152" s="0" t="inlineStr">
         <is>
-          <t>Shadda lace</t>
+          <t>ROBA ATAMPA</t>
         </is>
       </c>
       <c r="G152" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O152" s="0" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="R152" s="0" t="inlineStr">
         <is>
-          <t>25000.00</t>
+          <t>2630.00</t>
         </is>
       </c>
       <c r="S152" s="0" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="T152" s="0" t="inlineStr">
         <is>
-          <t>32000.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="Z152" s="0" t="inlineStr">
@@ -7185,23 +7185,28 @@
         </is>
       </c>
       <c r="AA152" s="0">
-        <v>9</v>
+        <v>689</v>
       </c>
       <c r="AV152" s="0" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>143</t>
         </is>
       </c>
     </row>
     <row r="153" spans="1:48">
       <c r="C153" s="0" t="inlineStr">
         <is>
-          <t>SHERATON BROCADE</t>
+          <t>Rotana holland</t>
         </is>
       </c>
       <c r="G153" s="0" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="H153" s="0" t="inlineStr">
+        <is>
+          <t>YAYA SANI</t>
         </is>
       </c>
       <c r="O153" s="0" t="inlineStr">
@@ -7211,7 +7216,7 @@
       </c>
       <c r="R153" s="0" t="inlineStr">
         <is>
-          <t>80000.00</t>
+          <t>8021.5189873418</t>
         </is>
       </c>
       <c r="S153" s="0" t="inlineStr">
@@ -7221,7 +7226,7 @@
       </c>
       <c r="T153" s="0" t="inlineStr">
         <is>
-          <t>100000.00</t>
+          <t>8500.00</t>
         </is>
       </c>
       <c r="Z153" s="0" t="inlineStr">
@@ -7230,23 +7235,23 @@
         </is>
       </c>
       <c r="AA153" s="0">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="AV153" s="0" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>214</t>
         </is>
       </c>
     </row>
     <row r="154" spans="1:48">
       <c r="C154" s="0" t="inlineStr">
         <is>
-          <t>SHERATON EXCLUSIVE EMBELLISHED</t>
+          <t>Shadda lace</t>
         </is>
       </c>
       <c r="G154" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O154" s="0" t="inlineStr">
@@ -7256,7 +7261,7 @@
       </c>
       <c r="R154" s="0" t="inlineStr">
         <is>
-          <t>244006.0851926978</t>
+          <t>25000.00</t>
         </is>
       </c>
       <c r="S154" s="0" t="inlineStr">
@@ -7266,7 +7271,7 @@
       </c>
       <c r="T154" s="0" t="inlineStr">
         <is>
-          <t>280000.00</t>
+          <t>32000.00</t>
         </is>
       </c>
       <c r="Z154" s="0" t="inlineStr">
@@ -7275,23 +7280,23 @@
         </is>
       </c>
       <c r="AA154" s="0">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AV154" s="0" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>205</t>
         </is>
       </c>
     </row>
     <row r="155" spans="1:48">
       <c r="C155" s="0" t="inlineStr">
         <is>
-          <t>SHERATON EXCLUSIVE PLAIN </t>
+          <t>SHERATON BROCADE</t>
         </is>
       </c>
       <c r="G155" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="O155" s="0" t="inlineStr">
@@ -7301,7 +7306,7 @@
       </c>
       <c r="R155" s="0" t="inlineStr">
         <is>
-          <t>200000.00</t>
+          <t>80000.00</t>
         </is>
       </c>
       <c r="S155" s="0" t="inlineStr">
@@ -7311,7 +7316,7 @@
       </c>
       <c r="T155" s="0" t="inlineStr">
         <is>
-          <t>220000.00</t>
+          <t>100000.00</t>
         </is>
       </c>
       <c r="Z155" s="0" t="inlineStr">
@@ -7320,18 +7325,18 @@
         </is>
       </c>
       <c r="AA155" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV155" s="0" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="156" spans="1:48">
       <c r="C156" s="0" t="inlineStr">
         <is>
-          <t>SHERATON HOLLAND EMBELLISHED</t>
+          <t>SHERATON EXCLUSIVE EMBELLISHED</t>
         </is>
       </c>
       <c r="G156" s="0" t="inlineStr">
@@ -7346,7 +7351,7 @@
       </c>
       <c r="R156" s="0" t="inlineStr">
         <is>
-          <t>210000.00</t>
+          <t>244006.0851926978</t>
         </is>
       </c>
       <c r="S156" s="0" t="inlineStr">
@@ -7356,7 +7361,7 @@
       </c>
       <c r="T156" s="0" t="inlineStr">
         <is>
-          <t>240000.00</t>
+          <t>280000.00</t>
         </is>
       </c>
       <c r="Z156" s="0" t="inlineStr">
@@ -7365,18 +7370,18 @@
         </is>
       </c>
       <c r="AA156" s="0">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AV156" s="0" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>70</t>
         </is>
       </c>
     </row>
     <row r="157" spans="1:48">
       <c r="C157" s="0" t="inlineStr">
         <is>
-          <t>SHERATON HOLLAND PLAIN</t>
+          <t>SHERATON EXCLUSIVE PLAIN </t>
         </is>
       </c>
       <c r="G157" s="0" t="inlineStr">
@@ -7391,7 +7396,7 @@
       </c>
       <c r="R157" s="0" t="inlineStr">
         <is>
-          <t>150000.00</t>
+          <t>200000.00</t>
         </is>
       </c>
       <c r="S157" s="0" t="inlineStr">
@@ -7401,7 +7406,7 @@
       </c>
       <c r="T157" s="0" t="inlineStr">
         <is>
-          <t>180000.00</t>
+          <t>220000.00</t>
         </is>
       </c>
       <c r="Z157" s="0" t="inlineStr">
@@ -7410,18 +7415,18 @@
         </is>
       </c>
       <c r="AA157" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AV157" s="0" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>71</t>
         </is>
       </c>
     </row>
     <row r="158" spans="1:48">
       <c r="C158" s="0" t="inlineStr">
         <is>
-          <t>SHERATON SATIN WAX</t>
+          <t>SHERATON HOLLAND EMBELLISHED</t>
         </is>
       </c>
       <c r="G158" s="0" t="inlineStr">
@@ -7436,7 +7441,7 @@
       </c>
       <c r="R158" s="0" t="inlineStr">
         <is>
-          <t>160000.00</t>
+          <t>210000.00</t>
         </is>
       </c>
       <c r="S158" s="0" t="inlineStr">
@@ -7446,7 +7451,7 @@
       </c>
       <c r="T158" s="0" t="inlineStr">
         <is>
-          <t>200000.00</t>
+          <t>240000.00</t>
         </is>
       </c>
       <c r="Z158" s="0" t="inlineStr">
@@ -7455,23 +7460,23 @@
         </is>
       </c>
       <c r="AA158" s="0">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="AV158" s="0" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>74</t>
         </is>
       </c>
     </row>
     <row r="159" spans="1:48">
       <c r="C159" s="0" t="inlineStr">
         <is>
-          <t>SMALL KAMPALA</t>
+          <t>SHERATON HOLLAND PLAIN</t>
         </is>
       </c>
       <c r="G159" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O159" s="0" t="inlineStr">
@@ -7481,7 +7486,7 @@
       </c>
       <c r="R159" s="0" t="inlineStr">
         <is>
-          <t>3500.00</t>
+          <t>150000.00</t>
         </is>
       </c>
       <c r="S159" s="0" t="inlineStr">
@@ -7491,7 +7496,7 @@
       </c>
       <c r="T159" s="0" t="inlineStr">
         <is>
-          <t>4500.00</t>
+          <t>180000.00</t>
         </is>
       </c>
       <c r="Z159" s="0" t="inlineStr">
@@ -7500,23 +7505,23 @@
         </is>
       </c>
       <c r="AA159" s="0">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="AV159" s="0" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>75</t>
         </is>
       </c>
     </row>
     <row r="160" spans="1:48">
       <c r="C160" s="0" t="inlineStr">
         <is>
-          <t>Sober And Queen VOILE EMBROIDERY </t>
+          <t>SHERATON SATIN WAX</t>
         </is>
       </c>
       <c r="G160" s="0" t="inlineStr">
         <is>
-          <t>VOILE</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O160" s="0" t="inlineStr">
@@ -7526,7 +7531,7 @@
       </c>
       <c r="R160" s="0" t="inlineStr">
         <is>
-          <t>32000.00</t>
+          <t>160000.00</t>
         </is>
       </c>
       <c r="S160" s="0" t="inlineStr">
@@ -7536,7 +7541,7 @@
       </c>
       <c r="T160" s="0" t="inlineStr">
         <is>
-          <t>40000.00</t>
+          <t>200000.00</t>
         </is>
       </c>
       <c r="Z160" s="0" t="inlineStr">
@@ -7545,23 +7550,23 @@
         </is>
       </c>
       <c r="AA160" s="0">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV160" s="0" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>69</t>
         </is>
       </c>
     </row>
     <row r="161" spans="1:48">
       <c r="C161" s="0" t="inlineStr">
         <is>
-          <t>SOLARI YARD COLLECTION</t>
+          <t>SMALL KAMPALA</t>
         </is>
       </c>
       <c r="G161" s="0" t="inlineStr">
         <is>
-          <t>YARD</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O161" s="0" t="inlineStr">
@@ -7571,7 +7576,7 @@
       </c>
       <c r="R161" s="0" t="inlineStr">
         <is>
-          <t>2000.00</t>
+          <t>3500.00</t>
         </is>
       </c>
       <c r="S161" s="0" t="inlineStr">
@@ -7581,7 +7586,7 @@
       </c>
       <c r="T161" s="0" t="inlineStr">
         <is>
-          <t>3000.00</t>
+          <t>4500.00</t>
         </is>
       </c>
       <c r="Z161" s="0" t="inlineStr">
@@ -7590,23 +7595,23 @@
         </is>
       </c>
       <c r="AA161" s="0">
-        <v>542</v>
+        <v>20</v>
       </c>
       <c r="AV161" s="0" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>154</t>
         </is>
       </c>
     </row>
     <row r="162" spans="1:48">
       <c r="C162" s="0" t="inlineStr">
         <is>
-          <t>STONE EMBELLISHED MIX ND MATCH</t>
+          <t>Sober And Queen VOILE EMBROIDERY </t>
         </is>
       </c>
       <c r="G162" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>VOILE</t>
         </is>
       </c>
       <c r="O162" s="0" t="inlineStr">
@@ -7616,7 +7621,7 @@
       </c>
       <c r="R162" s="0" t="inlineStr">
         <is>
-          <t>17000.00</t>
+          <t>32000.00</t>
         </is>
       </c>
       <c r="S162" s="0" t="inlineStr">
@@ -7626,7 +7631,7 @@
       </c>
       <c r="T162" s="0" t="inlineStr">
         <is>
-          <t>19000.00</t>
+          <t>40000.00</t>
         </is>
       </c>
       <c r="Z162" s="0" t="inlineStr">
@@ -7635,23 +7640,23 @@
         </is>
       </c>
       <c r="AA162" s="0">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AV162" s="0" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>45</t>
         </is>
       </c>
     </row>
     <row r="163" spans="1:48">
       <c r="C163" s="0" t="inlineStr">
         <is>
-          <t>SUBLIME COTED'VIORE</t>
+          <t>SOLARI YARD COLLECTION</t>
         </is>
       </c>
       <c r="G163" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>YARD</t>
         </is>
       </c>
       <c r="O163" s="0" t="inlineStr">
@@ -7661,7 +7666,7 @@
       </c>
       <c r="R163" s="0" t="inlineStr">
         <is>
-          <t>18500.00</t>
+          <t>2000.00</t>
         </is>
       </c>
       <c r="S163" s="0" t="inlineStr">
@@ -7671,7 +7676,7 @@
       </c>
       <c r="T163" s="0" t="inlineStr">
         <is>
-          <t>20000.00</t>
+          <t>3000.00</t>
         </is>
       </c>
       <c r="Z163" s="0" t="inlineStr">
@@ -7680,18 +7685,18 @@
         </is>
       </c>
       <c r="AA163" s="0">
-        <v>14</v>
+        <v>537</v>
       </c>
       <c r="AV163" s="0" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>190</t>
         </is>
       </c>
     </row>
     <row r="164" spans="1:48">
       <c r="C164" s="0" t="inlineStr">
         <is>
-          <t>SUBLIME STONE EMBELLISHED</t>
+          <t>STONE EMBELLISHED MIX ND MATCH</t>
         </is>
       </c>
       <c r="G164" s="0" t="inlineStr">
@@ -7706,7 +7711,7 @@
       </c>
       <c r="R164" s="0" t="inlineStr">
         <is>
-          <t>18000.00</t>
+          <t>17000.00</t>
         </is>
       </c>
       <c r="S164" s="0" t="inlineStr">
@@ -7716,7 +7721,7 @@
       </c>
       <c r="T164" s="0" t="inlineStr">
         <is>
-          <t>20000.00</t>
+          <t>19000.00</t>
         </is>
       </c>
       <c r="Z164" s="0" t="inlineStr">
@@ -7725,18 +7730,18 @@
         </is>
       </c>
       <c r="AA164" s="0">
-        <v>133</v>
+        <v>7</v>
       </c>
       <c r="AV164" s="0" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>112</t>
         </is>
       </c>
     </row>
     <row r="165" spans="1:48">
       <c r="C165" s="0" t="inlineStr">
         <is>
-          <t>SUPER BRILLIANT </t>
+          <t>SUBLIME COTED'VIORE</t>
         </is>
       </c>
       <c r="G165" s="0" t="inlineStr">
@@ -7751,7 +7756,7 @@
       </c>
       <c r="R165" s="0" t="inlineStr">
         <is>
-          <t>11000.00</t>
+          <t>18500.00</t>
         </is>
       </c>
       <c r="S165" s="0" t="inlineStr">
@@ -7761,7 +7766,7 @@
       </c>
       <c r="T165" s="0" t="inlineStr">
         <is>
-          <t>12000.00</t>
+          <t>20000.00</t>
         </is>
       </c>
       <c r="Z165" s="0" t="inlineStr">
@@ -7770,18 +7775,18 @@
         </is>
       </c>
       <c r="AA165" s="0">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="AV165" s="0" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>108</t>
         </is>
       </c>
     </row>
     <row r="166" spans="1:48">
       <c r="C166" s="0" t="inlineStr">
         <is>
-          <t>SUPER FAMOUS</t>
+          <t>SUBLIME STONE EMBELLISHED</t>
         </is>
       </c>
       <c r="G166" s="0" t="inlineStr">
@@ -7796,7 +7801,7 @@
       </c>
       <c r="R166" s="0" t="inlineStr">
         <is>
-          <t>9003.4277805886</t>
+          <t>18000.00</t>
         </is>
       </c>
       <c r="S166" s="0" t="inlineStr">
@@ -7806,7 +7811,7 @@
       </c>
       <c r="T166" s="0" t="inlineStr">
         <is>
-          <t>10000.00</t>
+          <t>20000.00</t>
         </is>
       </c>
       <c r="Z166" s="0" t="inlineStr">
@@ -7815,18 +7820,18 @@
         </is>
       </c>
       <c r="AA166" s="0">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="AV166" s="0" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>95</t>
         </is>
       </c>
     </row>
     <row r="167" spans="1:48">
       <c r="C167" s="0" t="inlineStr">
         <is>
-          <t>SUPER FASHION</t>
+          <t>SUPER BRILLIANT </t>
         </is>
       </c>
       <c r="G167" s="0" t="inlineStr">
@@ -7841,7 +7846,7 @@
       </c>
       <c r="R167" s="0" t="inlineStr">
         <is>
-          <t>10007.5373258309</t>
+          <t>11000.00</t>
         </is>
       </c>
       <c r="S167" s="0" t="inlineStr">
@@ -7851,7 +7856,7 @@
       </c>
       <c r="T167" s="0" t="inlineStr">
         <is>
-          <t>11000.00</t>
+          <t>12000.00</t>
         </is>
       </c>
       <c r="Z167" s="0" t="inlineStr">
@@ -7860,18 +7865,18 @@
         </is>
       </c>
       <c r="AA167" s="0">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AV167" s="0" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>127</t>
         </is>
       </c>
     </row>
     <row r="168" spans="1:48">
       <c r="C168" s="0" t="inlineStr">
         <is>
-          <t>SUPER HOLLAND EMBELLISHED</t>
+          <t>Super English ABC</t>
         </is>
       </c>
       <c r="G168" s="0" t="inlineStr">
@@ -7879,6 +7884,11 @@
           <t>ATAMPA</t>
         </is>
       </c>
+      <c r="H168" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
+        </is>
+      </c>
       <c r="O168" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -7886,7 +7896,7 @@
       </c>
       <c r="R168" s="0" t="inlineStr">
         <is>
-          <t>220000.00</t>
+          <t>12500.00</t>
         </is>
       </c>
       <c r="S168" s="0" t="inlineStr">
@@ -7896,7 +7906,7 @@
       </c>
       <c r="T168" s="0" t="inlineStr">
         <is>
-          <t>250000.00</t>
+          <t>15000.00</t>
         </is>
       </c>
       <c r="Z168" s="0" t="inlineStr">
@@ -7905,18 +7915,18 @@
         </is>
       </c>
       <c r="AA168" s="0">
-        <v>4</v>
+        <v>194</v>
       </c>
       <c r="AV168" s="0" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>221</t>
         </is>
       </c>
     </row>
     <row r="169" spans="1:48">
       <c r="C169" s="0" t="inlineStr">
         <is>
-          <t>SUPER HOLLAND WAX</t>
+          <t>SUPER FAMOUS</t>
         </is>
       </c>
       <c r="G169" s="0" t="inlineStr">
@@ -7931,7 +7941,7 @@
       </c>
       <c r="R169" s="0" t="inlineStr">
         <is>
-          <t>165381.0572182089</t>
+          <t>9003.0122920324</t>
         </is>
       </c>
       <c r="S169" s="0" t="inlineStr">
@@ -7941,7 +7951,7 @@
       </c>
       <c r="T169" s="0" t="inlineStr">
         <is>
-          <t>195000.00</t>
+          <t>10000.00</t>
         </is>
       </c>
       <c r="Z169" s="0" t="inlineStr">
@@ -7950,18 +7960,18 @@
         </is>
       </c>
       <c r="AA169" s="0">
-        <v>18</v>
+        <v>165</v>
       </c>
       <c r="AV169" s="0" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>137</t>
         </is>
       </c>
     </row>
     <row r="170" spans="1:48">
       <c r="C170" s="0" t="inlineStr">
         <is>
-          <t>SUPER WAX EMBELLISHED 4YRDS</t>
+          <t>SUPER FASHION</t>
         </is>
       </c>
       <c r="G170" s="0" t="inlineStr">
@@ -7976,7 +7986,7 @@
       </c>
       <c r="R170" s="0" t="inlineStr">
         <is>
-          <t>100000.00</t>
+          <t>10007.5373258309</t>
         </is>
       </c>
       <c r="S170" s="0" t="inlineStr">
@@ -7986,7 +7996,7 @@
       </c>
       <c r="T170" s="0" t="inlineStr">
         <is>
-          <t>120000.00</t>
+          <t>11000.00</t>
         </is>
       </c>
       <c r="Z170" s="0" t="inlineStr">
@@ -7995,18 +8005,18 @@
         </is>
       </c>
       <c r="AA170" s="0">
-        <v>3</v>
+        <v>87</v>
       </c>
       <c r="AV170" s="0" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>128</t>
         </is>
       </c>
     </row>
     <row r="171" spans="1:48">
       <c r="C171" s="0" t="inlineStr">
         <is>
-          <t>SUPER WAX MEDIUM</t>
+          <t>SUPER HOLLAND EMBELLISHED</t>
         </is>
       </c>
       <c r="G171" s="0" t="inlineStr">
@@ -8021,7 +8031,7 @@
       </c>
       <c r="R171" s="0" t="inlineStr">
         <is>
-          <t>14500.00</t>
+          <t>220000.00</t>
         </is>
       </c>
       <c r="S171" s="0" t="inlineStr">
@@ -8031,7 +8041,7 @@
       </c>
       <c r="T171" s="0" t="inlineStr">
         <is>
-          <t>16000.00</t>
+          <t>250000.00</t>
         </is>
       </c>
       <c r="Z171" s="0" t="inlineStr">
@@ -8040,23 +8050,23 @@
         </is>
       </c>
       <c r="AA171" s="0">
-        <v>102</v>
+        <v>4</v>
       </c>
       <c r="AV171" s="0" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>73</t>
         </is>
       </c>
     </row>
     <row r="172" spans="1:48">
       <c r="C172" s="0" t="inlineStr">
         <is>
-          <t>SUPREME PHANTOM</t>
+          <t>SUPER HOLLAND WAX</t>
         </is>
       </c>
       <c r="G172" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O172" s="0" t="inlineStr">
@@ -8066,7 +8076,7 @@
       </c>
       <c r="R172" s="0" t="inlineStr">
         <is>
-          <t>5500.00</t>
+          <t>165381.0572182089</t>
         </is>
       </c>
       <c r="S172" s="0" t="inlineStr">
@@ -8076,7 +8086,7 @@
       </c>
       <c r="T172" s="0" t="inlineStr">
         <is>
-          <t>7500.00</t>
+          <t>195000.00</t>
         </is>
       </c>
       <c r="Z172" s="0" t="inlineStr">
@@ -8085,23 +8095,23 @@
         </is>
       </c>
       <c r="AA172" s="0">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="AV172" s="0" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>76</t>
         </is>
       </c>
     </row>
     <row r="173" spans="1:48">
       <c r="C173" s="0" t="inlineStr">
         <is>
-          <t>SWISS LACE A</t>
+          <t>SUPER WAX EMBELLISHED 4YRDS</t>
         </is>
       </c>
       <c r="G173" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O173" s="0" t="inlineStr">
@@ -8111,7 +8121,7 @@
       </c>
       <c r="R173" s="0" t="inlineStr">
         <is>
-          <t>85078.125</t>
+          <t>100000.00</t>
         </is>
       </c>
       <c r="S173" s="0" t="inlineStr">
@@ -8121,7 +8131,7 @@
       </c>
       <c r="T173" s="0" t="inlineStr">
         <is>
-          <t>100000.00</t>
+          <t>120000.00</t>
         </is>
       </c>
       <c r="Z173" s="0" t="inlineStr">
@@ -8130,23 +8140,23 @@
         </is>
       </c>
       <c r="AA173" s="0">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AV173" s="0" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="174" spans="1:48">
       <c r="C174" s="0" t="inlineStr">
         <is>
-          <t>SWISS LACE B</t>
+          <t>SUPER WAX MEDIUM</t>
         </is>
       </c>
       <c r="G174" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O174" s="0" t="inlineStr">
@@ -8156,7 +8166,7 @@
       </c>
       <c r="R174" s="0" t="inlineStr">
         <is>
-          <t>74273.9898989899</t>
+          <t>14144.5497630332</t>
         </is>
       </c>
       <c r="S174" s="0" t="inlineStr">
@@ -8166,7 +8176,7 @@
       </c>
       <c r="T174" s="0" t="inlineStr">
         <is>
-          <t>85000.00</t>
+          <t>16000.00</t>
         </is>
       </c>
       <c r="Z174" s="0" t="inlineStr">
@@ -8175,23 +8185,23 @@
         </is>
       </c>
       <c r="AA174" s="0">
-        <v>18</v>
+        <v>382</v>
       </c>
       <c r="AV174" s="0" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>119</t>
         </is>
       </c>
     </row>
     <row r="175" spans="1:48">
       <c r="C175" s="0" t="inlineStr">
         <is>
-          <t>SWISS LACE B</t>
+          <t>SUPREME PHANTOM</t>
         </is>
       </c>
       <c r="G175" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O175" s="0" t="inlineStr">
@@ -8201,7 +8211,7 @@
       </c>
       <c r="R175" s="0" t="inlineStr">
         <is>
-          <t>75391.3043478261</t>
+          <t>5500.00</t>
         </is>
       </c>
       <c r="S175" s="0" t="inlineStr">
@@ -8211,7 +8221,7 @@
       </c>
       <c r="T175" s="0" t="inlineStr">
         <is>
-          <t>85000.00</t>
+          <t>7500.00</t>
         </is>
       </c>
       <c r="Z175" s="0" t="inlineStr">
@@ -8220,18 +8230,18 @@
         </is>
       </c>
       <c r="AA175" s="0">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="AV175" s="0" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>176</t>
         </is>
       </c>
     </row>
     <row r="176" spans="1:48">
       <c r="C176" s="0" t="inlineStr">
         <is>
-          <t>SWISS LACE C</t>
+          <t>SWISS LACE A</t>
         </is>
       </c>
       <c r="G176" s="0" t="inlineStr">
@@ -8246,7 +8256,7 @@
       </c>
       <c r="R176" s="0" t="inlineStr">
         <is>
-          <t>67000.00</t>
+          <t>85078.125</t>
         </is>
       </c>
       <c r="S176" s="0" t="inlineStr">
@@ -8256,7 +8266,7 @@
       </c>
       <c r="T176" s="0" t="inlineStr">
         <is>
-          <t>75000.00</t>
+          <t>100000.00</t>
         </is>
       </c>
       <c r="Z176" s="0" t="inlineStr">
@@ -8265,18 +8275,18 @@
         </is>
       </c>
       <c r="AA176" s="0">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV176" s="0" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="177" spans="1:48">
       <c r="C177" s="0" t="inlineStr">
         <is>
-          <t>SWISS LACE D</t>
+          <t>SWISS LACE B</t>
         </is>
       </c>
       <c r="G177" s="0" t="inlineStr">
@@ -8291,7 +8301,7 @@
       </c>
       <c r="R177" s="0" t="inlineStr">
         <is>
-          <t>53000.00</t>
+          <t>74273.9898989899</t>
         </is>
       </c>
       <c r="S177" s="0" t="inlineStr">
@@ -8301,7 +8311,7 @@
       </c>
       <c r="T177" s="0" t="inlineStr">
         <is>
-          <t>65000.00</t>
+          <t>85000.00</t>
         </is>
       </c>
       <c r="Z177" s="0" t="inlineStr">
@@ -8310,23 +8320,23 @@
         </is>
       </c>
       <c r="AA177" s="0">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AV177" s="0" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="178" spans="1:48">
       <c r="C178" s="0" t="inlineStr">
         <is>
-          <t>SWISS LAFAYA A</t>
+          <t>SWISS LACE B</t>
         </is>
       </c>
       <c r="G178" s="0" t="inlineStr">
         <is>
-          <t>LAFAYYA</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O178" s="0" t="inlineStr">
@@ -8336,7 +8346,7 @@
       </c>
       <c r="R178" s="0" t="inlineStr">
         <is>
-          <t>45000.00</t>
+          <t>75391.3043478261</t>
         </is>
       </c>
       <c r="S178" s="0" t="inlineStr">
@@ -8346,7 +8356,7 @@
       </c>
       <c r="T178" s="0" t="inlineStr">
         <is>
-          <t>60000.00</t>
+          <t>85000.00</t>
         </is>
       </c>
       <c r="Z178" s="0" t="inlineStr">
@@ -8355,23 +8365,23 @@
         </is>
       </c>
       <c r="AA178" s="0">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV178" s="0" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>161</t>
         </is>
       </c>
     </row>
     <row r="179" spans="1:48">
       <c r="C179" s="0" t="inlineStr">
         <is>
-          <t>SWISS LAFAYA B</t>
+          <t>SWISS LACE C</t>
         </is>
       </c>
       <c r="G179" s="0" t="inlineStr">
         <is>
-          <t>LAFAYYA</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O179" s="0" t="inlineStr">
@@ -8381,7 +8391,7 @@
       </c>
       <c r="R179" s="0" t="inlineStr">
         <is>
-          <t>48000.00</t>
+          <t>67000.00</t>
         </is>
       </c>
       <c r="S179" s="0" t="inlineStr">
@@ -8391,7 +8401,7 @@
       </c>
       <c r="T179" s="0" t="inlineStr">
         <is>
-          <t>55000.00</t>
+          <t>75000.00</t>
         </is>
       </c>
       <c r="Z179" s="0" t="inlineStr">
@@ -8400,23 +8410,23 @@
         </is>
       </c>
       <c r="AA179" s="0">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AV179" s="0" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="180" spans="1:48">
       <c r="C180" s="0" t="inlineStr">
         <is>
-          <t>SWISS LAFAYA C</t>
+          <t>SWISS LACE D</t>
         </is>
       </c>
       <c r="G180" s="0" t="inlineStr">
         <is>
-          <t>LAFAYYA</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O180" s="0" t="inlineStr">
@@ -8426,7 +8436,7 @@
       </c>
       <c r="R180" s="0" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>53000.00</t>
         </is>
       </c>
       <c r="S180" s="0" t="inlineStr">
@@ -8436,7 +8446,7 @@
       </c>
       <c r="T180" s="0" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>65000.00</t>
         </is>
       </c>
       <c r="Z180" s="0" t="inlineStr">
@@ -8444,16 +8454,19 @@
           <t>n</t>
         </is>
       </c>
+      <c r="AA180" s="0">
+        <v>7</v>
+      </c>
       <c r="AV180" s="0" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="181" spans="1:48">
       <c r="C181" s="0" t="inlineStr">
         <is>
-          <t>SWISS LAFAYA C</t>
+          <t>SWISS LAFAYA A</t>
         </is>
       </c>
       <c r="G181" s="0" t="inlineStr">
@@ -8468,7 +8481,7 @@
       </c>
       <c r="R181" s="0" t="inlineStr">
         <is>
-          <t>36000.00</t>
+          <t>45000.00</t>
         </is>
       </c>
       <c r="S181" s="0" t="inlineStr">
@@ -8478,7 +8491,7 @@
       </c>
       <c r="T181" s="0" t="inlineStr">
         <is>
-          <t>45000.00</t>
+          <t>60000.00</t>
         </is>
       </c>
       <c r="Z181" s="0" t="inlineStr">
@@ -8487,23 +8500,23 @@
         </is>
       </c>
       <c r="AA181" s="0">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="AV181" s="0" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="182" spans="1:48">
       <c r="C182" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY LACE A</t>
+          <t>SWISS LAFAYA B</t>
         </is>
       </c>
       <c r="G182" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>LAFAYYA</t>
         </is>
       </c>
       <c r="O182" s="0" t="inlineStr">
@@ -8513,7 +8526,7 @@
       </c>
       <c r="R182" s="0" t="inlineStr">
         <is>
-          <t>120000.00</t>
+          <t>48000.00</t>
         </is>
       </c>
       <c r="S182" s="0" t="inlineStr">
@@ -8523,7 +8536,7 @@
       </c>
       <c r="T182" s="0" t="inlineStr">
         <is>
-          <t>135000.00</t>
+          <t>55000.00</t>
         </is>
       </c>
       <c r="Z182" s="0" t="inlineStr">
@@ -8532,28 +8545,23 @@
         </is>
       </c>
       <c r="AA182" s="0">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="AV182" s="0" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="183" spans="1:48">
       <c r="C183" s="0" t="inlineStr">
         <is>
-          <t>Swiss luxury lace Aplus</t>
+          <t>SWISS LAFAYA C</t>
         </is>
       </c>
       <c r="G183" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
-        </is>
-      </c>
-      <c r="H183" s="0" t="inlineStr">
-        <is>
-          <t>FAHAD TAHIR</t>
+          <t>LAFAYYA</t>
         </is>
       </c>
       <c r="O183" s="0" t="inlineStr">
@@ -8563,7 +8571,7 @@
       </c>
       <c r="R183" s="0" t="inlineStr">
         <is>
-          <t>130000.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="S183" s="0" t="inlineStr">
@@ -8573,7 +8581,7 @@
       </c>
       <c r="T183" s="0" t="inlineStr">
         <is>
-          <t>165000.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Z183" s="0" t="inlineStr">
@@ -8581,24 +8589,21 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA183" s="0">
-        <v>0</v>
-      </c>
       <c r="AV183" s="0" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>29</t>
         </is>
       </c>
     </row>
     <row r="184" spans="1:48">
       <c r="C184" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY LACE B</t>
+          <t>SWISS LAFAYA C</t>
         </is>
       </c>
       <c r="G184" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>LAFAYYA</t>
         </is>
       </c>
       <c r="O184" s="0" t="inlineStr">
@@ -8608,7 +8613,7 @@
       </c>
       <c r="R184" s="0" t="inlineStr">
         <is>
-          <t>117202.7972027972</t>
+          <t>36000.00</t>
         </is>
       </c>
       <c r="S184" s="0" t="inlineStr">
@@ -8618,7 +8623,7 @@
       </c>
       <c r="T184" s="0" t="inlineStr">
         <is>
-          <t>130000.00</t>
+          <t>45000.00</t>
         </is>
       </c>
       <c r="Z184" s="0" t="inlineStr">
@@ -8627,18 +8632,18 @@
         </is>
       </c>
       <c r="AA184" s="0">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AV184" s="0" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>30</t>
         </is>
       </c>
     </row>
     <row r="185" spans="1:48">
       <c r="C185" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY LACE BIG A</t>
+          <t>SWISS LUXURY LACE A</t>
         </is>
       </c>
       <c r="G185" s="0" t="inlineStr">
@@ -8653,7 +8658,7 @@
       </c>
       <c r="R185" s="0" t="inlineStr">
         <is>
-          <t>220000.00</t>
+          <t>120000.00</t>
         </is>
       </c>
       <c r="S185" s="0" t="inlineStr">
@@ -8663,7 +8668,7 @@
       </c>
       <c r="T185" s="0" t="inlineStr">
         <is>
-          <t>270000.00</t>
+          <t>135000.00</t>
         </is>
       </c>
       <c r="Z185" s="0" t="inlineStr">
@@ -8672,18 +8677,18 @@
         </is>
       </c>
       <c r="AA185" s="0">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AV185" s="0" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="186" spans="1:48">
       <c r="C186" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY LACE BIG B</t>
+          <t>Swiss luxury lace Aplus</t>
         </is>
       </c>
       <c r="G186" s="0" t="inlineStr">
@@ -8691,6 +8696,11 @@
           <t>LACE</t>
         </is>
       </c>
+      <c r="H186" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
+        </is>
+      </c>
       <c r="O186" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -8698,7 +8708,7 @@
       </c>
       <c r="R186" s="0" t="inlineStr">
         <is>
-          <t>180000.00</t>
+          <t>130000.00</t>
         </is>
       </c>
       <c r="S186" s="0" t="inlineStr">
@@ -8708,7 +8718,7 @@
       </c>
       <c r="T186" s="0" t="inlineStr">
         <is>
-          <t>250000.00</t>
+          <t>165000.00</t>
         </is>
       </c>
       <c r="Z186" s="0" t="inlineStr">
@@ -8717,18 +8727,18 @@
         </is>
       </c>
       <c r="AA186" s="0">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV186" s="0" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>198</t>
         </is>
       </c>
     </row>
     <row r="187" spans="1:48">
       <c r="C187" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY LACE BIG C</t>
+          <t>SWISS LUXURY LACE B</t>
         </is>
       </c>
       <c r="G187" s="0" t="inlineStr">
@@ -8743,7 +8753,7 @@
       </c>
       <c r="R187" s="0" t="inlineStr">
         <is>
-          <t>180000.00</t>
+          <t>117202.7972027972</t>
         </is>
       </c>
       <c r="S187" s="0" t="inlineStr">
@@ -8753,7 +8763,7 @@
       </c>
       <c r="T187" s="0" t="inlineStr">
         <is>
-          <t>230000.00</t>
+          <t>130000.00</t>
         </is>
       </c>
       <c r="Z187" s="0" t="inlineStr">
@@ -8762,18 +8772,18 @@
         </is>
       </c>
       <c r="AA187" s="0">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AV187" s="0" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="188" spans="1:48">
       <c r="C188" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY LACE BIG D </t>
+          <t>SWISS LUXURY LACE BIG A</t>
         </is>
       </c>
       <c r="G188" s="0" t="inlineStr">
@@ -8788,7 +8798,7 @@
       </c>
       <c r="R188" s="0" t="inlineStr">
         <is>
-          <t>123750.00</t>
+          <t>220000.00</t>
         </is>
       </c>
       <c r="S188" s="0" t="inlineStr">
@@ -8798,7 +8808,7 @@
       </c>
       <c r="T188" s="0" t="inlineStr">
         <is>
-          <t>200000.00</t>
+          <t>270000.00</t>
         </is>
       </c>
       <c r="Z188" s="0" t="inlineStr">
@@ -8807,18 +8817,18 @@
         </is>
       </c>
       <c r="AA188" s="0">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AV188" s="0" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="189" spans="1:48">
       <c r="C189" s="0" t="inlineStr">
         <is>
-          <t>Swiss luxury lace Bplus</t>
+          <t>SWISS LUXURY LACE BIG B</t>
         </is>
       </c>
       <c r="G189" s="0" t="inlineStr">
@@ -8826,11 +8836,6 @@
           <t>LACE</t>
         </is>
       </c>
-      <c r="H189" s="0" t="inlineStr">
-        <is>
-          <t>FAHAD TAHIR</t>
-        </is>
-      </c>
       <c r="O189" s="0" t="inlineStr">
         <is>
           <t>y</t>
@@ -8838,7 +8843,7 @@
       </c>
       <c r="R189" s="0" t="inlineStr">
         <is>
-          <t>120000.00</t>
+          <t>180000.00</t>
         </is>
       </c>
       <c r="S189" s="0" t="inlineStr">
@@ -8848,7 +8853,7 @@
       </c>
       <c r="T189" s="0" t="inlineStr">
         <is>
-          <t>140000.00</t>
+          <t>250000.00</t>
         </is>
       </c>
       <c r="Z189" s="0" t="inlineStr">
@@ -8857,18 +8862,18 @@
         </is>
       </c>
       <c r="AA189" s="0">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV189" s="0" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="190" spans="1:48">
       <c r="C190" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY LACE C</t>
+          <t>SWISS LUXURY LACE BIG C</t>
         </is>
       </c>
       <c r="G190" s="0" t="inlineStr">
@@ -8883,7 +8888,7 @@
       </c>
       <c r="R190" s="0" t="inlineStr">
         <is>
-          <t>106000.00</t>
+          <t>180000.00</t>
         </is>
       </c>
       <c r="S190" s="0" t="inlineStr">
@@ -8893,7 +8898,7 @@
       </c>
       <c r="T190" s="0" t="inlineStr">
         <is>
-          <t>120000.00</t>
+          <t>230000.00</t>
         </is>
       </c>
       <c r="Z190" s="0" t="inlineStr">
@@ -8902,18 +8907,18 @@
         </is>
       </c>
       <c r="AA190" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV190" s="0" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="191" spans="1:48">
       <c r="C191" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY LACE D</t>
+          <t>SWISS LUXURY LACE BIG D </t>
         </is>
       </c>
       <c r="G191" s="0" t="inlineStr">
@@ -8928,7 +8933,7 @@
       </c>
       <c r="R191" s="0" t="inlineStr">
         <is>
-          <t>98164.3888673712</t>
+          <t>123750.00</t>
         </is>
       </c>
       <c r="S191" s="0" t="inlineStr">
@@ -8938,7 +8943,7 @@
       </c>
       <c r="T191" s="0" t="inlineStr">
         <is>
-          <t>110000.00</t>
+          <t>200000.00</t>
         </is>
       </c>
       <c r="Z191" s="0" t="inlineStr">
@@ -8947,23 +8952,28 @@
         </is>
       </c>
       <c r="AA191" s="0">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="AV191" s="0" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
     </row>
     <row r="192" spans="1:48">
       <c r="C192" s="0" t="inlineStr">
         <is>
-          <t>SWISS LUXURY VOILE</t>
+          <t>Swiss luxury lace Bplus</t>
         </is>
       </c>
       <c r="G192" s="0" t="inlineStr">
         <is>
-          <t>VOILE</t>
+          <t>LACE</t>
+        </is>
+      </c>
+      <c r="H192" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
         </is>
       </c>
       <c r="O192" s="0" t="inlineStr">
@@ -8973,7 +8983,7 @@
       </c>
       <c r="R192" s="0" t="inlineStr">
         <is>
-          <t>48656.00</t>
+          <t>120000.00</t>
         </is>
       </c>
       <c r="S192" s="0" t="inlineStr">
@@ -8983,7 +8993,7 @@
       </c>
       <c r="T192" s="0" t="inlineStr">
         <is>
-          <t>65000.00</t>
+          <t>140000.00</t>
         </is>
       </c>
       <c r="Z192" s="0" t="inlineStr">
@@ -8992,18 +9002,18 @@
         </is>
       </c>
       <c r="AA192" s="0">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="AV192" s="0" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>200</t>
         </is>
       </c>
     </row>
     <row r="193" spans="1:48">
       <c r="C193" s="0" t="inlineStr">
         <is>
-          <t>SWISS VOILE LACE A</t>
+          <t>SWISS LUXURY LACE C</t>
         </is>
       </c>
       <c r="G193" s="0" t="inlineStr">
@@ -9018,7 +9028,7 @@
       </c>
       <c r="R193" s="0" t="inlineStr">
         <is>
-          <t>150000.00</t>
+          <t>106000.00</t>
         </is>
       </c>
       <c r="S193" s="0" t="inlineStr">
@@ -9028,7 +9038,7 @@
       </c>
       <c r="T193" s="0" t="inlineStr">
         <is>
-          <t>280000.00</t>
+          <t>120000.00</t>
         </is>
       </c>
       <c r="Z193" s="0" t="inlineStr">
@@ -9037,18 +9047,18 @@
         </is>
       </c>
       <c r="AA193" s="0">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV193" s="0" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="194" spans="1:48">
       <c r="C194" s="0" t="inlineStr">
         <is>
-          <t>SWISS VOILE LACE B</t>
+          <t>SWISS LUXURY LACE D</t>
         </is>
       </c>
       <c r="G194" s="0" t="inlineStr">
@@ -9063,7 +9073,7 @@
       </c>
       <c r="R194" s="0" t="inlineStr">
         <is>
-          <t>135000.00</t>
+          <t>98164.3888673712</t>
         </is>
       </c>
       <c r="S194" s="0" t="inlineStr">
@@ -9073,7 +9083,7 @@
       </c>
       <c r="T194" s="0" t="inlineStr">
         <is>
-          <t>180000.00</t>
+          <t>110000.00</t>
         </is>
       </c>
       <c r="Z194" s="0" t="inlineStr">
@@ -9082,28 +9092,23 @@
         </is>
       </c>
       <c r="AA194" s="0">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="AV194" s="0" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>19</t>
         </is>
       </c>
     </row>
     <row r="195" spans="1:48">
       <c r="C195" s="0" t="inlineStr">
         <is>
-          <t>Two Color Mesh Lace</t>
+          <t>SWISS LUXURY VOILE</t>
         </is>
       </c>
       <c r="G195" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
-        </is>
-      </c>
-      <c r="H195" s="0" t="inlineStr">
-        <is>
-          <t>FAHAD TAHIR</t>
+          <t>VOILE</t>
         </is>
       </c>
       <c r="O195" s="0" t="inlineStr">
@@ -9113,7 +9118,7 @@
       </c>
       <c r="R195" s="0" t="inlineStr">
         <is>
-          <t>190000.00</t>
+          <t>48656.00</t>
         </is>
       </c>
       <c r="S195" s="0" t="inlineStr">
@@ -9123,7 +9128,7 @@
       </c>
       <c r="T195" s="0" t="inlineStr">
         <is>
-          <t>300000.00</t>
+          <t>65000.00</t>
         </is>
       </c>
       <c r="Z195" s="0" t="inlineStr">
@@ -9132,23 +9137,23 @@
         </is>
       </c>
       <c r="AA195" s="0">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="AV195" s="0" t="inlineStr">
         <is>
-          <t>218</t>
+          <t>44</t>
         </is>
       </c>
     </row>
     <row r="196" spans="1:48">
       <c r="C196" s="0" t="inlineStr">
         <is>
-          <t>TYCOON AND GAZA WOOL</t>
+          <t>SWISS VOILE LACE A</t>
         </is>
       </c>
       <c r="G196" s="0" t="inlineStr">
         <is>
-          <t>YARD</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O196" s="0" t="inlineStr">
@@ -9158,7 +9163,7 @@
       </c>
       <c r="R196" s="0" t="inlineStr">
         <is>
-          <t>4000.00</t>
+          <t>150000.00</t>
         </is>
       </c>
       <c r="S196" s="0" t="inlineStr">
@@ -9168,7 +9173,7 @@
       </c>
       <c r="T196" s="0" t="inlineStr">
         <is>
-          <t>5000.00</t>
+          <t>280000.00</t>
         </is>
       </c>
       <c r="Z196" s="0" t="inlineStr">
@@ -9177,18 +9182,18 @@
         </is>
       </c>
       <c r="AA196" s="0">
-        <v>598</v>
+        <v>2</v>
       </c>
       <c r="AV196" s="0" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="197" spans="1:48">
       <c r="C197" s="0" t="inlineStr">
         <is>
-          <t>ULTRA SWISS LACE A</t>
+          <t>SWISS VOILE LACE B</t>
         </is>
       </c>
       <c r="G197" s="0" t="inlineStr">
@@ -9203,7 +9208,7 @@
       </c>
       <c r="R197" s="0" t="inlineStr">
         <is>
-          <t>300000.00</t>
+          <t>135000.00</t>
         </is>
       </c>
       <c r="S197" s="0" t="inlineStr">
@@ -9213,7 +9218,7 @@
       </c>
       <c r="T197" s="0" t="inlineStr">
         <is>
-          <t>380000.00</t>
+          <t>180000.00</t>
         </is>
       </c>
       <c r="Z197" s="0" t="inlineStr">
@@ -9222,23 +9227,28 @@
         </is>
       </c>
       <c r="AA197" s="0">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV197" s="0" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="198" spans="1:48">
       <c r="C198" s="0" t="inlineStr">
         <is>
-          <t>ULTRA SWISS LACE B</t>
+          <t>Two Color Mesh Lace</t>
         </is>
       </c>
       <c r="G198" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="H198" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
         </is>
       </c>
       <c r="O198" s="0" t="inlineStr">
@@ -9248,7 +9258,7 @@
       </c>
       <c r="R198" s="0" t="inlineStr">
         <is>
-          <t>250000.00</t>
+          <t>190000.00</t>
         </is>
       </c>
       <c r="S198" s="0" t="inlineStr">
@@ -9258,7 +9268,7 @@
       </c>
       <c r="T198" s="0" t="inlineStr">
         <is>
-          <t>350000.00</t>
+          <t>300000.00</t>
         </is>
       </c>
       <c r="Z198" s="0" t="inlineStr">
@@ -9267,23 +9277,23 @@
         </is>
       </c>
       <c r="AA198" s="0">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="AV198" s="0" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>218</t>
         </is>
       </c>
     </row>
     <row r="199" spans="1:48">
       <c r="C199" s="0" t="inlineStr">
         <is>
-          <t>ULTRA SWISS LACE C</t>
+          <t>TYCOON AND GAZA WOOL</t>
         </is>
       </c>
       <c r="G199" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>YARD</t>
         </is>
       </c>
       <c r="O199" s="0" t="inlineStr">
@@ -9293,7 +9303,7 @@
       </c>
       <c r="R199" s="0" t="inlineStr">
         <is>
-          <t>253214.2857142857</t>
+          <t>4000.00</t>
         </is>
       </c>
       <c r="S199" s="0" t="inlineStr">
@@ -9303,7 +9313,7 @@
       </c>
       <c r="T199" s="0" t="inlineStr">
         <is>
-          <t>320000.00</t>
+          <t>5000.00</t>
         </is>
       </c>
       <c r="Z199" s="0" t="inlineStr">
@@ -9312,18 +9322,18 @@
         </is>
       </c>
       <c r="AA199" s="0">
-        <v>28</v>
+        <v>582</v>
       </c>
       <c r="AV199" s="0" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>187</t>
         </is>
       </c>
     </row>
     <row r="200" spans="1:48">
       <c r="C200" s="0" t="inlineStr">
         <is>
-          <t>ULTRA SWISS LACE D</t>
+          <t>ULTRA SWISS LACE A</t>
         </is>
       </c>
       <c r="G200" s="0" t="inlineStr">
@@ -9338,7 +9348,7 @@
       </c>
       <c r="R200" s="0" t="inlineStr">
         <is>
-          <t>230000.00</t>
+          <t>300000.00</t>
         </is>
       </c>
       <c r="S200" s="0" t="inlineStr">
@@ -9348,7 +9358,7 @@
       </c>
       <c r="T200" s="0" t="inlineStr">
         <is>
-          <t>300000.00</t>
+          <t>380000.00</t>
         </is>
       </c>
       <c r="Z200" s="0" t="inlineStr">
@@ -9357,23 +9367,23 @@
         </is>
       </c>
       <c r="AA200" s="0">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AV200" s="0" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="201" spans="1:48">
       <c r="C201" s="0" t="inlineStr">
         <is>
-          <t>VALANTINO</t>
+          <t>ULTRA SWISS LACE B</t>
         </is>
       </c>
       <c r="G201" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O201" s="0" t="inlineStr">
@@ -9383,7 +9393,7 @@
       </c>
       <c r="R201" s="0" t="inlineStr">
         <is>
-          <t>10070.8693671806</t>
+          <t>250000.00</t>
         </is>
       </c>
       <c r="S201" s="0" t="inlineStr">
@@ -9393,7 +9403,7 @@
       </c>
       <c r="T201" s="0" t="inlineStr">
         <is>
-          <t>11000.00</t>
+          <t>350000.00</t>
         </is>
       </c>
       <c r="Z201" s="0" t="inlineStr">
@@ -9402,23 +9412,23 @@
         </is>
       </c>
       <c r="AA201" s="0">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AV201" s="0" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="202" spans="1:48">
       <c r="C202" s="0" t="inlineStr">
         <is>
-          <t>VALANTINO HOLLAND</t>
+          <t>ULTRA SWISS LACE C</t>
         </is>
       </c>
       <c r="G202" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O202" s="0" t="inlineStr">
@@ -9428,7 +9438,7 @@
       </c>
       <c r="R202" s="0" t="inlineStr">
         <is>
-          <t>10500.00</t>
+          <t>253214.2857142857</t>
         </is>
       </c>
       <c r="S202" s="0" t="inlineStr">
@@ -9438,7 +9448,7 @@
       </c>
       <c r="T202" s="0" t="inlineStr">
         <is>
-          <t>11000.00</t>
+          <t>320000.00</t>
         </is>
       </c>
       <c r="Z202" s="0" t="inlineStr">
@@ -9447,28 +9457,23 @@
         </is>
       </c>
       <c r="AA202" s="0">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AV202" s="0" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="203" spans="1:48">
       <c r="C203" s="0" t="inlineStr">
         <is>
-          <t>Vibes Metallic Cotton Satin</t>
+          <t>ULTRA SWISS LACE D</t>
         </is>
       </c>
       <c r="G203" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
-        </is>
-      </c>
-      <c r="H203" s="0" t="inlineStr">
-        <is>
-          <t>FAHAD TAHIR</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O203" s="0" t="inlineStr">
@@ -9478,7 +9483,7 @@
       </c>
       <c r="R203" s="0" t="inlineStr">
         <is>
-          <t>29000.00</t>
+          <t>230000.00</t>
         </is>
       </c>
       <c r="S203" s="0" t="inlineStr">
@@ -9488,7 +9493,7 @@
       </c>
       <c r="T203" s="0" t="inlineStr">
         <is>
-          <t>35000.00</t>
+          <t>300000.00</t>
         </is>
       </c>
       <c r="Z203" s="0" t="inlineStr">
@@ -9497,23 +9502,23 @@
         </is>
       </c>
       <c r="AA203" s="0">
-        <v>322</v>
+        <v>9</v>
       </c>
       <c r="AV203" s="0" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="204" spans="1:48">
       <c r="C204" s="0" t="inlineStr">
         <is>
-          <t>VICE CHAIRMAN</t>
+          <t>VALANTINO</t>
         </is>
       </c>
       <c r="G204" s="0" t="inlineStr">
         <is>
-          <t>YARD</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O204" s="0" t="inlineStr">
@@ -9523,7 +9528,7 @@
       </c>
       <c r="R204" s="0" t="inlineStr">
         <is>
-          <t>8151.5151515152</t>
+          <t>10070.8693671806</t>
         </is>
       </c>
       <c r="S204" s="0" t="inlineStr">
@@ -9533,7 +9538,7 @@
       </c>
       <c r="T204" s="0" t="inlineStr">
         <is>
-          <t>12000.00</t>
+          <t>11000.00</t>
         </is>
       </c>
       <c r="Z204" s="0" t="inlineStr">
@@ -9542,23 +9547,23 @@
         </is>
       </c>
       <c r="AA204" s="0">
-        <v>122</v>
+        <v>31</v>
       </c>
       <c r="AV204" s="0" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>135</t>
         </is>
       </c>
     </row>
     <row r="205" spans="1:48">
       <c r="C205" s="0" t="inlineStr">
         <is>
-          <t>VICTOIRE MAGIC MEDIUM</t>
+          <t>VALANTINO HOLLAND</t>
         </is>
       </c>
       <c r="G205" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>ATAMPA</t>
         </is>
       </c>
       <c r="O205" s="0" t="inlineStr">
@@ -9568,7 +9573,7 @@
       </c>
       <c r="R205" s="0" t="inlineStr">
         <is>
-          <t>25000.00</t>
+          <t>10500.00</t>
         </is>
       </c>
       <c r="S205" s="0" t="inlineStr">
@@ -9578,7 +9583,7 @@
       </c>
       <c r="T205" s="0" t="inlineStr">
         <is>
-          <t>30000.00</t>
+          <t>11000.00</t>
         </is>
       </c>
       <c r="Z205" s="0" t="inlineStr">
@@ -9587,23 +9592,28 @@
         </is>
       </c>
       <c r="AA205" s="0">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AV205" s="0" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>157</t>
         </is>
       </c>
     </row>
     <row r="206" spans="1:48">
       <c r="C206" s="0" t="inlineStr">
         <is>
-          <t>VICTOIRE MAGIC PRINCESS</t>
+          <t>Vibes Metallic Cotton Satin</t>
         </is>
       </c>
       <c r="G206" s="0" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="H206" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
         </is>
       </c>
       <c r="O206" s="0" t="inlineStr">
@@ -9613,7 +9623,7 @@
       </c>
       <c r="R206" s="0" t="inlineStr">
         <is>
-          <t>175000.00</t>
+          <t>29000.00</t>
         </is>
       </c>
       <c r="S206" s="0" t="inlineStr">
@@ -9623,7 +9633,7 @@
       </c>
       <c r="T206" s="0" t="inlineStr">
         <is>
-          <t>210000.00</t>
+          <t>35000.00</t>
         </is>
       </c>
       <c r="Z206" s="0" t="inlineStr">
@@ -9632,23 +9642,23 @@
         </is>
       </c>
       <c r="AA206" s="0">
-        <v>85</v>
+        <v>313</v>
       </c>
       <c r="AV206" s="0" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>199</t>
         </is>
       </c>
     </row>
     <row r="207" spans="1:48">
       <c r="C207" s="0" t="inlineStr">
         <is>
-          <t>VICTORY BROCADE</t>
+          <t>VICE CHAIRMAN</t>
         </is>
       </c>
       <c r="G207" s="0" t="inlineStr">
         <is>
-          <t>MATERIAL</t>
+          <t>YARD</t>
         </is>
       </c>
       <c r="O207" s="0" t="inlineStr">
@@ -9658,7 +9668,7 @@
       </c>
       <c r="R207" s="0" t="inlineStr">
         <is>
-          <t>8000.00</t>
+          <t>8151.5151515152</t>
         </is>
       </c>
       <c r="S207" s="0" t="inlineStr">
@@ -9668,7 +9678,7 @@
       </c>
       <c r="T207" s="0" t="inlineStr">
         <is>
-          <t>14000.00</t>
+          <t>12000.00</t>
         </is>
       </c>
       <c r="Z207" s="0" t="inlineStr">
@@ -9677,23 +9687,23 @@
         </is>
       </c>
       <c r="AA207" s="0">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="AV207" s="0" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>181</t>
         </is>
       </c>
     </row>
     <row r="208" spans="1:48">
       <c r="C208" s="0" t="inlineStr">
         <is>
-          <t>VIENNA YARD</t>
+          <t>VICTOIRE MAGIC MEDIUM</t>
         </is>
       </c>
       <c r="G208" s="0" t="inlineStr">
         <is>
-          <t>YARD</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O208" s="0" t="inlineStr">
@@ -9703,7 +9713,7 @@
       </c>
       <c r="R208" s="0" t="inlineStr">
         <is>
-          <t>1500.00</t>
+          <t>25000.00</t>
         </is>
       </c>
       <c r="S208" s="0" t="inlineStr">
@@ -9713,7 +9723,7 @@
       </c>
       <c r="T208" s="0" t="inlineStr">
         <is>
-          <t>2500.00</t>
+          <t>30000.00</t>
         </is>
       </c>
       <c r="Z208" s="0" t="inlineStr">
@@ -9721,26 +9731,24 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA208" s="0" t="inlineStr">
-        <is>
-          <t>313.5</t>
-        </is>
+      <c r="AA208" s="0">
+        <v>43</v>
       </c>
       <c r="AV208" s="0" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>56</t>
         </is>
       </c>
     </row>
     <row r="209" spans="1:48">
       <c r="C209" s="0" t="inlineStr">
         <is>
-          <t>VLISCO LACE MIX AND MATCH</t>
+          <t>VICTOIRE MAGIC PRINCESS</t>
         </is>
       </c>
       <c r="G209" s="0" t="inlineStr">
         <is>
-          <t>LACE</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="O209" s="0" t="inlineStr">
@@ -9750,7 +9758,7 @@
       </c>
       <c r="R209" s="0" t="inlineStr">
         <is>
-          <t>370000.00</t>
+          <t>175000.00</t>
         </is>
       </c>
       <c r="S209" s="0" t="inlineStr">
@@ -9760,7 +9768,7 @@
       </c>
       <c r="T209" s="0" t="inlineStr">
         <is>
-          <t>420000.00</t>
+          <t>210000.00</t>
         </is>
       </c>
       <c r="Z209" s="0" t="inlineStr">
@@ -9769,23 +9777,23 @@
         </is>
       </c>
       <c r="AA209" s="0">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="AV209" s="0" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>50</t>
         </is>
       </c>
     </row>
     <row r="210" spans="1:48">
       <c r="C210" s="0" t="inlineStr">
         <is>
-          <t>VOILE EMBROIDERY MIX AND MATCH</t>
+          <t>VICTORY BROCADE</t>
         </is>
       </c>
       <c r="G210" s="0" t="inlineStr">
         <is>
-          <t>VOILE</t>
+          <t>MATERIAL</t>
         </is>
       </c>
       <c r="O210" s="0" t="inlineStr">
@@ -9795,7 +9803,7 @@
       </c>
       <c r="R210" s="0" t="inlineStr">
         <is>
-          <t>33229.5081967213</t>
+          <t>8000.00</t>
         </is>
       </c>
       <c r="S210" s="0" t="inlineStr">
@@ -9805,7 +9813,7 @@
       </c>
       <c r="T210" s="0" t="inlineStr">
         <is>
-          <t>40000.00</t>
+          <t>14000.00</t>
         </is>
       </c>
       <c r="Z210" s="0" t="inlineStr">
@@ -9814,23 +9822,23 @@
         </is>
       </c>
       <c r="AA210" s="0">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="AV210" s="0" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>53</t>
         </is>
       </c>
     </row>
     <row r="211" spans="1:48">
       <c r="C211" s="0" t="inlineStr">
         <is>
-          <t>VOILE MATERIAL </t>
+          <t>VIENNA YARD</t>
         </is>
       </c>
       <c r="G211" s="0" t="inlineStr">
         <is>
-          <t>VOILE</t>
+          <t>YARD</t>
         </is>
       </c>
       <c r="O211" s="0" t="inlineStr">
@@ -9840,7 +9848,7 @@
       </c>
       <c r="R211" s="0" t="inlineStr">
         <is>
-          <t>27000.00</t>
+          <t>1500.00</t>
         </is>
       </c>
       <c r="S211" s="0" t="inlineStr">
@@ -9850,7 +9858,7 @@
       </c>
       <c r="T211" s="0" t="inlineStr">
         <is>
-          <t>32000.00</t>
+          <t>2500.00</t>
         </is>
       </c>
       <c r="Z211" s="0" t="inlineStr">
@@ -9858,24 +9866,26 @@
           <t>n</t>
         </is>
       </c>
-      <c r="AA211" s="0">
-        <v>4</v>
+      <c r="AA211" s="0" t="inlineStr">
+        <is>
+          <t>313.5</t>
+        </is>
       </c>
       <c r="AV211" s="0" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>191</t>
         </is>
       </c>
     </row>
     <row r="212" spans="1:48">
       <c r="C212" s="0" t="inlineStr">
         <is>
-          <t>WAGAMBARI PLUS SHADDA</t>
+          <t>VLISCO LACE MIX AND MATCH</t>
         </is>
       </c>
       <c r="G212" s="0" t="inlineStr">
         <is>
-          <t>SHADDA</t>
+          <t>LACE</t>
         </is>
       </c>
       <c r="O212" s="0" t="inlineStr">
@@ -9885,7 +9895,7 @@
       </c>
       <c r="R212" s="0" t="inlineStr">
         <is>
-          <t>35000.00</t>
+          <t>370000.00</t>
         </is>
       </c>
       <c r="S212" s="0" t="inlineStr">
@@ -9895,7 +9905,7 @@
       </c>
       <c r="T212" s="0" t="inlineStr">
         <is>
-          <t>45000.00</t>
+          <t>420000.00</t>
         </is>
       </c>
       <c r="Z212" s="0" t="inlineStr">
@@ -9908,24 +9918,19 @@
       </c>
       <c r="AV212" s="0" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="213" spans="1:48">
       <c r="C213" s="0" t="inlineStr">
         <is>
-          <t>Win wax Holland</t>
+          <t>VOILE EMBROIDERY MIX AND MATCH</t>
         </is>
       </c>
       <c r="G213" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
-        </is>
-      </c>
-      <c r="H213" s="0" t="inlineStr">
-        <is>
-          <t>FAHAD TAHIR</t>
+          <t>VOILE</t>
         </is>
       </c>
       <c r="O213" s="0" t="inlineStr">
@@ -9935,7 +9940,7 @@
       </c>
       <c r="R213" s="0" t="inlineStr">
         <is>
-          <t>12000.00</t>
+          <t>33229.5081967213</t>
         </is>
       </c>
       <c r="S213" s="0" t="inlineStr">
@@ -9945,7 +9950,7 @@
       </c>
       <c r="T213" s="0" t="inlineStr">
         <is>
-          <t>13000.00</t>
+          <t>40000.00</t>
         </is>
       </c>
       <c r="Z213" s="0" t="inlineStr">
@@ -9954,23 +9959,23 @@
         </is>
       </c>
       <c r="AA213" s="0">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="AV213" s="0" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="214" spans="1:48">
       <c r="C214" s="0" t="inlineStr">
         <is>
-          <t>WOODIN LE CREATURE</t>
+          <t>VOILE MATERIAL </t>
         </is>
       </c>
       <c r="G214" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>VOILE</t>
         </is>
       </c>
       <c r="O214" s="0" t="inlineStr">
@@ -9980,7 +9985,7 @@
       </c>
       <c r="R214" s="0" t="inlineStr">
         <is>
-          <t>13500.00</t>
+          <t>27000.00</t>
         </is>
       </c>
       <c r="S214" s="0" t="inlineStr">
@@ -9990,7 +9995,7 @@
       </c>
       <c r="T214" s="0" t="inlineStr">
         <is>
-          <t>15000.00</t>
+          <t>32000.00</t>
         </is>
       </c>
       <c r="Z214" s="0" t="inlineStr">
@@ -9999,23 +10004,23 @@
         </is>
       </c>
       <c r="AA214" s="0">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="AV214" s="0" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>47</t>
         </is>
       </c>
     </row>
     <row r="215" spans="1:48">
       <c r="C215" s="0" t="inlineStr">
         <is>
-          <t>ZAHRA BATIK</t>
+          <t>WAGAMBARI PLUS SHADDA</t>
         </is>
       </c>
       <c r="G215" s="0" t="inlineStr">
         <is>
-          <t>ATAMPA</t>
+          <t>SHADDA</t>
         </is>
       </c>
       <c r="O215" s="0" t="inlineStr">
@@ -10025,7 +10030,7 @@
       </c>
       <c r="R215" s="0" t="inlineStr">
         <is>
-          <t>25000.00</t>
+          <t>35000.00</t>
         </is>
       </c>
       <c r="S215" s="0" t="inlineStr">
@@ -10035,7 +10040,7 @@
       </c>
       <c r="T215" s="0" t="inlineStr">
         <is>
-          <t>26000.00</t>
+          <t>45000.00</t>
         </is>
       </c>
       <c r="Z215" s="0" t="inlineStr">
@@ -10044,54 +10049,194 @@
         </is>
       </c>
       <c r="AA215" s="0">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="AV215" s="0" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>193</t>
         </is>
       </c>
     </row>
     <row r="216" spans="1:48">
       <c r="C216" s="0" t="inlineStr">
         <is>
+          <t>Win wax Holland</t>
+        </is>
+      </c>
+      <c r="G216" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="H216" s="0" t="inlineStr">
+        <is>
+          <t>FAHAD TAHIR</t>
+        </is>
+      </c>
+      <c r="O216" s="0" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R216" s="0" t="inlineStr">
+        <is>
+          <t>12000.00</t>
+        </is>
+      </c>
+      <c r="S216" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="T216" s="0" t="inlineStr">
+        <is>
+          <t>13000.00</t>
+        </is>
+      </c>
+      <c r="Z216" s="0" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="AA216" s="0">
+        <v>73</v>
+      </c>
+      <c r="AV216" s="0" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" spans="1:48">
+      <c r="C217" s="0" t="inlineStr">
+        <is>
+          <t>WOODIN LE CREATURE</t>
+        </is>
+      </c>
+      <c r="G217" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="O217" s="0" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R217" s="0" t="inlineStr">
+        <is>
+          <t>13500.00</t>
+        </is>
+      </c>
+      <c r="S217" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="T217" s="0" t="inlineStr">
+        <is>
+          <t>15000.00</t>
+        </is>
+      </c>
+      <c r="Z217" s="0" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="AA217" s="0">
+        <v>41</v>
+      </c>
+      <c r="AV217" s="0" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" spans="1:48">
+      <c r="C218" s="0" t="inlineStr">
+        <is>
+          <t>ZAHRA BATIK</t>
+        </is>
+      </c>
+      <c r="G218" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="O218" s="0" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R218" s="0" t="inlineStr">
+        <is>
+          <t>25000.00</t>
+        </is>
+      </c>
+      <c r="S218" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="T218" s="0" t="inlineStr">
+        <is>
+          <t>26000.00</t>
+        </is>
+      </c>
+      <c r="Z218" s="0" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="AA218" s="0">
+        <v>35</v>
+      </c>
+      <c r="AV218" s="0" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" spans="1:48">
+      <c r="C219" s="0" t="inlineStr">
+        <is>
           <t>ZAZMA METTALIC </t>
         </is>
       </c>
-      <c r="G216" s="0" t="inlineStr">
-        <is>
-          <t>ATAMPA</t>
-        </is>
-      </c>
-      <c r="O216" s="0" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="R216" s="0" t="inlineStr">
+      <c r="G219" s="0" t="inlineStr">
+        <is>
+          <t>ATAMPA</t>
+        </is>
+      </c>
+      <c r="O219" s="0" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R219" s="0" t="inlineStr">
         <is>
           <t>32000.00</t>
         </is>
       </c>
-      <c r="S216" s="0" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="T216" s="0" t="inlineStr">
+      <c r="S219" s="0" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="T219" s="0" t="inlineStr">
         <is>
           <t>35000.00</t>
         </is>
       </c>
-      <c r="Z216" s="0" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="AA216" s="0">
+      <c r="Z219" s="0" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="AA219" s="0">
         <v>41</v>
       </c>
-      <c r="AV216" s="0" t="inlineStr">
+      <c r="AV219" s="0" t="inlineStr">
         <is>
           <t>88</t>
         </is>
